--- a/Översikt NORRTÄLJE.xlsx
+++ b/Översikt NORRTÄLJE.xlsx
@@ -567,7 +567,7 @@
         <v>45135</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44757</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44249</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45757</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>44909</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45457</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45226</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45367</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45715</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44949</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45436</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>44263</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>45190</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>44550</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>45600</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>44467</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>45586.88145833334</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45638</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45688.38224537037</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>44846</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>44858</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>44650</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>44447</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45400.5958912037</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>45800</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>45068</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44544</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45748.6521875</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>45831.53390046296</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>44076</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44711</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>45784.32179398148</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>45783.58123842593</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44545</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>44336</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45722</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>45847.47052083333</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44839</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44300</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44749</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>44843</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>44279</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>45611.47233796296</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>44945</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>44698</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>45616.54866898148</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44866</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>45821</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>44370</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>44489</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>45219</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>44763</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>44872</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>45772.30234953704</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>45723</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>45772.31609953703</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>45609.37094907407</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>44670</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>45800</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>45847.47685185185</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>45446.35888888889</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>45226</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>44868</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44573</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>44102</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>44564.66387731482</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44161</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>44363</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>44788.70217592592</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44680</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>45225</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>45474</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>45735.54510416667</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44955.71322916666</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>45081</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>45082</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>45205</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>44855</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>45092</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>44956</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44695.43527777777</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>45784.54878472222</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>44620</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45794.63298611111</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>45798</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>44489</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>45841.5721875</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>45800</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>45687.34177083334</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45146</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>45532</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>45803.62766203703</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>45754</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>45065</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>44683</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>45741.38688657407</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>44704</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44965</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>45708</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>45826.46392361111</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45450.63958333333</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>44207</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>45468.45995370371</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44993</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>44863</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>45280</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>45609.83747685186</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>44210</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>44209</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>44306</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44650.86518518518</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>44642</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>44540</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>44650.8699537037</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44447</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>44833</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>44284.59546296296</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>44069</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>44330</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>44420</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>44420</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>44097</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>44728.73465277778</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>44777</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>44810.85092592592</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>44552</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>44560</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>44470.72148148148</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>44634</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>44581.75819444445</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>44771</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>44111.45320601852</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>44477.94327546296</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44380</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>44524</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>44399.43450231481</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44574.42978009259</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44516.72827546296</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>44103</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44868</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44834</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44309.47061342592</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>44400</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44161</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44252</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44451</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         <v>44858</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>44244</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>44626</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>44690</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>44682.79203703703</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>44496</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>44708</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>44642</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>44776</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>44103</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>44176</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>44746</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>44306</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>44214</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>44727</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>44845.47585648148</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>44694.57549768518</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>44495</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>44749.61980324074</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>44543</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>44543</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>44882.44732638889</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>44882</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>44224</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>44545.4189699074</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>44314</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>44279</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>44300</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>44722</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44742</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>44806.34577546296</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>44756.40881944444</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>44294</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>44124</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44330</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>44330</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>44511.69885416667</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>44510</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>44447</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>44435</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>44391.5580787037</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>44067</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>44867</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>44571</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>44453</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>44511</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>44495</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>44683</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>44201</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>44201</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44375</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44539</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44516.5275462963</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44496</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>44299</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>44694.57413194444</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44414.81494212963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44380</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44594.75950231482</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>44826</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44326</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44607</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44425</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44425</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44363.5784375</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>44575.52831018518</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>44712.83118055556</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>44769.62320601852</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44309</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>44251.43971064815</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>44698</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>44845.47672453704</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>44397</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44270</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44270</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44572</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>44543</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44543</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44526</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44650.92714120371</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44760</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44609</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44817.70516203704</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44545</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>44545</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44230</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44230</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44477</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>44725.49491898148</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>44427</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>44621</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44868</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44496.77542824074</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44251</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44580</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>44658</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>44100</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>44665.66407407408</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>44584.91538194445</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44678</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44300</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>44880.68423611111</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>44637</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>44777</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>44735</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>44816.89569444444</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>44682.75924768519</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18849,7 +18849,7 @@
         <v>44682.77616898148</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
         <v>44623</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>44637</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>44655.45373842592</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>44350</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>44143</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44763.4182175926</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>44105</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>44502</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>44132</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>44665.65474537037</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>44665.78351851852</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>44642.55565972222</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>44533</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>44466.37496527778</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>44153</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>44076</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>44595</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>44376</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19937,7 +19937,7 @@
         <v>44342</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>44704</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>44543</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>44682.76528935185</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>44735</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>44523.61635416667</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>44176</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>44595</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>44370.72197916666</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>44725</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>44333</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>44744</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>44350</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>44637</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>44815</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>44284</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>44495</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>45740.47288194444</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>45414.58650462963</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>45730.69143518519</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>45162</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>45679</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45554.55707175926</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44524</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44670.4190162037</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>45621.34813657407</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45139</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>44851</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>45092</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>44379</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45019.28847222222</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>45730.35026620371</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>45082.69179398148</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>45772.71221064815</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45215</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>44272</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>44743.47407407407</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>44266</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>44376</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>45482.53388888889</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22232,7 +22232,7 @@
         <v>45772.30436342592</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>45054</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22346,7 +22346,7 @@
         <v>45273</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>45075.91362268518</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>45075.91971064815</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>44764</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>45051.455</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>44098</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>45749</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45362.62811342593</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>44778.92797453704</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>44956</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>45691.41101851852</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>44956</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         <v>45772.29622685185</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45084.57695601852</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>45708.61761574074</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45203.63303240741</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>45257</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>44824.36069444445</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>44419</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>44803</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45772.3078125</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>45625</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>45208</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>44879.70518518519</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23724,7 +23724,7 @@
         <v>45729.60859953704</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>44833.40876157407</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>44687</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>45236.46369212963</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>45055.43509259259</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>45772.51127314815</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>44110</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>45405.57927083333</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>45735.59287037037</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24247,7 +24247,7 @@
         <v>45075</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>44315</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45735.36873842592</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>45705.66126157407</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>45764.6359837963</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45330.50098379629</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>44596.66335648148</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45218</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>44549</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>44145</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>44456</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>45063</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>45065.55917824074</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45356.4722800926</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
         <v>44285</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>45490.45342592592</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>45469</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44840</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>45433.58431712963</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>44459</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>44732</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45383</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>45056</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45530</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45435</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>44452</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>44124</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
         <v>44895</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>45218.65849537037</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>44817.56120370371</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>44390</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>45397</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45450.64208333333</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>45450</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45755.36583333334</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>44760</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44760</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>45022</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>44816</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45723</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>45223</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44272</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>45239</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>45089</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>44845.48064814815</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>45558.46283564815</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>44841.52804398148</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>45454.65774305556</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>45518</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45757.61421296297</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>45721.89123842592</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>44809</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>45740.47550925926</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>45740.47724537037</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27380,7 +27380,7 @@
         <v>45344</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45202</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45075.90270833333</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>45075.91042824074</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>45075.91265046296</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>45075.92153935185</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>45708</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>44962</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27851,7 +27851,7 @@
         <v>45089</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>44934</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>45548.72306712963</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>45131.666875</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>44866.63775462963</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>44778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28193,7 +28193,7 @@
         <v>44581</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>45376.55704861111</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>45448.56746527777</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>45257</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>45293.37263888889</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>45231.34144675926</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         <v>45418.6968287037</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>45104</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>45245</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>45245</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44992</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>44956.65920138889</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>44931.65626157408</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44483</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44362.37172453704</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>45460.45523148148</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>45293</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29172,7 +29172,7 @@
         <v>45063.35880787037</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>44956</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>45726.48377314815</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>44321</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>44472</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>45054.54091435186</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45054</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>45119.57728009259</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>45463.80486111111</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>45118</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29747,7 +29747,7 @@
         <v>45723</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29809,7 +29809,7 @@
         <v>45617.57439814815</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29866,7 +29866,7 @@
         <v>45457</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>45468.45628472222</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>44076</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
         <v>45706.60130787037</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>44900</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>44714.92253472222</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>44743.59504629629</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>45104</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30337,7 +30337,7 @@
         <v>45394.58778935186</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>45245</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>45356.47784722222</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30513,7 +30513,7 @@
         <v>45022.61003472222</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>45092</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30627,7 +30627,7 @@
         <v>44637</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30684,7 +30684,7 @@
         <v>44816</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>44470.72987268519</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>44834.38636574074</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30855,7 +30855,7 @@
         <v>44113</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30912,7 +30912,7 @@
         <v>45757.60658564815</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>44231</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         <v>44949</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>44643</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31145,7 +31145,7 @@
         <v>45760.91174768518</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>44949</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>45075.90703703704</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>45490.60572916667</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>44953.67443287037</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>45638.59979166667</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>45357</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         <v>44963</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>45524</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>45694.68207175926</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>45341.39853009259</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>45084.54459490741</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>45058.78607638889</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>45483.57244212963</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>44100</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>45600.86128472222</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>44869</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>45644.47878472223</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>44882</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>45086.3629050926</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>45253.55641203704</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44474.62141203704</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>45737.43347222222</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32476,7 +32476,7 @@
         <v>45169</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>45455.33037037037</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>45147.65222222222</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32652,7 +32652,7 @@
         <v>45147.65311342593</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>45147</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32766,7 +32766,7 @@
         <v>45175</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>44952.57989583333</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         <v>45469</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>45469</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>44556</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>44705.60626157407</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>44470</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>44621</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>45391.3395949074</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>44868.45741898148</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>45473.94501157408</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>44395</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>45259</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>45485</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33569,7 +33569,7 @@
         <v>44132</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>45253.63089120371</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33683,7 +33683,7 @@
         <v>45104</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>45104</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33797,7 +33797,7 @@
         <v>45776.62563657408</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>45316.60306712963</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33911,7 +33911,7 @@
         <v>45586</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>45776.47346064815</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>45776.46369212963</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34082,7 +34082,7 @@
         <v>45769</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>45776.59871527777</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>44540</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>45190.55609953704</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>45776.47122685185</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>45414.65855324074</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>44133</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>45089</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>45376.64532407407</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>44985</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>44904</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>44143</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>44901</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>44510</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>45576</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>44592</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>45721</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>44105</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>45783</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>45075.91148148148</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>45075</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>44145</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35341,7 +35341,7 @@
         <v>45418</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>45783.66429398148</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45783.48878472222</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45385.36243055556</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>45610.47414351852</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>45485.60261574074</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
         <v>45385.38146990741</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>45536</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>45549</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>44993.66707175926</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>44124</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44511.70518518519</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>45531</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>44977</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>45581</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>44525</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>45170</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>45187</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>45735</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44525</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44546</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>45709.39361111111</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44516</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>44516.40674768519</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>45468.45541666666</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36791,7 +36791,7 @@
         <v>45468.45747685185</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>45610.39271990741</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36905,7 +36905,7 @@
         <v>45442.45686342593</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36962,7 +36962,7 @@
         <v>45155</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37019,7 +37019,7 @@
         <v>44769.66039351852</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>44938</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37133,7 +37133,7 @@
         <v>45572.57828703704</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37190,7 +37190,7 @@
         <v>45271</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>45642.64634259259</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37304,7 +37304,7 @@
         <v>45460.44347222222</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>45260</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>45785.65300925926</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>44637</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45537</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45579</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>44179</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>44162</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>44325</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>44461</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>44959.74533564815</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>44902</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38003,7 +38003,7 @@
         <v>45831.56521990741</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>45443</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
         <v>45735</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>45735.60863425926</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>45352.74090277778</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38288,7 +38288,7 @@
         <v>45245</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>44578</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>45715</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>44108</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>45687</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45408.57707175926</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>44953.69298611111</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45533</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45547</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>44139.54078703704</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45534.38240740741</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>44923.90159722222</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>44183</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>45412.4104050926</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39101,7 +39101,7 @@
         <v>44585</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39163,7 +39163,7 @@
         <v>45786.55645833333</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>44584.91001157407</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>45177</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>45721.88684027778</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>45706.40086805556</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>45635.88849537037</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>45552.52827546297</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>45600.4558912037</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39629,7 +39629,7 @@
         <v>44945.67409722223</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>44937</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>45540</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>45145.51</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
         <v>45215</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39919,7 +39919,7 @@
         <v>44629</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>44617</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45692</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>44795</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>45075</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>45075</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40266,7 +40266,7 @@
         <v>45075.90934027778</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>45089</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>45155</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>45254</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>45260.43225694444</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45260.4333449074</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>45203.83891203703</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>45589.68289351852</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>44714.56040509259</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>44596</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45837.94081018519</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45835.46034722222</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45636.38974537037</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>45272.64479166667</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45272</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>45385.37922453704</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>45729.7271875</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41240,7 +41240,7 @@
         <v>45639.45166666667</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45205</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>45639.47385416667</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45629.65143518519</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41473,7 +41473,7 @@
         <v>45713</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>45436</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>45518</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45838.43261574074</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>45735</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>44888</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>44867.62090277778</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45701.44372685185</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>45644.90815972222</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45223</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45450.64643518518</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45475.61896990741</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45640.60240740741</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45600.47275462963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>44580</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45113</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>45113</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>44673</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>44611</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>44648</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>44643</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>44986.5887962963</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45835.4928125</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45048</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45837.93730324074</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45835.68076388889</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45740.47055555556</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>44708.67822916667</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>44775</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45223</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>45840.67829861111</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>45840.70885416667</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>44816</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45456</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>45798.66767361111</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43488,7 +43488,7 @@
         <v>45617.58453703704</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43545,7 +43545,7 @@
         <v>45839</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43602,7 +43602,7 @@
         <v>45786</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43659,7 +43659,7 @@
         <v>45121</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>45726.48152777777</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45070</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43830,7 +43830,7 @@
         <v>45798.67082175926</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43887,7 +43887,7 @@
         <v>45798</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43944,7 +43944,7 @@
         <v>45798.66104166667</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44001,7 +44001,7 @@
         <v>45797.58399305555</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44058,7 +44058,7 @@
         <v>44693</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44115,7 +44115,7 @@
         <v>44649</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44172,7 +44172,7 @@
         <v>44155.69458333333</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44229,7 +44229,7 @@
         <v>44963</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44286,7 +44286,7 @@
         <v>45112</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>44266</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44400,7 +44400,7 @@
         <v>44266</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
         <v>45837</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45839.62398148148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44571,7 +44571,7 @@
         <v>45232</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>44867</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>45735.36594907408</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
         <v>45729.71065972222</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44804,7 +44804,7 @@
         <v>45376.55484953704</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>45797.58350694444</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44918,7 +44918,7 @@
         <v>44819</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>44778</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45032,7 +45032,7 @@
         <v>45623.62563657408</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45094,7 +45094,7 @@
         <v>45386.34175925926</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45183</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45208,7 +45208,7 @@
         <v>44644</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45265,7 +45265,7 @@
         <v>45075</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45322,7 +45322,7 @@
         <v>45841.35611111111</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45379,7 +45379,7 @@
         <v>45478.42887731481</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>45712</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45498,7 +45498,7 @@
         <v>44635</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45555,7 +45555,7 @@
         <v>45348.46300925926</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45617,7 +45617,7 @@
         <v>44656</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45679,7 +45679,7 @@
         <v>45687.5038425926</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45741,7 +45741,7 @@
         <v>44670</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>45695.57881944445</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45860,7 +45860,7 @@
         <v>45608</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45917,7 +45917,7 @@
         <v>44803</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>45800</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>45617.62358796296</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>45800</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>45800</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>45069</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46279,7 +46279,7 @@
         <v>45841.5737962963</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45581</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46393,7 +46393,7 @@
         <v>45208.58004629629</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46450,7 +46450,7 @@
         <v>45799</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         <v>45693</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46564,7 +46564,7 @@
         <v>45730.42851851852</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>45092</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46683,7 +46683,7 @@
         <v>45092</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46740,7 +46740,7 @@
         <v>45840.62755787037</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46797,7 +46797,7 @@
         <v>45842.46885416667</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46854,7 +46854,7 @@
         <v>45427.88731481481</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46911,7 +46911,7 @@
         <v>45202.65660879629</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46968,7 +46968,7 @@
         <v>45664</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47025,7 +47025,7 @@
         <v>45800</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47082,7 +47082,7 @@
         <v>45075.90817129629</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47139,7 +47139,7 @@
         <v>45841.56996527778</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>45800</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47253,7 +47253,7 @@
         <v>45841.74596064815</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47310,7 +47310,7 @@
         <v>44797</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>45803.4675</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47424,7 +47424,7 @@
         <v>44624.59434027778</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47481,7 +47481,7 @@
         <v>45224</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47538,7 +47538,7 @@
         <v>45800</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47600,7 +47600,7 @@
         <v>45147.65407407407</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47657,7 +47657,7 @@
         <v>44687</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>45803.69228009259</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47776,7 +47776,7 @@
         <v>45559.54706018518</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47833,7 +47833,7 @@
         <v>45804.74479166666</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47890,7 +47890,7 @@
         <v>45757.65178240741</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47947,7 +47947,7 @@
         <v>45775.41451388889</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48004,7 +48004,7 @@
         <v>44243.33587962963</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48061,7 +48061,7 @@
         <v>45636.41572916666</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48118,7 +48118,7 @@
         <v>45020</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48175,7 +48175,7 @@
         <v>45139.51457175926</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48232,7 +48232,7 @@
         <v>45549</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48289,7 +48289,7 @@
         <v>44697</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48346,7 +48346,7 @@
         <v>44813</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>45614.39627314815</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48460,7 +48460,7 @@
         <v>45146</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>45803.66587962963</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>45522.44414351852</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45844.62609953704</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>45586</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45844.91234953704</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48812,7 +48812,7 @@
         <v>45685.44592592592</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>45376.54115740741</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>45757.62482638889</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48983,7 +48983,7 @@
         <v>45174.68702546296</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>45686.65545138889</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>45721.40780092592</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>44704</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45709.40231481481</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49278,7 +49278,7 @@
         <v>45847.37414351852</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>45022</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>44704</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49454,7 +49454,7 @@
         <v>44903</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>45168.44489583333</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49573,7 +49573,7 @@
         <v>45446.4287962963</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49630,7 +49630,7 @@
         <v>45670.65921296296</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49687,7 +49687,7 @@
         <v>44790</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49744,7 +49744,7 @@
         <v>45208</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49801,7 +49801,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49858,7 +49858,7 @@
         <v>45414</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>45237</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>45145.63584490741</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45411.54768518519</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50091,7 +50091,7 @@
         <v>44953.70481481482</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50148,7 +50148,7 @@
         <v>45847.48436342592</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50205,7 +50205,7 @@
         <v>45519</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50262,7 +50262,7 @@
         <v>45107.42538194444</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50319,7 +50319,7 @@
         <v>45111</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50376,7 +50376,7 @@
         <v>45700</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50438,7 +50438,7 @@
         <v>44680</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50495,7 +50495,7 @@
         <v>44266</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50552,7 +50552,7 @@
         <v>45810.42393518519</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50609,7 +50609,7 @@
         <v>45245</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50666,7 +50666,7 @@
         <v>44708</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50723,7 +50723,7 @@
         <v>44708.36708333333</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50785,7 +50785,7 @@
         <v>44974</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50842,7 +50842,7 @@
         <v>44746.58530092592</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50899,7 +50899,7 @@
         <v>45790.81410879629</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50956,7 +50956,7 @@
         <v>44771</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51013,7 +51013,7 @@
         <v>45679</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51070,7 +51070,7 @@
         <v>44684</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51127,7 +51127,7 @@
         <v>45127.69371527778</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51189,7 +51189,7 @@
         <v>45810.5333912037</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51246,7 +51246,7 @@
         <v>45245</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51303,7 +51303,7 @@
         <v>45748.53761574074</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51360,7 +51360,7 @@
         <v>45609.70778935185</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51422,7 +51422,7 @@
         <v>45609.85146990741</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
         <v>44743.59331018518</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51541,7 +51541,7 @@
         <v>44743.67418981482</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>45852.58030092593</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51660,7 +51660,7 @@
         <v>45427.89121527778</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51717,7 +51717,7 @@
         <v>45587.62565972222</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>45810.45236111111</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51831,7 +51831,7 @@
         <v>45810.45263888889</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51888,7 +51888,7 @@
         <v>44732</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>45208.70996527778</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52002,7 +52002,7 @@
         <v>45601.56726851852</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
         <v>45177.61498842593</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45635.44788194444</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>44763.40914351852</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52230,7 +52230,7 @@
         <v>45810.45633101852</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>45811.60451388889</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52344,7 +52344,7 @@
         <v>45630.52866898148</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52401,7 +52401,7 @@
         <v>44181</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52458,7 +52458,7 @@
         <v>45728.38924768518</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52515,7 +52515,7 @@
         <v>45667.49878472222</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52572,7 +52572,7 @@
         <v>44722</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52629,7 +52629,7 @@
         <v>44097</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52686,7 +52686,7 @@
         <v>45853</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52743,7 +52743,7 @@
         <v>44495.5893287037</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52800,7 +52800,7 @@
         <v>45853</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52857,7 +52857,7 @@
         <v>45128</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52914,7 +52914,7 @@
         <v>44749.55258101852</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52971,7 +52971,7 @@
         <v>44782</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -53028,7 +53028,7 @@
         <v>45855.68413194444</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -53090,7 +53090,7 @@
         <v>45855.57033564815</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -53152,7 +53152,7 @@
         <v>45813.63650462963</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53209,7 +53209,7 @@
         <v>45813.66961805556</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53266,7 +53266,7 @@
         <v>45813.6799537037</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53323,7 +53323,7 @@
         <v>45855.69387731481</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53385,7 +53385,7 @@
         <v>44799.65013888889</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53442,7 +53442,7 @@
         <v>45813.4709375</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53504,7 +53504,7 @@
         <v>45680.42665509259</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53561,7 +53561,7 @@
         <v>45293</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53623,7 +53623,7 @@
         <v>45219.56697916667</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53680,7 +53680,7 @@
         <v>45728.38409722222</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53737,7 +53737,7 @@
         <v>44813.59915509259</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53794,7 +53794,7 @@
         <v>44325</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53851,7 +53851,7 @@
         <v>45376.55638888889</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53913,7 +53913,7 @@
         <v>45817.2565625</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53970,7 +53970,7 @@
         <v>45817.30329861111</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -54027,7 +54027,7 @@
         <v>45817.31085648148</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -54084,7 +54084,7 @@
         <v>45817.31708333334</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -54141,7 +54141,7 @@
         <v>45817.31986111111</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -54198,7 +54198,7 @@
         <v>45817.33503472222</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45859</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45859</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>44719</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45747.63471064815</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45817.291875</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45254.41509259259</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45817.32538194444</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>44980</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>45700</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45817.25471064815</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>44690</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45817.34083333334</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45840</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45835</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -55058,7 +55058,7 @@
         <v>45743.44953703704</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45707.84997685185</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>44777</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55229,7 +55229,7 @@
         <v>45085</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
         <v>45730.69502314815</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>45243.45289351852</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>44925</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55462,7 +55462,7 @@
         <v>45188.41637731482</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>45168.40565972222</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>44760</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>45042.74291666667</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55700,7 +55700,7 @@
         <v>44375</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55757,7 +55757,7 @@
         <v>45219</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45442</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45824.37275462963</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55933,7 +55933,7 @@
         <v>44111.44373842593</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45068.51783564815</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -56047,7 +56047,7 @@
         <v>44806.41576388889</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>44783</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>44785</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -56223,7 +56223,7 @@
         <v>45394.72869212963</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56280,7 +56280,7 @@
         <v>45063</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56337,7 +56337,7 @@
         <v>45868.62267361111</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56394,7 +56394,7 @@
         <v>45706.61178240741</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56456,7 +56456,7 @@
         <v>44398</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56518,7 +56518,7 @@
         <v>45845</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56575,7 +56575,7 @@
         <v>45191</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56637,7 +56637,7 @@
         <v>44510.51422453704</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56699,7 +56699,7 @@
         <v>45831.51659722222</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56756,7 +56756,7 @@
         <v>44815.74539351852</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56813,7 +56813,7 @@
         <v>45831.65079861111</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
         <v>45293</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56937,7 +56937,7 @@
         <v>45019.3959837963</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>44380.77346064815</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -57051,7 +57051,7 @@
         <v>45771</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -57108,7 +57108,7 @@
         <v>45345.6059837963</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -57165,7 +57165,7 @@
         <v>45631.73952546297</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -57222,7 +57222,7 @@
         <v>45631.74673611111</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57279,7 +57279,7 @@
         <v>44769</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57336,7 +57336,7 @@
         <v>44217.40149305556</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57393,7 +57393,7 @@
         <v>44732</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57450,7 +57450,7 @@
         <v>45401.3653125</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>45831.4844212963</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57564,7 +57564,7 @@
         <v>45832.66385416667</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57621,7 +57621,7 @@
         <v>45208.69671296296</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57678,7 +57678,7 @@
         <v>45238</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57735,7 +57735,7 @@
         <v>45831.54618055555</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57792,7 +57792,7 @@
         <v>44698</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57849,7 +57849,7 @@
         <v>45469</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57906,7 +57906,7 @@
         <v>44146</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57963,7 +57963,7 @@
         <v>44621</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -58020,7 +58020,7 @@
         <v>45532</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -58077,7 +58077,7 @@
         <v>45212</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -58134,7 +58134,7 @@
         <v>45640.58716435185</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -58191,7 +58191,7 @@
         <v>45834</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>45876.45253472222</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58310,7 +58310,7 @@
         <v>45575</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58367,7 +58367,7 @@
         <v>45834.6447337963</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58424,7 +58424,7 @@
         <v>45699.46283564815</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58481,7 +58481,7 @@
         <v>45834.65538194445</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58538,7 +58538,7 @@
         <v>45328.46336805556</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58595,7 +58595,7 @@
         <v>45589.6756712963</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58652,7 +58652,7 @@
         <v>45642.63512731482</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58709,7 +58709,7 @@
         <v>45721.65858796296</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58766,7 +58766,7 @@
         <v>45456</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58823,7 +58823,7 @@
         <v>44152</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58885,7 +58885,7 @@
         <v>45525</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58942,7 +58942,7 @@
         <v>45531</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58999,7 +58999,7 @@
         <v>44319</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -59056,7 +59056,7 @@
         <v>44691.5652662037</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -59113,7 +59113,7 @@
         <v>44326</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59170,7 +59170,7 @@
         <v>44908.77368055555</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59227,7 +59227,7 @@
         <v>44251</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59284,7 +59284,7 @@
         <v>45518</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59341,7 +59341,7 @@
         <v>45033</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59398,7 +59398,7 @@
         <v>44769.66864583334</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59455,7 +59455,7 @@
         <v>44306</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59517,7 +59517,7 @@
         <v>45183</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59574,7 +59574,7 @@
         <v>44854</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59631,7 +59631,7 @@
         <v>44778.69210648148</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59688,7 +59688,7 @@
         <v>44747</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59745,7 +59745,7 @@
         <v>44832</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59802,7 +59802,7 @@
         <v>44960.60469907407</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59859,7 +59859,7 @@
         <v>44682.78430555556</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59916,7 +59916,7 @@
         <v>44252</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59973,7 +59973,7 @@
         <v>45587</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -60030,7 +60030,7 @@
         <v>45085.5309375</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -60092,7 +60092,7 @@
         <v>45370</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60149,7 +60149,7 @@
         <v>44925</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60206,7 +60206,7 @@
         <v>45733.82105324074</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60263,7 +60263,7 @@
         <v>44528.91494212963</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60320,7 +60320,7 @@
         <v>44866.49827546296</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60377,7 +60377,7 @@
         <v>45561.62141203704</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60434,7 +60434,7 @@
         <v>44922</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60491,7 +60491,7 @@
         <v>44767.60601851852</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60548,7 +60548,7 @@
         <v>44490.02482638889</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60605,7 +60605,7 @@
         <v>44490.03621527777</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60662,7 +60662,7 @@
         <v>44995</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60719,7 +60719,7 @@
         <v>44083</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60776,7 +60776,7 @@
         <v>44750.66068287037</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60833,7 +60833,7 @@
         <v>44750</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60890,7 +60890,7 @@
         <v>45338</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60947,7 +60947,7 @@
         <v>45082</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -61004,7 +61004,7 @@
         <v>45082.68922453704</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -61061,7 +61061,7 @@
         <v>44771</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>44813</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -61180,7 +61180,7 @@
         <v>44376.50728009259</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -61237,7 +61237,7 @@
         <v>45468.45877314815</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -61294,7 +61294,7 @@
         <v>45261</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61351,7 +61351,7 @@
         <v>45259</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61408,7 +61408,7 @@
         <v>45253.61146990741</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61465,7 +61465,7 @@
         <v>45435.43466435185</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61522,7 +61522,7 @@
         <v>45435.43820601852</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61579,7 +61579,7 @@
         <v>45621.34425925926</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61641,7 +61641,7 @@
         <v>45621.35712962963</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61703,7 +61703,7 @@
         <v>45600.411875</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61760,7 +61760,7 @@
         <v>45435.43123842592</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61817,7 +61817,7 @@
         <v>45282</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61874,7 +61874,7 @@
         <v>44938</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61931,7 +61931,7 @@
         <v>44260</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61993,7 +61993,7 @@
         <v>44753</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -62050,7 +62050,7 @@
         <v>44698</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -62112,7 +62112,7 @@
         <v>45729.72851851852</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -62174,7 +62174,7 @@
         <v>44777</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -62231,7 +62231,7 @@
         <v>45668.67446759259</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62288,7 +62288,7 @@
         <v>45670.3079050926</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62345,7 +62345,7 @@
         <v>44218</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62402,7 +62402,7 @@
         <v>45007</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62459,7 +62459,7 @@
         <v>44599.58428240741</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62516,7 +62516,7 @@
         <v>45713.92623842593</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62573,7 +62573,7 @@
         <v>44743.59765046297</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62635,7 +62635,7 @@
         <v>44743.64592592593</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62697,7 +62697,7 @@
         <v>45152</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62754,7 +62754,7 @@
         <v>45640.57305555556</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>44326.61967592593</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62868,7 +62868,7 @@
         <v>44858</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62925,7 +62925,7 @@
         <v>45183</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62982,7 +62982,7 @@
         <v>45638.5987037037</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -63044,7 +63044,7 @@
         <v>45453</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -63101,7 +63101,7 @@
         <v>45770</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -63158,7 +63158,7 @@
         <v>45310.40628472222</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -63215,7 +63215,7 @@
         <v>45310</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63272,7 +63272,7 @@
         <v>44700.50659722222</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63329,7 +63329,7 @@
         <v>45254</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63386,7 +63386,7 @@
         <v>45089</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63443,7 +63443,7 @@
         <v>45159</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63500,7 +63500,7 @@
         <v>45322</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>

--- a/Översikt NORRTÄLJE.xlsx
+++ b/Översikt NORRTÄLJE.xlsx
@@ -567,7 +567,7 @@
         <v>45135</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44757</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44249</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45757</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>44909</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45457</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45226</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45367</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45715</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44949</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45436</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>44263</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>45190</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>44550</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>45600</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>44467</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>45586.88145833334</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45638</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45688.38224537037</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>44846</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>44858</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>44650</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>44447</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45400.5958912037</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>45800</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>45068</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>44544</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45748.6521875</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>45831.53390046296</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>44076</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44711</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>45784.32179398148</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>45783.58123842593</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44545</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>44336</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
         <v>45722</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>45847.47052083333</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44839</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44300</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44749</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>44843</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>44279</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>45611.47233796296</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>44945</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>44698</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5032,7 +5032,7 @@
         <v>45616.54866898148</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5119,7 +5119,7 @@
         <v>44866</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>45821</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>44370</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>44489</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>45219</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>44763</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>44872</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>45772.30234953704</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>45723</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>45772.31609953703</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>45609.37094907407</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>44670</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>45800</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>45847.47685185185</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>45446.35888888889</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>45226</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>44868</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44573</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>44102</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>44564.66387731482</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44161</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>44363</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>44788.70217592592</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44680</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>45225</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>45474</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>45735.54510416667</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44955.71322916666</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>45081</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>45082</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>45205</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         <v>44855</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>45092</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7996,7 +7996,7 @@
         <v>44956</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         <v>44695.43527777777</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>45784.54878472222</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8251,7 +8251,7 @@
         <v>44620</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45794.63298611111</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>45798</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>44489</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>45841.5721875</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>45800</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>45687.34177083334</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>45146</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>45532</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>45803.62766203703</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>45754</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>45065</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>44683</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>45741.38688657407</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         <v>44704</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44965</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>45708</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>45826.46392361111</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45450.63958333333</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>44207</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9998,7 +9998,7 @@
         <v>45468.45995370371</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44993</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>44863</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>45280</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>45609.83747685186</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>44210</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>44209</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>44306</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44650.86518518518</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>44642</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>44540</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>44650.8699537037</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44447</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>44833</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>44284.59546296296</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>44069</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>44330</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>44420</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>44420</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>44097</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>44728.73465277778</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>44777</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>44810.85092592592</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>44552</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>44560</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>44470.72148148148</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>44634</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>44581.75819444445</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>44771</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>44111.45320601852</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>44477.94327546296</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44380</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>44524</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>44399.43450231481</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44574.42978009259</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44516.72827546296</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>44103</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>44868</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44834</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44309.47061342592</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>44400</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44161</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>44252</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44451</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         <v>44858</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>44244</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>44626</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>44690</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>44682.79203703703</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>44496</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>44708</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>44642</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>44776</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>44103</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>44176</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>44746</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>44306</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>44214</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>44727</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>44845.47585648148</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>44694.57549768518</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>44495</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>44749.61980324074</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>44543</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>44543</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>44882.44732638889</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>44882</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>44224</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>44545.4189699074</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>44314</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>44279</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>44300</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>44722</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44742</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>44806.34577546296</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>44756.40881944444</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>44294</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>44124</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44330</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>44330</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>44511.69885416667</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>44510</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>44447</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>44435</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>44391.5580787037</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>44067</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>44867</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>44571</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>44453</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>44511</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>44495</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>44683</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>44201</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>44201</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44375</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44539</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44516.5275462963</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44496</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>44299</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>44694.57413194444</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44414.81494212963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44380</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44594.75950231482</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>44826</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44326</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44607</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44425</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44425</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44363.5784375</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>44575.52831018518</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>44712.83118055556</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>44769.62320601852</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44309</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>44251.43971064815</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>44698</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>44845.47672453704</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>44397</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44270</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44270</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16991,7 +16991,7 @@
         <v>44572</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>44543</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>44543</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17162,7 +17162,7 @@
         <v>44526</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44650.92714120371</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44760</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>44609</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44817.70516203704</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>44545</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>44545</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>44230</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>44230</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44477</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>44725.49491898148</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>44427</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>44621</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44868</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44496.77542824074</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>44251</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44580</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>44658</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>44100</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>44665.66407407408</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>44584.91538194445</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>44678</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>44300</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>44880.68423611111</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>44637</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18621,7 +18621,7 @@
         <v>44777</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>44735</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18735,7 +18735,7 @@
         <v>44816.89569444444</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>44682.75924768519</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18849,7 +18849,7 @@
         <v>44682.77616898148</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
         <v>44623</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>44637</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>44655.45373842592</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>44350</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>44143</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>44763.4182175926</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>44105</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>44502</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>44132</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>44665.65474537037</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>44665.78351851852</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19533,7 +19533,7 @@
         <v>44642.55565972222</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>44533</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>44466.37496527778</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19709,7 +19709,7 @@
         <v>44153</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>44076</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>44595</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>44376</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19937,7 +19937,7 @@
         <v>44342</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>44704</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>44543</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20113,7 +20113,7 @@
         <v>44682.76528935185</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>44735</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>44523.61635416667</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>44176</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20341,7 +20341,7 @@
         <v>44595</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>44370.72197916666</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>44725</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20512,7 +20512,7 @@
         <v>44333</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>44744</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>44350</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>44637</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20740,7 +20740,7 @@
         <v>44815</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>44284</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>44495</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20911,7 +20911,7 @@
         <v>45740.47288194444</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>45414.58650462963</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>45730.69143518519</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>45162</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>45679</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45554.55707175926</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>44524</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44670.4190162037</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21372,7 +21372,7 @@
         <v>45621.34813657407</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45139</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>44851</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>45092</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>44379</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45019.28847222222</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>45730.35026620371</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>45082.69179398148</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>45772.71221064815</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45215</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>44272</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>44743.47407407407</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>44266</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>44376</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>45482.53388888889</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22232,7 +22232,7 @@
         <v>45772.30436342592</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>45054</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22346,7 +22346,7 @@
         <v>45273</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22403,7 +22403,7 @@
         <v>45075.91362268518</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22460,7 +22460,7 @@
         <v>45075.91971064815</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>44764</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>45051.455</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>44098</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>45749</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45362.62811342593</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>44778.92797453704</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>44956</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22921,7 +22921,7 @@
         <v>45691.41101851852</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>44956</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         <v>45772.29622685185</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45084.57695601852</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>45708.61761574074</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45203.63303240741</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>45257</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23325,7 +23325,7 @@
         <v>44824.36069444445</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>44419</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23439,7 +23439,7 @@
         <v>44803</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45772.3078125</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>45625</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>45208</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>44879.70518518519</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23724,7 +23724,7 @@
         <v>45729.60859953704</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>44833.40876157407</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>44687</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>45236.46369212963</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23957,7 +23957,7 @@
         <v>45055.43509259259</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>45772.51127314815</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>44110</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>45405.57927083333</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>45735.59287037037</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24247,7 +24247,7 @@
         <v>45075</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24304,7 +24304,7 @@
         <v>44315</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45735.36873842592</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>45705.66126157407</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>45764.6359837963</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45330.50098379629</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>44596.66335648148</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45218</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>44549</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>44145</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>44456</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>45063</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>45065.55917824074</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45356.4722800926</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
         <v>44285</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         <v>45490.45342592592</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>45469</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25241,7 +25241,7 @@
         <v>44840</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>45433.58431712963</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>44459</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>44732</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45383</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25531,7 +25531,7 @@
         <v>45056</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>45530</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45435</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>44452</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25759,7 +25759,7 @@
         <v>44124</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
         <v>44895</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>45218.65849537037</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25935,7 +25935,7 @@
         <v>44817.56120370371</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>44390</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>45397</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45450.64208333333</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>45450</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45755.36583333334</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>44760</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44760</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>45022</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26458,7 +26458,7 @@
         <v>44816</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45723</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>45223</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44272</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>45239</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         <v>45089</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>44845.48064814815</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>45558.46283564815</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>44841.52804398148</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>45454.65774305556</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27038,7 +27038,7 @@
         <v>45518</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45757.61421296297</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>45721.89123842592</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>44809</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>45740.47550925926</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>45740.47724537037</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27380,7 +27380,7 @@
         <v>45344</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>45202</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>45075.90270833333</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>45075.91042824074</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>45075.91265046296</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>45075.92153935185</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>45708</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27794,7 +27794,7 @@
         <v>44962</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27851,7 +27851,7 @@
         <v>45089</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>44934</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>45548.72306712963</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28022,7 +28022,7 @@
         <v>45131.666875</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28079,7 +28079,7 @@
         <v>44866.63775462963</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28136,7 +28136,7 @@
         <v>44778</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28193,7 +28193,7 @@
         <v>44581</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>45376.55704861111</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28307,7 +28307,7 @@
         <v>45448.56746527777</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28364,7 +28364,7 @@
         <v>45257</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>45293.37263888889</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>45231.34144675926</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         <v>45418.6968287037</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28592,7 +28592,7 @@
         <v>45104</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>45245</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>45245</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>44992</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>44956.65920138889</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>44931.65626157408</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44483</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>44362.37172453704</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>45460.45523148148</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>45293</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29172,7 +29172,7 @@
         <v>45063.35880787037</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>44956</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>45726.48377314815</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>44321</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>44472</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>45054.54091435186</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>45054</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>45119.57728009259</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29628,7 +29628,7 @@
         <v>45463.80486111111</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>45118</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29747,7 +29747,7 @@
         <v>45723</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29809,7 +29809,7 @@
         <v>45617.57439814815</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29866,7 +29866,7 @@
         <v>45457</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29928,7 +29928,7 @@
         <v>45468.45628472222</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>44076</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30042,7 +30042,7 @@
         <v>45706.60130787037</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>44900</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>44714.92253472222</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>44743.59504629629</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>45104</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30337,7 +30337,7 @@
         <v>45394.58778935186</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>45245</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>45356.47784722222</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30513,7 +30513,7 @@
         <v>45022.61003472222</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>45092</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30627,7 +30627,7 @@
         <v>44637</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30684,7 +30684,7 @@
         <v>44816</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>44470.72987268519</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30798,7 +30798,7 @@
         <v>44834.38636574074</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30855,7 +30855,7 @@
         <v>44113</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30912,7 +30912,7 @@
         <v>45757.60658564815</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30969,7 +30969,7 @@
         <v>44231</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         <v>44949</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>44643</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31145,7 +31145,7 @@
         <v>45760.91174768518</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>44949</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>45075.90703703704</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>45490.60572916667</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>44953.67443287037</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>45638.59979166667</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>45357</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         <v>44963</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>45524</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>45694.68207175926</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>45341.39853009259</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>45084.54459490741</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>45058.78607638889</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>45483.57244212963</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>44100</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>45600.86128472222</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>44869</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>45644.47878472223</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32186,7 +32186,7 @@
         <v>44882</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32243,7 +32243,7 @@
         <v>45086.3629050926</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32300,7 +32300,7 @@
         <v>45253.55641203704</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44474.62141203704</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32414,7 +32414,7 @@
         <v>45737.43347222222</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32476,7 +32476,7 @@
         <v>45169</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>45455.33037037037</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>45147.65222222222</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32652,7 +32652,7 @@
         <v>45147.65311342593</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>45147</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32766,7 +32766,7 @@
         <v>45175</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>44952.57989583333</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32885,7 +32885,7 @@
         <v>45469</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>45469</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>44556</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>44705.60626157407</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>44470</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>44621</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>45391.3395949074</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>44868.45741898148</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>45473.94501157408</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>44395</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>45259</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>45485</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33569,7 +33569,7 @@
         <v>44132</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>45253.63089120371</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33683,7 +33683,7 @@
         <v>45104</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>45104</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33797,7 +33797,7 @@
         <v>45776.62563657408</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>45316.60306712963</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33911,7 +33911,7 @@
         <v>45586</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>45776.47346064815</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>45776.46369212963</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34082,7 +34082,7 @@
         <v>45769</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>45776.59871527777</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>44540</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>45190.55609953704</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>45776.47122685185</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>45414.65855324074</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>44133</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>45089</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>45376.64532407407</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>44985</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>44904</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>44143</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>44901</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>44510</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>45576</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>44592</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>45721</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>44105</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>45783</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>45075.91148148148</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>45075</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>44145</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35341,7 +35341,7 @@
         <v>45418</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>45783.66429398148</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45783.48878472222</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45385.36243055556</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>45610.47414351852</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>45485.60261574074</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
         <v>45385.38146990741</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>45536</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>45549</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>44993.66707175926</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>44124</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44511.70518518519</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>45531</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>44977</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>45581</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>44525</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>45170</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>45187</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>45735</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44525</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44546</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>45709.39361111111</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44516</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>44516.40674768519</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>45468.45541666666</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36791,7 +36791,7 @@
         <v>45468.45747685185</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>45610.39271990741</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36905,7 +36905,7 @@
         <v>45442.45686342593</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36962,7 +36962,7 @@
         <v>45155</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37019,7 +37019,7 @@
         <v>44769.66039351852</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>44938</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37133,7 +37133,7 @@
         <v>45572.57828703704</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37190,7 +37190,7 @@
         <v>45271</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>45642.64634259259</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37304,7 +37304,7 @@
         <v>45460.44347222222</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>45260</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>45785.65300925926</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>44637</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45537</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45579</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37651,7 +37651,7 @@
         <v>44179</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>44162</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>44325</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>44461</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>44959.74533564815</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>44902</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38003,7 +38003,7 @@
         <v>45831.56521990741</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38060,7 +38060,7 @@
         <v>45443</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38117,7 +38117,7 @@
         <v>45735</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>45735.60863425926</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>45352.74090277778</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38288,7 +38288,7 @@
         <v>45245</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>44578</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>45715</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>44108</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>45687</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>45408.57707175926</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38640,7 +38640,7 @@
         <v>44953.69298611111</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45533</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45547</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38811,7 +38811,7 @@
         <v>44139.54078703704</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>45534.38240740741</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>44923.90159722222</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>44183</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>45412.4104050926</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39101,7 +39101,7 @@
         <v>44585</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39163,7 +39163,7 @@
         <v>45786.55645833333</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>44584.91001157407</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>45177</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>45721.88684027778</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>45706.40086805556</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>45635.88849537037</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>45552.52827546297</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>45600.4558912037</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39629,7 +39629,7 @@
         <v>44945.67409722223</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>44937</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>45540</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>45145.51</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
         <v>45215</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39919,7 +39919,7 @@
         <v>44629</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>44617</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45692</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>44795</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>45075</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>45075</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40266,7 +40266,7 @@
         <v>45075.90934027778</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>45089</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>45155</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>45254</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>45260.43225694444</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45260.4333449074</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>45203.83891203703</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>45589.68289351852</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>44714.56040509259</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>44596</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45837.94081018519</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45835.46034722222</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45636.38974537037</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>45272.64479166667</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45272</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>45385.37922453704</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>45729.7271875</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41240,7 +41240,7 @@
         <v>45639.45166666667</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45205</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>45639.47385416667</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45629.65143518519</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41473,7 +41473,7 @@
         <v>45713</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>45436</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>45518</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45838.43261574074</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>45735</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>44888</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>44867.62090277778</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45701.44372685185</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>45644.90815972222</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45223</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45450.64643518518</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45475.61896990741</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45640.60240740741</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45600.47275462963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>44580</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45113</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>45113</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>44673</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>44611</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>44648</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>44643</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>44986.5887962963</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45835.4928125</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42804,7 +42804,7 @@
         <v>45048</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>45837.93730324074</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45835.68076388889</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42975,7 +42975,7 @@
         <v>45740.47055555556</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>44708.67822916667</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>44775</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45223</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>45840.67829861111</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>45840.70885416667</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>44816</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45456</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>45798.66767361111</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43488,7 +43488,7 @@
         <v>45617.58453703704</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43545,7 +43545,7 @@
         <v>45839</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43602,7 +43602,7 @@
         <v>45786</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43659,7 +43659,7 @@
         <v>45121</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>45726.48152777777</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45070</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43830,7 +43830,7 @@
         <v>45798.67082175926</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43887,7 +43887,7 @@
         <v>45798</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43944,7 +43944,7 @@
         <v>45798.66104166667</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44001,7 +44001,7 @@
         <v>45797.58399305555</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44058,7 +44058,7 @@
         <v>44693</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44115,7 +44115,7 @@
         <v>44649</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44172,7 +44172,7 @@
         <v>44155.69458333333</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44229,7 +44229,7 @@
         <v>44963</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44286,7 +44286,7 @@
         <v>45112</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>44266</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44400,7 +44400,7 @@
         <v>44266</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44457,7 +44457,7 @@
         <v>45837</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44514,7 +44514,7 @@
         <v>45839.62398148148</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44571,7 +44571,7 @@
         <v>45232</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>44867</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>45735.36594907408</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
         <v>45729.71065972222</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44804,7 +44804,7 @@
         <v>45376.55484953704</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>45797.58350694444</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44918,7 +44918,7 @@
         <v>44819</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>44778</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45032,7 +45032,7 @@
         <v>45623.62563657408</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45094,7 +45094,7 @@
         <v>45386.34175925926</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45183</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45208,7 +45208,7 @@
         <v>44644</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45265,7 +45265,7 @@
         <v>45075</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45322,7 +45322,7 @@
         <v>45841.35611111111</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45379,7 +45379,7 @@
         <v>45478.42887731481</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45436,7 +45436,7 @@
         <v>45712</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45498,7 +45498,7 @@
         <v>44635</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45555,7 +45555,7 @@
         <v>45348.46300925926</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45617,7 +45617,7 @@
         <v>44656</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45679,7 +45679,7 @@
         <v>45687.5038425926</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45741,7 +45741,7 @@
         <v>44670</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>45695.57881944445</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45860,7 +45860,7 @@
         <v>45608</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45917,7 +45917,7 @@
         <v>44803</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>45800</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>45617.62358796296</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>45800</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>45800</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>45069</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46279,7 +46279,7 @@
         <v>45841.5737962963</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46336,7 +46336,7 @@
         <v>45581</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46393,7 +46393,7 @@
         <v>45208.58004629629</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46450,7 +46450,7 @@
         <v>45799</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46507,7 +46507,7 @@
         <v>45693</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46564,7 +46564,7 @@
         <v>45730.42851851852</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>45092</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46683,7 +46683,7 @@
         <v>45092</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46740,7 +46740,7 @@
         <v>45840.62755787037</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46797,7 +46797,7 @@
         <v>45842.46885416667</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46854,7 +46854,7 @@
         <v>45427.88731481481</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46911,7 +46911,7 @@
         <v>45202.65660879629</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46968,7 +46968,7 @@
         <v>45664</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47025,7 +47025,7 @@
         <v>45800</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47082,7 +47082,7 @@
         <v>45075.90817129629</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47139,7 +47139,7 @@
         <v>45841.56996527778</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47196,7 +47196,7 @@
         <v>45800</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47253,7 +47253,7 @@
         <v>45841.74596064815</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47310,7 +47310,7 @@
         <v>44797</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47367,7 +47367,7 @@
         <v>45803.4675</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47424,7 +47424,7 @@
         <v>44624.59434027778</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47481,7 +47481,7 @@
         <v>45224</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47538,7 +47538,7 @@
         <v>45800</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47600,7 +47600,7 @@
         <v>45147.65407407407</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47657,7 +47657,7 @@
         <v>44687</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47719,7 +47719,7 @@
         <v>45803.69228009259</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47776,7 +47776,7 @@
         <v>45559.54706018518</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47833,7 +47833,7 @@
         <v>45804.74479166666</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47890,7 +47890,7 @@
         <v>45757.65178240741</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47947,7 +47947,7 @@
         <v>45775.41451388889</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48004,7 +48004,7 @@
         <v>44243.33587962963</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48061,7 +48061,7 @@
         <v>45636.41572916666</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48118,7 +48118,7 @@
         <v>45020</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48175,7 +48175,7 @@
         <v>45139.51457175926</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48232,7 +48232,7 @@
         <v>45549</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48289,7 +48289,7 @@
         <v>44697</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48346,7 +48346,7 @@
         <v>44813</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>45614.39627314815</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48460,7 +48460,7 @@
         <v>45146</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>45803.66587962963</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>45522.44414351852</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45844.62609953704</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>45586</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45844.91234953704</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48812,7 +48812,7 @@
         <v>45685.44592592592</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>45376.54115740741</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>45757.62482638889</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48983,7 +48983,7 @@
         <v>45174.68702546296</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>45686.65545138889</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>45721.40780092592</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>44704</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45709.40231481481</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49278,7 +49278,7 @@
         <v>45847.37414351852</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49340,7 +49340,7 @@
         <v>45022</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49397,7 +49397,7 @@
         <v>44704</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49454,7 +49454,7 @@
         <v>44903</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49511,7 +49511,7 @@
         <v>45168.44489583333</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49573,7 +49573,7 @@
         <v>45446.4287962963</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49630,7 +49630,7 @@
         <v>45670.65921296296</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49687,7 +49687,7 @@
         <v>44790</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49744,7 +49744,7 @@
         <v>45208</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49801,7 +49801,7 @@
         <v>45208</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49858,7 +49858,7 @@
         <v>45414</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>45237</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>45145.63584490741</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45411.54768518519</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50091,7 +50091,7 @@
         <v>44953.70481481482</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50148,7 +50148,7 @@
         <v>45847.48436342592</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50205,7 +50205,7 @@
         <v>45519</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50262,7 +50262,7 @@
         <v>45107.42538194444</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50319,7 +50319,7 @@
         <v>45111</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50376,7 +50376,7 @@
         <v>45700</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50438,7 +50438,7 @@
         <v>44680</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50495,7 +50495,7 @@
         <v>44266</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50552,7 +50552,7 @@
         <v>45810.42393518519</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50609,7 +50609,7 @@
         <v>45245</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50666,7 +50666,7 @@
         <v>44708</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50723,7 +50723,7 @@
         <v>44708.36708333333</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50785,7 +50785,7 @@
         <v>44974</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50842,7 +50842,7 @@
         <v>44746.58530092592</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50899,7 +50899,7 @@
         <v>45790.81410879629</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50956,7 +50956,7 @@
         <v>44771</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51013,7 +51013,7 @@
         <v>45679</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51070,7 +51070,7 @@
         <v>44684</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51127,7 +51127,7 @@
         <v>45127.69371527778</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51189,7 +51189,7 @@
         <v>45810.5333912037</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51246,7 +51246,7 @@
         <v>45245</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51303,7 +51303,7 @@
         <v>45748.53761574074</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51360,7 +51360,7 @@
         <v>45609.70778935185</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51422,7 +51422,7 @@
         <v>45609.85146990741</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
         <v>44743.59331018518</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51541,7 +51541,7 @@
         <v>44743.67418981482</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>45852.58030092593</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51660,7 +51660,7 @@
         <v>45427.89121527778</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51717,7 +51717,7 @@
         <v>45587.62565972222</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>45810.45236111111</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51831,7 +51831,7 @@
         <v>45810.45263888889</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51888,7 +51888,7 @@
         <v>44732</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>45208.70996527778</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52002,7 +52002,7 @@
         <v>45601.56726851852</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
         <v>45177.61498842593</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52116,7 +52116,7 @@
         <v>45635.44788194444</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52173,7 +52173,7 @@
         <v>44763.40914351852</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52230,7 +52230,7 @@
         <v>45810.45633101852</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52287,7 +52287,7 @@
         <v>45811.60451388889</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52344,7 +52344,7 @@
         <v>45630.52866898148</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52401,7 +52401,7 @@
         <v>44181</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52458,7 +52458,7 @@
         <v>45728.38924768518</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52515,7 +52515,7 @@
         <v>45667.49878472222</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52572,7 +52572,7 @@
         <v>44722</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52629,7 +52629,7 @@
         <v>44097</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52686,7 +52686,7 @@
         <v>45853</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52743,7 +52743,7 @@
         <v>44495.5893287037</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52800,7 +52800,7 @@
         <v>45853</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52857,7 +52857,7 @@
         <v>45128</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52914,7 +52914,7 @@
         <v>44749.55258101852</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52971,7 +52971,7 @@
         <v>44782</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -53028,7 +53028,7 @@
         <v>45855.68413194444</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -53090,7 +53090,7 @@
         <v>45855.57033564815</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -53152,7 +53152,7 @@
         <v>45813.63650462963</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53209,7 +53209,7 @@
         <v>45813.66961805556</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53266,7 +53266,7 @@
         <v>45813.6799537037</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53323,7 +53323,7 @@
         <v>45855.69387731481</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53385,7 +53385,7 @@
         <v>44799.65013888889</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53442,7 +53442,7 @@
         <v>45813.4709375</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53504,7 +53504,7 @@
         <v>45680.42665509259</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53561,7 +53561,7 @@
         <v>45293</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53623,7 +53623,7 @@
         <v>45219.56697916667</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53680,7 +53680,7 @@
         <v>45728.38409722222</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53737,7 +53737,7 @@
         <v>44813.59915509259</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53794,7 +53794,7 @@
         <v>44325</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53851,7 +53851,7 @@
         <v>45376.55638888889</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53913,7 +53913,7 @@
         <v>45817.2565625</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53970,7 +53970,7 @@
         <v>45817.30329861111</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -54027,7 +54027,7 @@
         <v>45817.31085648148</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -54084,7 +54084,7 @@
         <v>45817.31708333334</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -54141,7 +54141,7 @@
         <v>45817.31986111111</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -54198,7 +54198,7 @@
         <v>45817.33503472222</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45859</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45859</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>44719</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54431,7 +54431,7 @@
         <v>45747.63471064815</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54488,7 +54488,7 @@
         <v>45817.291875</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54545,7 +54545,7 @@
         <v>45254.41509259259</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54602,7 +54602,7 @@
         <v>45817.32538194444</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54659,7 +54659,7 @@
         <v>44980</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>45700</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54773,7 +54773,7 @@
         <v>45817.25471064815</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54830,7 +54830,7 @@
         <v>44690</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54887,7 +54887,7 @@
         <v>45817.34083333334</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54944,7 +54944,7 @@
         <v>45840</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45835</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -55058,7 +55058,7 @@
         <v>45743.44953703704</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>45707.84997685185</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -55172,7 +55172,7 @@
         <v>44777</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55229,7 +55229,7 @@
         <v>45085</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
         <v>45730.69502314815</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55343,7 +55343,7 @@
         <v>45243.45289351852</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>44925</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55462,7 +55462,7 @@
         <v>45188.41637731482</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55524,7 +55524,7 @@
         <v>45168.40565972222</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>44760</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55643,7 +55643,7 @@
         <v>45042.74291666667</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55700,7 +55700,7 @@
         <v>44375</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55757,7 +55757,7 @@
         <v>45219</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>45442</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>45824.37275462963</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55933,7 +55933,7 @@
         <v>44111.44373842593</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>45068.51783564815</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -56047,7 +56047,7 @@
         <v>44806.41576388889</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -56104,7 +56104,7 @@
         <v>44783</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -56161,7 +56161,7 @@
         <v>44785</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -56223,7 +56223,7 @@
         <v>45394.72869212963</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56280,7 +56280,7 @@
         <v>45063</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56337,7 +56337,7 @@
         <v>45868.62267361111</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56394,7 +56394,7 @@
         <v>45706.61178240741</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56456,7 +56456,7 @@
         <v>44398</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56518,7 +56518,7 @@
         <v>45845</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56575,7 +56575,7 @@
         <v>45191</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56637,7 +56637,7 @@
         <v>44510.51422453704</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56699,7 +56699,7 @@
         <v>45831.51659722222</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56756,7 +56756,7 @@
         <v>44815.74539351852</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56813,7 +56813,7 @@
         <v>45831.65079861111</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
         <v>45293</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56937,7 +56937,7 @@
         <v>45019.3959837963</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56994,7 +56994,7 @@
         <v>44380.77346064815</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -57051,7 +57051,7 @@
         <v>45771</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -57108,7 +57108,7 @@
         <v>45345.6059837963</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -57165,7 +57165,7 @@
         <v>45631.73952546297</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -57222,7 +57222,7 @@
         <v>45631.74673611111</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57279,7 +57279,7 @@
         <v>44769</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57336,7 +57336,7 @@
         <v>44217.40149305556</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57393,7 +57393,7 @@
         <v>44732</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57450,7 +57450,7 @@
         <v>45401.3653125</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>45831.4844212963</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57564,7 +57564,7 @@
         <v>45832.66385416667</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57621,7 +57621,7 @@
         <v>45208.69671296296</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57678,7 +57678,7 @@
         <v>45238</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57735,7 +57735,7 @@
         <v>45831.54618055555</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57792,7 +57792,7 @@
         <v>44698</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57849,7 +57849,7 @@
         <v>45469</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57906,7 +57906,7 @@
         <v>44146</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57963,7 +57963,7 @@
         <v>44621</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -58020,7 +58020,7 @@
         <v>45532</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -58077,7 +58077,7 @@
         <v>45212</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -58134,7 +58134,7 @@
         <v>45640.58716435185</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -58191,7 +58191,7 @@
         <v>45834</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58248,7 +58248,7 @@
         <v>45876.45253472222</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58310,7 +58310,7 @@
         <v>45575</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58367,7 +58367,7 @@
         <v>45834.6447337963</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58424,7 +58424,7 @@
         <v>45699.46283564815</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58481,7 +58481,7 @@
         <v>45834.65538194445</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58538,7 +58538,7 @@
         <v>45328.46336805556</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58595,7 +58595,7 @@
         <v>45589.6756712963</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58652,7 +58652,7 @@
         <v>45642.63512731482</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58709,7 +58709,7 @@
         <v>45721.65858796296</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58766,7 +58766,7 @@
         <v>45456</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58823,7 +58823,7 @@
         <v>44152</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58885,7 +58885,7 @@
         <v>45525</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58942,7 +58942,7 @@
         <v>45531</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58999,7 +58999,7 @@
         <v>44319</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -59056,7 +59056,7 @@
         <v>44691.5652662037</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -59113,7 +59113,7 @@
         <v>44326</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59170,7 +59170,7 @@
         <v>44908.77368055555</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59227,7 +59227,7 @@
         <v>44251</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59284,7 +59284,7 @@
         <v>45518</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59341,7 +59341,7 @@
         <v>45033</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59398,7 +59398,7 @@
         <v>44769.66864583334</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59455,7 +59455,7 @@
         <v>44306</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59517,7 +59517,7 @@
         <v>45183</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59574,7 +59574,7 @@
         <v>44854</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59631,7 +59631,7 @@
         <v>44778.69210648148</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59688,7 +59688,7 @@
         <v>44747</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59745,7 +59745,7 @@
         <v>44832</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59802,7 +59802,7 @@
         <v>44960.60469907407</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59859,7 +59859,7 @@
         <v>44682.78430555556</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59916,7 +59916,7 @@
         <v>44252</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59973,7 +59973,7 @@
         <v>45587</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -60030,7 +60030,7 @@
         <v>45085.5309375</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -60092,7 +60092,7 @@
         <v>45370</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60149,7 +60149,7 @@
         <v>44925</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60206,7 +60206,7 @@
         <v>45733.82105324074</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60263,7 +60263,7 @@
         <v>44528.91494212963</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60320,7 +60320,7 @@
         <v>44866.49827546296</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60377,7 +60377,7 @@
         <v>45561.62141203704</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60434,7 +60434,7 @@
         <v>44922</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60491,7 +60491,7 @@
         <v>44767.60601851852</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60548,7 +60548,7 @@
         <v>44490.02482638889</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60605,7 +60605,7 @@
         <v>44490.03621527777</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60662,7 +60662,7 @@
         <v>44995</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60719,7 +60719,7 @@
         <v>44083</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60776,7 +60776,7 @@
         <v>44750.66068287037</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60833,7 +60833,7 @@
         <v>44750</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60890,7 +60890,7 @@
         <v>45338</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60947,7 +60947,7 @@
         <v>45082</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -61004,7 +61004,7 @@
         <v>45082.68922453704</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -61061,7 +61061,7 @@
         <v>44771</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -61123,7 +61123,7 @@
         <v>44813</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -61180,7 +61180,7 @@
         <v>44376.50728009259</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -61237,7 +61237,7 @@
         <v>45468.45877314815</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -61294,7 +61294,7 @@
         <v>45261</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61351,7 +61351,7 @@
         <v>45259</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61408,7 +61408,7 @@
         <v>45253.61146990741</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61465,7 +61465,7 @@
         <v>45435.43466435185</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61522,7 +61522,7 @@
         <v>45435.43820601852</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61579,7 +61579,7 @@
         <v>45621.34425925926</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61641,7 +61641,7 @@
         <v>45621.35712962963</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61703,7 +61703,7 @@
         <v>45600.411875</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61760,7 +61760,7 @@
         <v>45435.43123842592</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61817,7 +61817,7 @@
         <v>45282</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61874,7 +61874,7 @@
         <v>44938</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61931,7 +61931,7 @@
         <v>44260</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61993,7 +61993,7 @@
         <v>44753</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -62050,7 +62050,7 @@
         <v>44698</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -62112,7 +62112,7 @@
         <v>45729.72851851852</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -62174,7 +62174,7 @@
         <v>44777</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -62231,7 +62231,7 @@
         <v>45668.67446759259</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62288,7 +62288,7 @@
         <v>45670.3079050926</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62345,7 +62345,7 @@
         <v>44218</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62402,7 +62402,7 @@
         <v>45007</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62459,7 +62459,7 @@
         <v>44599.58428240741</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62516,7 +62516,7 @@
         <v>45713.92623842593</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62573,7 +62573,7 @@
         <v>44743.59765046297</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62635,7 +62635,7 @@
         <v>44743.64592592593</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62697,7 +62697,7 @@
         <v>45152</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62754,7 +62754,7 @@
         <v>45640.57305555556</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>44326.61967592593</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62868,7 +62868,7 @@
         <v>44858</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62925,7 +62925,7 @@
         <v>45183</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62982,7 +62982,7 @@
         <v>45638.5987037037</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -63044,7 +63044,7 @@
         <v>45453</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -63101,7 +63101,7 @@
         <v>45770</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -63158,7 +63158,7 @@
         <v>45310.40628472222</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -63215,7 +63215,7 @@
         <v>45310</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63272,7 +63272,7 @@
         <v>44700.50659722222</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63329,7 +63329,7 @@
         <v>45254</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63386,7 +63386,7 @@
         <v>45089</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63443,7 +63443,7 @@
         <v>45159</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63500,7 +63500,7 @@
         <v>45322</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>

--- a/Översikt NORRTÄLJE.xlsx
+++ b/Översikt NORRTÄLJE.xlsx
@@ -567,7 +567,7 @@
         <v>45135</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44757</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44249</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45757</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>44909</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45457</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45226</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45367</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45715</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44949</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45436</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>45190</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44263</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>44550</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>44467</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45586.88145833334</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>45600</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45638</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45688.38224537037</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>44846</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>44858</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>44447</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>45400.5958912037</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>44650</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>45800</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>45831.53390046296</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>45748.6521875</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44076</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>45068</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>44544</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44711</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>45784.32179398148</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>45783.58123842593</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44545</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>45722</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>45847.47052083333</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44336</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44839</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44300</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44749</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>44843</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>44279</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>45616.54866898148</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>45611.47233796296</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>44866</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45821</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44945</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44698</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>44370</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>44489</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>45219</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>44763</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45772.31609953703</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>45723</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>45609.37094907407</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>45800</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>45847.47685185185</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>45226</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44670</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>45446.35888888889</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>44868</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44872</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45772.30234953704</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44573</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>44102</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>44564.66387731482</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44161</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>44363</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>44788.70217592592</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44680</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>44695.43527777777</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>45784.54878472222</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44620</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44855</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>45794.63298611111</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>45800</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>45146</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>45532</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>45803.62766203703</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>44956</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45687.34177083334</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>45754</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>44965</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>45826.46392361111</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>45741.38688657407</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>44704</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44207</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>45468.45995370371</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>45798</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>45841.5721875</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>44993</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44863</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>44489</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>45280</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>45065</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>44683</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>45609.83747685186</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45708</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>45450.63958333333</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>45225</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>45474</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>45735.54510416667</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>44955.71322916666</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>45205</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>45081</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>45082</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>45092</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>44210</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>44209</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>44306</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44642</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>44650.86518518518</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>44540</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>44650.8699537037</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44447</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>44833</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>44284.59546296296</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>44069</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>44420</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>44420</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>44330</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>44097</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>44777</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44728.73465277778</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>44810.85092592592</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>44552</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>44560</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>44470.72148148148</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>44771</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>44634</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>44581.75819444445</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>44111.45320601852</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>44477.94327546296</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44380</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>44524</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>44399.43450231481</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44574.42978009259</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44516.72827546296</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>44868</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>44309.47061342592</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44834</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44103</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>44161</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44252</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44451</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44400</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         <v>44496</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>44858</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>44244</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>44690</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>44626</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>44682.79203703703</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>44708</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>44642</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>44776</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>44103</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>44746</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>44176</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>44306</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>44214</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>44727</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>44845.47585648148</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>44543</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>44543</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>44694.57549768518</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>44495</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>44749.61980324074</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>44882.44732638889</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>44882</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>44224</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>44545.4189699074</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>44279</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>44314</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>44300</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>44722</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44742</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>44806.34577546296</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>44294</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>44756.40881944444</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>44124</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44330</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>44330</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>44511.69885416667</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>44510</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>44447</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>44391.5580787037</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>44435</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>44067</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>44867</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>44571</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>44453</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>44511</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>44495</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>44201</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>44201</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>44683</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44375</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44539</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44516.5275462963</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44496</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>44694.57413194444</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>44299</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44414.81494212963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44380</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44594.75950231482</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>44363.5784375</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44712.83118055556</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>44769.62320601852</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44251.43971064815</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>44698</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>44572</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>44397</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>44845.47672453704</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>44270</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44270</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>44543</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44543</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>44650.92714120371</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>44526</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>44760</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>44609</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>44545</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>44545</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>44817.70516203704</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>44725.49491898148</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44427</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44477</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>44230</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>44230</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>44621</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>44496.77542824074</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>44868</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>44251</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44580</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44665.66407407408</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44658</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44777</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>44100</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44880.68423611111</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>44584.91538194445</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>44678</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>44637</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>44300</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>44735</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>44637</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>44816.89569444444</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>44655.45373842592</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>44682.75924768519</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>44682.77616898148</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>44623</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>44350</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>44143</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>44763.4182175926</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         <v>44502</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>44105</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>44132</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>44665.65474537037</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44665.78351851852</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>44466.37496527778</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>44076</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>44595</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>44642.55565972222</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>44376</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19414,7 +19414,7 @@
         <v>44153</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>44533</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>44342</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>44735</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>44176</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>44704</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>44543</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>44333</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>44682.76528935185</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>44744</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>44523.61635416667</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>44595</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>44370.72197916666</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>44725</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>44284</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>44350</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>44637</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>44826</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>44326</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>44607</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44815</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>44425</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>44425</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>44524</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>44495</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
         <v>44379</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         <v>44309</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>45621.34813657407</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45092</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44575.52831018518</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>45730.35026620371</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45772.51127314815</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>45405.57927083333</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44231</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>44949</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>44272</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>44643</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>44743.47407407407</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>44315</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>45705.66126157407</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>44949</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44266</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>44376</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>44953.67443287037</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>45644.47878472223</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45772.30436342592</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>44963</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>45330.50098379629</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>45273</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45086.3629050926</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>45253.55641203704</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45737.43347222222</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>45694.68207175926</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>45075.91362268518</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45075.91971064815</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45218</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>44764</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         <v>45051.455</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>44098</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>45749</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>45175</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>45362.62811342593</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>44778.92797453704</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>45084.54459490741</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>45356.4722800926</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>44285</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>44882</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>45455.33037037037</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>45147.65222222222</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45147.65311342593</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>45147</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>45203.63303240741</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44840</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>45433.58431712963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>44824.36069444445</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>45383</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>45435</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>44895</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>44419</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45772.3078125</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>45397</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>44556</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>45473.94501157408</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45625</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>45259</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45208</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>44705.60626157407</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>44879.70518518519</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45450.64208333333</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45450</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>45755.36583333334</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>44470</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>45253.63089120371</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>45776.62563657408</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45223</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>44272</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>45239</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
         <v>45316.60306712963</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>44621</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>45776.47346064815</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45776.46369212963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>45391.3395949074</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>44845.48064814815</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>45776.59871527777</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>44833.40876157407</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>44868.45741898148</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>45190.55609953704</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>45776.47122685185</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45485</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>45104</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>45104</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25801,7 +25801,7 @@
         <v>45769</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>45376.64532407407</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>45558.46283564815</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44510</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>45576</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>45783</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>44105</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>45783.66429398148</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>45783.48878472222</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45418</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>45454.65774305556</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45385.38146990741</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>45385.36243055556</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45485.60261574074</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45549</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45536</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>45187</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45735</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>45581</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>45170</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
         <v>45709.39361111111</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>44525</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>44546</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>44516</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>44516.40674768519</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45468.45541666666</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45468.45747685185</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>45610.39271990741</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>45572.57828703704</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>45460.44347222222</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>44769.66039351852</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>45785.65300925926</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>45537</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>45579</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>45271</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>45642.64634259259</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>45831.56521990741</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>45260</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>44637</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45352.74090277778</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>44578</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44325</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>44461</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45443</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>45408.57707175926</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45245</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>45715</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>45786.55645833333</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>45635.88849537037</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>44108</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>44953.69298611111</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>45533</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>45547</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>44139.54078703704</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>44584.91001157407</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45177</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45721.88684027778</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>45272.64479166667</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>45272</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45600.4558912037</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>45540</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>44809</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>45385.37922453704</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>45729.7271875</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>45202</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>45713</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>44795</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29675,7 +29675,7 @@
         <v>45436</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>45075</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>45075</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>45075.90934027778</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45518</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45735</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>45089</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45475.61896990741</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45075.90270833333</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>45203.83891203703</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45589.68289351852</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45075.91042824074</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>45075.91265046296</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>45075.92153935185</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>44708.67822916667</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>44596</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30592,7 +30592,7 @@
         <v>45840.70885416667</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45798.66767361111</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45786</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>45636.38974537037</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45798.67082175926</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>45798</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>45798.66104166667</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30991,7 +30991,7 @@
         <v>45797.58399305555</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31048,7 +31048,7 @@
         <v>45639.45166666667</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         <v>45797.58350694444</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>45639.47385416667</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>45478.42887731481</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>45644.90815972222</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>45800</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>45450.64643518518</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>45640.60240740741</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>45800</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31566,7 +31566,7 @@
         <v>45800</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31623,7 +31623,7 @@
         <v>45600.47275462963</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>44580</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31737,7 +31737,7 @@
         <v>45799</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>45113</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>45113</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>44673</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>45800</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>45800</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>44648</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>45803.4675</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>44643</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>45224</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>45800</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>45803.69228009259</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>45559.54706018518</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>44962</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>45089</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>45804.74479166666</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45549</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>44813</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>44816</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>45456</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45803.66587962963</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>45617.58453703704</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>45121</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>45844.62609953704</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>45726.48152777777</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>45586</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>45844.91234953704</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>45131.666875</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>44866.63775462963</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>44649</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>44155.69458333333</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>45847.37414351852</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33576,7 +33576,7 @@
         <v>45448.56746527777</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45257</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>45418.6968287037</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33747,7 +33747,7 @@
         <v>45232</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>45847.48436342592</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>45735.36594907408</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>45729.71065972222</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>45376.55484953704</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34037,7 +34037,7 @@
         <v>44362.37172453704</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34099,7 +34099,7 @@
         <v>44819</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34156,7 +34156,7 @@
         <v>45063.35880787037</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34213,7 +34213,7 @@
         <v>45386.34175925926</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34270,7 +34270,7 @@
         <v>44956</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45183</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>44644</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>44472</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45119.57728009259</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>45810.42393518519</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44635</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>45463.80486111111</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44656</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45687.5038425926</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>44670</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>45695.57881944445</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>45608</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>45457</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>45468.45628472222</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>45617.62358796296</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>44076</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35259,7 +35259,7 @@
         <v>45069</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45208.58004629629</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>45790.81410879629</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>45427.88731481481</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>45202.65660879629</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>45810.5333912037</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>45664</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35678,7 +35678,7 @@
         <v>44470.72987268519</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         <v>44834.38636574074</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>44624.59434027778</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>44113</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>45147.65407407407</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>44687</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36025,7 +36025,7 @@
         <v>45757.65178240741</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45775.41451388889</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45524</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>44697</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45146</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>45341.39853009259</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45852.58030092593</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45522.44414351852</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45483.57244212963</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>44100</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>44869</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>45810.45236111111</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>45810.45263888889</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         <v>45685.44592592592</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36828,7 +36828,7 @@
         <v>45376.54115740741</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>45757.62482638889</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>44474.62141203704</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36999,7 +36999,7 @@
         <v>45174.68702546296</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>45169</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>45686.65545138889</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37180,7 +37180,7 @@
         <v>45721.40780092592</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37237,7 +37237,7 @@
         <v>45709.40231481481</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>44704</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>44952.57989583333</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>45469</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>45469</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>45810.45633101852</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>45811.60451388889</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37646,7 +37646,7 @@
         <v>45670.65921296296</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37703,7 +37703,7 @@
         <v>45208</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>45208</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>45237</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>45145.63584490741</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>45700</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>44680</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>44395</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>44132</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38164,7 +38164,7 @@
         <v>45245</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45855.68413194444</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>45855.57033564815</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>45813.63650462963</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>44708</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>44708.36708333333</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>45813.66961805556</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>45813.6799537037</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45855.69387731481</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45586</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45813.4709375</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38816,7 +38816,7 @@
         <v>44540</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>45414.65855324074</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>44133</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>44746.58530092592</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>45089</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39101,7 +39101,7 @@
         <v>44985</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>44904</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>44143</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45376.55638888889</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39334,7 +39334,7 @@
         <v>44901</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>45679</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>44684</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>45127.69371527778</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>45817.2565625</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>45817.30329861111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45817.31085648148</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>45817.31708333334</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45817.31986111111</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45817.33503472222</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45859</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39971,7 +39971,7 @@
         <v>45859</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>44592</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>45721</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>45075.91148148148</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45245</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>45748.53761574074</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>44743.67418981482</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45075</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>44145</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45747.63471064815</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>45817.291875</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>45817.32538194444</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>45817.25471064815</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40717,7 +40717,7 @@
         <v>45610.47414351852</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40774,7 +40774,7 @@
         <v>44732</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>45817.34083333334</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>45208.70996527778</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>44993.66707175926</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44124</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>44511.70518518519</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>45531</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>44977</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41235,7 +41235,7 @@
         <v>44525</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45840</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>44181</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>44722</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>45188.41637731482</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45168.40565972222</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>45128</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45824.37275462963</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>45442.45686342593</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>45155</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>44938</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45868.62267361111</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>44799.65013888889</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45680.42665509259</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45293</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45219.56697916667</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45845</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45728.38409722222</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>44813.59915509259</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>44325</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>44179</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>44162</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>44959.74533564815</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>44902</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>45831.51659722222</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>45831.65079861111</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45735</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45735.60863425926</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45254.41509259259</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>44690</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45687</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>45534.38240740741</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>44923.90159722222</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>44183</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45412.4104050926</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45831.4844212963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45730.69502314815</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45832.66385416667</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>44585</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45831.54618055555</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>44925</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45706.40086805556</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>44111.44373842593</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45552.52827546297</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>44806.41576388889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45834</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>45876.45253472222</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45834.6447337963</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45699.46283564815</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>44783</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>44785</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45394.72869212963</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44264,7 +44264,7 @@
         <v>44945.67409722223</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44321,7 +44321,7 @@
         <v>45834.65538194445</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44378,7 +44378,7 @@
         <v>44937</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44435,7 +44435,7 @@
         <v>45145.51</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44492,7 +44492,7 @@
         <v>45835.68076388889</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         <v>45293</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44611,7 +44611,7 @@
         <v>45019.3959837963</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44668,7 +44668,7 @@
         <v>45835.4928125</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44730,7 +44730,7 @@
         <v>45345.6059837963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44787,7 +44787,7 @@
         <v>45215</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>45631.73952546297</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44901,7 +44901,7 @@
         <v>45631.74673611111</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44958,7 +44958,7 @@
         <v>44769</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>44629</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45077,7 +45077,7 @@
         <v>45880.46524305556</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>44617</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>45692</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45253,7 +45253,7 @@
         <v>45880.46372685185</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>45835.46034722222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45377,7 +45377,7 @@
         <v>44217.40149305556</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>44732</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>45401.3653125</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>45835</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>45837</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45837.94081018519</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45880.46189814815</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>45838.43261574074</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45208.69671296296</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45238</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
         <v>44698</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>45155</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46071,7 +46071,7 @@
         <v>45469</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46128,7 +46128,7 @@
         <v>45254</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46185,7 +46185,7 @@
         <v>45260.43225694444</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46242,7 +46242,7 @@
         <v>45260.4333449074</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>44146</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46356,7 +46356,7 @@
         <v>44714.56040509259</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45837.93730324074</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>44621</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46527,7 +46527,7 @@
         <v>45840.62755787037</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>45532</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>45839.62398148148</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46698,7 +46698,7 @@
         <v>45840.67829861111</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45839</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46812,7 +46812,7 @@
         <v>45212</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46869,7 +46869,7 @@
         <v>45853</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46926,7 +46926,7 @@
         <v>45853</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46983,7 +46983,7 @@
         <v>45882.59722222222</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47040,7 +47040,7 @@
         <v>45640.58716435185</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45575</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47154,7 +47154,7 @@
         <v>45205</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47211,7 +47211,7 @@
         <v>45841.74596064815</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>45629.65143518519</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47330,7 +47330,7 @@
         <v>45841.35611111111</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>45328.46336805556</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>45884.48696759259</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>44888</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>44867.62090277778</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45589.6756712963</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45701.44372685185</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47729,7 +47729,7 @@
         <v>45223</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45642.63512731482</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45721.65858796296</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45841.5737962963</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>45841.56996527778</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>45456</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48071,7 +48071,7 @@
         <v>44611</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>44152</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>44986.5887962963</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>45842.46885416667</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>45048</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>45525</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>45531</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>44319</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>44691.5652662037</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45740.47055555556</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>44326</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>44908.77368055555</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>44775</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>45223</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48874,7 +48874,7 @@
         <v>44251</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45518</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45070</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>44693</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>45033</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>44963</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45112</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>44266</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49330,7 +49330,7 @@
         <v>44266</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>44769.66864583334</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>44306</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49506,7 +49506,7 @@
         <v>45183</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>44867</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49620,7 +49620,7 @@
         <v>44778</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49677,7 +49677,7 @@
         <v>45623.62563657408</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>45075</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>44854</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>45712</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>44778.69210648148</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>44747</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45348.46300925926</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50091,7 +50091,7 @@
         <v>44832</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50148,7 +50148,7 @@
         <v>44960.60469907407</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50205,7 +50205,7 @@
         <v>44803</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50262,7 +50262,7 @@
         <v>45581</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50319,7 +50319,7 @@
         <v>45693</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50376,7 +50376,7 @@
         <v>45730.42851851852</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50438,7 +50438,7 @@
         <v>45092</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50495,7 +50495,7 @@
         <v>45092</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50552,7 +50552,7 @@
         <v>45075.90817129629</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50609,7 +50609,7 @@
         <v>44682.78430555556</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50666,7 +50666,7 @@
         <v>44797</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50723,7 +50723,7 @@
         <v>44252</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50780,7 +50780,7 @@
         <v>45587</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50837,7 +50837,7 @@
         <v>45085.5309375</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50899,7 +50899,7 @@
         <v>44243.33587962963</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50956,7 +50956,7 @@
         <v>45636.41572916666</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51013,7 +51013,7 @@
         <v>45020</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51070,7 +51070,7 @@
         <v>45139.51457175926</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51127,7 +51127,7 @@
         <v>45370</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51184,7 +51184,7 @@
         <v>45614.39627314815</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51241,7 +51241,7 @@
         <v>44704</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51298,7 +51298,7 @@
         <v>45022</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51355,7 +51355,7 @@
         <v>44903</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51412,7 +51412,7 @@
         <v>44925</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51469,7 +51469,7 @@
         <v>45168.44489583333</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51531,7 +51531,7 @@
         <v>45733.82105324074</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>44528.91494212963</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51645,7 +51645,7 @@
         <v>44866.49827546296</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51702,7 +51702,7 @@
         <v>45446.4287962963</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>44790</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51816,7 +51816,7 @@
         <v>45561.62141203704</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51873,7 +51873,7 @@
         <v>45414</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51930,7 +51930,7 @@
         <v>45411.54768518519</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>44922</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52049,7 +52049,7 @@
         <v>44953.70481481482</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52106,7 +52106,7 @@
         <v>44767.60601851852</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52163,7 +52163,7 @@
         <v>45519</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52220,7 +52220,7 @@
         <v>45107.42538194444</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52277,7 +52277,7 @@
         <v>45111</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52334,7 +52334,7 @@
         <v>44490.02482638889</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52391,7 +52391,7 @@
         <v>44490.03621527777</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52448,7 +52448,7 @@
         <v>44995</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52505,7 +52505,7 @@
         <v>44266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52562,7 +52562,7 @@
         <v>44083</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52619,7 +52619,7 @@
         <v>44750.66068287037</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52676,7 +52676,7 @@
         <v>44750</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>45338</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52790,7 +52790,7 @@
         <v>45082</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52847,7 +52847,7 @@
         <v>45082.68922453704</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52904,7 +52904,7 @@
         <v>44771</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52966,7 +52966,7 @@
         <v>44974</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -53023,7 +53023,7 @@
         <v>44771</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -53080,7 +53080,7 @@
         <v>44813</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>44376.50728009259</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53194,7 +53194,7 @@
         <v>45609.70778935185</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53256,7 +53256,7 @@
         <v>45609.85146990741</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53313,7 +53313,7 @@
         <v>44743.59331018518</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53375,7 +53375,7 @@
         <v>45468.45877314815</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53432,7 +53432,7 @@
         <v>45261</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53489,7 +53489,7 @@
         <v>45427.89121527778</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53546,7 +53546,7 @@
         <v>45587.62565972222</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53603,7 +53603,7 @@
         <v>45259</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53660,7 +53660,7 @@
         <v>45253.61146990741</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
         <v>45435.43466435185</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53774,7 +53774,7 @@
         <v>45435.43820601852</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53831,7 +53831,7 @@
         <v>45621.34425925926</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53893,7 +53893,7 @@
         <v>45621.35712962963</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53955,7 +53955,7 @@
         <v>45600.411875</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -54012,7 +54012,7 @@
         <v>45601.56726851852</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -54069,7 +54069,7 @@
         <v>45435.43123842592</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -54126,7 +54126,7 @@
         <v>45177.61498842593</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -54183,7 +54183,7 @@
         <v>45635.44788194444</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54240,7 +54240,7 @@
         <v>45282</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54297,7 +54297,7 @@
         <v>44938</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54354,7 +54354,7 @@
         <v>44763.40914351852</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54411,7 +54411,7 @@
         <v>44260</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54473,7 +54473,7 @@
         <v>45630.52866898148</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54530,7 +54530,7 @@
         <v>44753</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54587,7 +54587,7 @@
         <v>45728.38924768518</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54644,7 +54644,7 @@
         <v>44698</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54706,7 +54706,7 @@
         <v>45667.49878472222</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54763,7 +54763,7 @@
         <v>45729.72851851852</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54825,7 +54825,7 @@
         <v>44097</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54882,7 +54882,7 @@
         <v>44777</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54939,7 +54939,7 @@
         <v>44495.5893287037</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54996,7 +54996,7 @@
         <v>45668.67446759259</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -55053,7 +55053,7 @@
         <v>45670.3079050926</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -55110,7 +55110,7 @@
         <v>44749.55258101852</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -55167,7 +55167,7 @@
         <v>44782</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55224,7 +55224,7 @@
         <v>44218</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55281,7 +55281,7 @@
         <v>45007</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55338,7 +55338,7 @@
         <v>44599.58428240741</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55395,7 +55395,7 @@
         <v>45713.92623842593</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55452,7 +55452,7 @@
         <v>44743.59765046297</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55514,7 +55514,7 @@
         <v>44743.64592592593</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55576,7 +55576,7 @@
         <v>45152</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55633,7 +55633,7 @@
         <v>45640.57305555556</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55690,7 +55690,7 @@
         <v>44719</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55747,7 +55747,7 @@
         <v>44326.61967592593</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55804,7 +55804,7 @@
         <v>44858</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55861,7 +55861,7 @@
         <v>44980</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55918,7 +55918,7 @@
         <v>45700</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55975,7 +55975,7 @@
         <v>45183</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -56032,7 +56032,7 @@
         <v>45638.5987037037</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -56094,7 +56094,7 @@
         <v>45453</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -56151,7 +56151,7 @@
         <v>45770</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -56208,7 +56208,7 @@
         <v>45310.40628472222</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56265,7 +56265,7 @@
         <v>45310</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56322,7 +56322,7 @@
         <v>45743.44953703704</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56379,7 +56379,7 @@
         <v>45707.84997685185</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56436,7 +56436,7 @@
         <v>44700.50659722222</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56493,7 +56493,7 @@
         <v>44777</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56550,7 +56550,7 @@
         <v>45085</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56607,7 +56607,7 @@
         <v>45243.45289351852</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56669,7 +56669,7 @@
         <v>45254</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56726,7 +56726,7 @@
         <v>44760</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56783,7 +56783,7 @@
         <v>45042.74291666667</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56840,7 +56840,7 @@
         <v>44375</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56897,7 +56897,7 @@
         <v>45219</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56954,7 +56954,7 @@
         <v>45089</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -57011,7 +57011,7 @@
         <v>45442</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -57068,7 +57068,7 @@
         <v>45159</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -57125,7 +57125,7 @@
         <v>45068.51783564815</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -57182,7 +57182,7 @@
         <v>45322</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57239,7 +57239,7 @@
         <v>45414.58650462963</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57296,7 +57296,7 @@
         <v>45063</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57353,7 +57353,7 @@
         <v>45162</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57415,7 +57415,7 @@
         <v>45679</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57472,7 +57472,7 @@
         <v>45706.61178240741</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57534,7 +57534,7 @@
         <v>45139</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57591,7 +57591,7 @@
         <v>44398</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57653,7 +57653,7 @@
         <v>45019.28847222222</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57710,7 +57710,7 @@
         <v>45082.69179398148</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57767,7 +57767,7 @@
         <v>45191</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>45482.53388888889</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>44510.51422453704</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57948,7 +57948,7 @@
         <v>44815.74539351852</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>44956</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>44956</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -58119,7 +58119,7 @@
         <v>44380.77346064815</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45771</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58233,7 +58233,7 @@
         <v>45084.57695601852</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58295,7 +58295,7 @@
         <v>45257</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58352,7 +58352,7 @@
         <v>44803</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58409,7 +58409,7 @@
         <v>45740.47288194444</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58466,7 +58466,7 @@
         <v>45730.69143518519</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58523,7 +58523,7 @@
         <v>45554.55707175926</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58580,7 +58580,7 @@
         <v>44670.4190162037</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58637,7 +58637,7 @@
         <v>44687</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58694,7 +58694,7 @@
         <v>44851</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>45772.71221064815</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58808,7 +58808,7 @@
         <v>45215</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58865,7 +58865,7 @@
         <v>44110</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58927,7 +58927,7 @@
         <v>45054</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58984,7 +58984,7 @@
         <v>45691.41101851852</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -59041,7 +59041,7 @@
         <v>45772.29622685185</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -59098,7 +59098,7 @@
         <v>45708.61761574074</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59155,7 +59155,7 @@
         <v>44456</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59212,7 +59212,7 @@
         <v>45729.60859953704</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59274,7 +59274,7 @@
         <v>45236.46369212963</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59331,7 +59331,7 @@
         <v>44732</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59388,7 +59388,7 @@
         <v>45056</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59445,7 +59445,7 @@
         <v>45530</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59502,7 +59502,7 @@
         <v>45055.43509259259</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59559,7 +59559,7 @@
         <v>45735.59287037037</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59616,7 +59616,7 @@
         <v>45218.65849537037</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59673,7 +59673,7 @@
         <v>44817.56120370371</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59730,7 +59730,7 @@
         <v>44390</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59787,7 +59787,7 @@
         <v>45075</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>45735.36873842592</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59901,7 +59901,7 @@
         <v>45022</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59958,7 +59958,7 @@
         <v>45723</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -60020,7 +60020,7 @@
         <v>45764.6359837963</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -60077,7 +60077,7 @@
         <v>44596.66335648148</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>44841.52804398148</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60201,7 +60201,7 @@
         <v>45518</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60258,7 +60258,7 @@
         <v>45757.61421296297</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60315,7 +60315,7 @@
         <v>44549</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60372,7 +60372,7 @@
         <v>44145</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60429,7 +60429,7 @@
         <v>45063</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60486,7 +60486,7 @@
         <v>45065.55917824074</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60548,7 +60548,7 @@
         <v>45721.89123842592</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60605,7 +60605,7 @@
         <v>45490.45342592592</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45469</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60724,7 +60724,7 @@
         <v>45708</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60786,7 +60786,7 @@
         <v>44459</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60848,7 +60848,7 @@
         <v>44452</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60905,7 +60905,7 @@
         <v>44934</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60962,7 +60962,7 @@
         <v>44124</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -61024,7 +61024,7 @@
         <v>44778</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -61081,7 +61081,7 @@
         <v>44581</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -61138,7 +61138,7 @@
         <v>45376.55704861111</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -61195,7 +61195,7 @@
         <v>45293.37263888889</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -61252,7 +61252,7 @@
         <v>44760</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -61309,7 +61309,7 @@
         <v>44760</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61366,7 +61366,7 @@
         <v>45245</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61423,7 +61423,7 @@
         <v>45245</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61480,7 +61480,7 @@
         <v>44816</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61537,7 +61537,7 @@
         <v>44956.65920138889</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61594,7 +61594,7 @@
         <v>44931.65626157408</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61651,7 +61651,7 @@
         <v>45460.45523148148</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61708,7 +61708,7 @@
         <v>45293</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61765,7 +61765,7 @@
         <v>45089</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61822,7 +61822,7 @@
         <v>45726.48377314815</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61879,7 +61879,7 @@
         <v>44321</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61936,7 +61936,7 @@
         <v>45118</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61998,7 +61998,7 @@
         <v>45723</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -62060,7 +62060,7 @@
         <v>45617.57439814815</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -62117,7 +62117,7 @@
         <v>45740.47550925926</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -62174,7 +62174,7 @@
         <v>45740.47724537037</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -62231,7 +62231,7 @@
         <v>45344</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62288,7 +62288,7 @@
         <v>45706.60130787037</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62350,7 +62350,7 @@
         <v>44900</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62407,7 +62407,7 @@
         <v>44714.92253472222</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62464,7 +62464,7 @@
         <v>44743.59504629629</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62526,7 +62526,7 @@
         <v>45548.72306712963</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62583,7 +62583,7 @@
         <v>45245</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62640,7 +62640,7 @@
         <v>45356.47784722222</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62697,7 +62697,7 @@
         <v>45092</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62754,7 +62754,7 @@
         <v>44637</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>44816</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62868,7 +62868,7 @@
         <v>45757.60658564815</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62925,7 +62925,7 @@
         <v>45231.34144675926</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62982,7 +62982,7 @@
         <v>45104</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -63044,7 +63044,7 @@
         <v>44992</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -63101,7 +63101,7 @@
         <v>45760.91174768518</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -63158,7 +63158,7 @@
         <v>45075.90703703704</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -63215,7 +63215,7 @@
         <v>45490.60572916667</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63272,7 +63272,7 @@
         <v>44483</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63329,7 +63329,7 @@
         <v>45054.54091435186</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63386,7 +63386,7 @@
         <v>45054</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63443,7 +63443,7 @@
         <v>45638.59979166667</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63505,7 +63505,7 @@
         <v>45357</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63562,7 +63562,7 @@
         <v>45104</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63619,7 +63619,7 @@
         <v>45394.58778935186</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63681,7 +63681,7 @@
         <v>45022.61003472222</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63738,7 +63738,7 @@
         <v>45058.78607638889</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63795,7 +63795,7 @@
         <v>45600.86128472222</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>

--- a/Översikt NORRTÄLJE.xlsx
+++ b/Översikt NORRTÄLJE.xlsx
@@ -567,7 +567,7 @@
         <v>45135</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44757</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44249</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45757</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>44909</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45457</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45226</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45367</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45715</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44949</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45436</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>45190</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44263</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>44550</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>44467</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45586.88145833334</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>45600</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45638</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45688.38224537037</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>44846</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>44858</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>44447</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>45400.5958912037</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>44650</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>45800</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>45831.53390046296</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>45748.6521875</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>44076</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>45068</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>44544</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44711</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>45784.32179398148</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>45783.58123842593</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44545</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>45722</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>45847.47052083333</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44336</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44839</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44300</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44749</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>44843</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>44279</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>45616.54866898148</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>45611.47233796296</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>44866</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45821</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44945</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44698</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>44370</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>44489</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>45219</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>44763</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45772.31609953703</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>45723</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>45609.37094907407</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>45800</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>45847.47685185185</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>45226</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44670</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>45446.35888888889</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         <v>44868</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44872</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>45772.30234953704</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44573</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>44102</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>44564.66387731482</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44161</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>44363</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>44788.70217592592</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44680</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>44695.43527777777</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>45784.54878472222</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44620</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44855</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>45794.63298611111</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>45800</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>45146</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>45532</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>45803.62766203703</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>44956</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>45687.34177083334</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8175,7 +8175,7 @@
         <v>45754</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>44965</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>45826.46392361111</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>45741.38688657407</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>44704</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         <v>44207</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>45468.45995370371</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>45798</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>45841.5721875</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>44993</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44863</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>44489</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9205,7 +9205,7 @@
         <v>45280</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>45065</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>44683</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>45609.83747685186</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45708</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>45450.63958333333</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>45225</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>45474</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9904,7 +9904,7 @@
         <v>45735.54510416667</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>44955.71322916666</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>45205</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>45081</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>45082</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>45092</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>44210</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>44209</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>44306</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44642</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>44650.86518518518</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>44540</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>44650.8699537037</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10827,7 +10827,7 @@
         <v>44447</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>44833</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>44284.59546296296</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>44069</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>44420</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>44420</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>44330</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11231,7 +11231,7 @@
         <v>44097</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>44777</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v>44728.73465277778</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11412,7 +11412,7 @@
         <v>44810.85092592592</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>44552</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>44560</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11588,7 +11588,7 @@
         <v>44470.72148148148</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>44771</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>44634</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>44581.75819444445</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>44111.45320601852</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>44477.94327546296</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>44380</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>44524</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>44399.43450231481</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>44574.42978009259</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>44516.72827546296</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12220,7 +12220,7 @@
         <v>44868</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12277,7 +12277,7 @@
         <v>44309.47061342592</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>44834</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>44103</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12458,7 +12458,7 @@
         <v>44161</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>44252</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12577,7 +12577,7 @@
         <v>44451</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44400</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12691,7 +12691,7 @@
         <v>44496</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>44858</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>44244</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>44690</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>44626</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12976,7 +12976,7 @@
         <v>44682.79203703703</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>44708</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         <v>44642</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>44776</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>44103</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>44746</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>44176</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13380,7 +13380,7 @@
         <v>44306</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>44214</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>44727</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>44845.47585648148</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>44543</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>44543</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>44694.57549768518</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>44495</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13836,7 +13836,7 @@
         <v>44749.61980324074</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         <v>44882.44732638889</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>44882</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>44224</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>44545.4189699074</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>44279</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>44314</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>44300</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>44722</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44742</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>44806.34577546296</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>44294</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>44756.40881944444</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>44124</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44330</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>44330</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>44511.69885416667</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14810,7 +14810,7 @@
         <v>44510</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>44447</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>44391.5580787037</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>44435</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15038,7 +15038,7 @@
         <v>44067</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>44867</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>44571</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>44453</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>44511</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15323,7 +15323,7 @@
         <v>44495</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15380,7 +15380,7 @@
         <v>44201</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>44201</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>44683</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44375</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44539</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44516.5275462963</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44496</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>44694.57413194444</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>44299</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15893,7 +15893,7 @@
         <v>44414.81494212963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>44380</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16007,7 +16007,7 @@
         <v>44594.75950231482</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         <v>44363.5784375</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16121,7 +16121,7 @@
         <v>44712.83118055556</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16178,7 +16178,7 @@
         <v>44769.62320601852</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>44251.43971064815</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>44698</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>44572</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>44397</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>44845.47672453704</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>44270</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44270</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>44543</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>44543</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>44650.92714120371</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>44526</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>44760</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>44609</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>44545</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>44545</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>44817.70516203704</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>44725.49491898148</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>44427</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44477</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>44230</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17385,7 +17385,7 @@
         <v>44230</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>44621</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>44496.77542824074</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>44868</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>44251</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>44580</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>44665.66407407408</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>44658</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44777</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>44100</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>44880.68423611111</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>44584.91538194445</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>44678</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>44637</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>44300</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>44735</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>44637</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>44816.89569444444</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>44655.45373842592</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>44682.75924768519</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>44682.77616898148</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>44623</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         <v>44350</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>44143</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18782,7 +18782,7 @@
         <v>44763.4182175926</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         <v>44502</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>44105</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>44132</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19010,7 +19010,7 @@
         <v>44665.65474537037</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44665.78351851852</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19124,7 +19124,7 @@
         <v>44466.37496527778</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
         <v>44076</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>44595</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>44642.55565972222</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19357,7 +19357,7 @@
         <v>44376</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19414,7 +19414,7 @@
         <v>44153</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>44533</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>44342</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>44735</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19647,7 +19647,7 @@
         <v>44176</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>44704</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>44543</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>44333</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>44682.76528935185</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19932,7 +19932,7 @@
         <v>44744</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19989,7 +19989,7 @@
         <v>44523.61635416667</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>44595</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>44370.72197916666</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20160,7 +20160,7 @@
         <v>44725</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>44284</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>44350</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>44637</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>44826</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>44326</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20507,7 +20507,7 @@
         <v>44607</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44815</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>44425</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>44425</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20735,7 +20735,7 @@
         <v>44524</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20792,7 +20792,7 @@
         <v>44495</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
         <v>44379</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20906,7 +20906,7 @@
         <v>44309</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20968,7 +20968,7 @@
         <v>45621.34813657407</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21030,7 +21030,7 @@
         <v>45092</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>44575.52831018518</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>45730.35026620371</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45772.51127314815</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>45405.57927083333</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>44231</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>44949</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>44272</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>44643</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>44743.47407407407</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>44315</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>45705.66126157407</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>44949</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44266</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>44376</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>44953.67443287037</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>45644.47878472223</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45772.30436342592</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>44963</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>45330.50098379629</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>45273</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45086.3629050926</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>45253.55641203704</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>45737.43347222222</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>45694.68207175926</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>45075.91362268518</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>45075.91971064815</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45218</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22651,7 +22651,7 @@
         <v>44764</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         <v>45051.455</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22765,7 +22765,7 @@
         <v>44098</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22822,7 +22822,7 @@
         <v>45749</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>45175</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22941,7 +22941,7 @@
         <v>45362.62811342593</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22998,7 +22998,7 @@
         <v>44778.92797453704</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>45084.54459490741</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>45356.4722800926</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>44285</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>44882</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>45455.33037037037</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>45147.65222222222</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45147.65311342593</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>45147</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23511,7 +23511,7 @@
         <v>45203.63303240741</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>44840</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23625,7 +23625,7 @@
         <v>45433.58431712963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23682,7 +23682,7 @@
         <v>44824.36069444445</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>45383</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>45435</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>44895</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>44419</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45772.3078125</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>45397</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>44556</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>45473.94501157408</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45625</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>45259</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45208</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>44705.60626157407</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>44879.70518518519</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45450.64208333333</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45450</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>45755.36583333334</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>44470</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>45253.63089120371</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>45776.62563657408</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45223</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24889,7 +24889,7 @@
         <v>44272</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>45239</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
         <v>45316.60306712963</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>44621</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>45776.47346064815</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45776.46369212963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>45391.3395949074</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>44845.48064814815</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>45776.59871527777</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>44833.40876157407</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>44868.45741898148</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>45190.55609953704</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>45776.47122685185</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45485</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>45104</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>45104</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25801,7 +25801,7 @@
         <v>45769</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>45376.64532407407</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25915,7 +25915,7 @@
         <v>45558.46283564815</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44510</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>45576</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>45783</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>44105</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26205,7 +26205,7 @@
         <v>45783.66429398148</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>45783.48878472222</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45418</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>45454.65774305556</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45385.38146990741</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>45385.36243055556</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45485.60261574074</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45549</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45536</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>45187</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45735</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>45581</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>45170</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
         <v>45709.39361111111</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>44525</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>44546</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>44516</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>44516.40674768519</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45468.45541666666</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>45468.45747685185</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>45610.39271990741</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>45572.57828703704</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>45460.44347222222</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>44769.66039351852</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>45785.65300925926</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>45537</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>45579</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>45271</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>45642.64634259259</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>45831.56521990741</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>45260</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>44637</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45352.74090277778</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>44578</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44325</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>44461</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45443</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>45408.57707175926</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45245</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>45715</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>45786.55645833333</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>45635.88849537037</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>44108</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>44953.69298611111</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>45533</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>45547</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>44139.54078703704</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>44584.91001157407</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45177</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45721.88684027778</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>45272.64479166667</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>45272</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45600.4558912037</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>45540</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>44809</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>45385.37922453704</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>45729.7271875</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>45202</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>45713</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29618,7 +29618,7 @@
         <v>44795</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29675,7 +29675,7 @@
         <v>45436</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>45075</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>45075</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>45075.90934027778</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45518</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45735</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>45089</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45475.61896990741</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45075.90270833333</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>45203.83891203703</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45589.68289351852</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45075.91042824074</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>45075.91265046296</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>45075.92153935185</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>44708.67822916667</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>44596</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30592,7 +30592,7 @@
         <v>45840.70885416667</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45798.66767361111</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45786</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30763,7 +30763,7 @@
         <v>45636.38974537037</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45798.67082175926</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30877,7 +30877,7 @@
         <v>45798</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30934,7 +30934,7 @@
         <v>45798.66104166667</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30991,7 +30991,7 @@
         <v>45797.58399305555</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31048,7 +31048,7 @@
         <v>45639.45166666667</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31105,7 +31105,7 @@
         <v>45797.58350694444</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>45639.47385416667</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>45478.42887731481</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>45644.90815972222</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>45800</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>45450.64643518518</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31452,7 +31452,7 @@
         <v>45640.60240740741</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31509,7 +31509,7 @@
         <v>45800</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31566,7 +31566,7 @@
         <v>45800</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31623,7 +31623,7 @@
         <v>45600.47275462963</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>44580</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31737,7 +31737,7 @@
         <v>45799</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31794,7 +31794,7 @@
         <v>45113</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31851,7 +31851,7 @@
         <v>45113</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>44673</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>45800</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>45800</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>44648</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>45803.4675</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>44643</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32250,7 +32250,7 @@
         <v>45224</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32307,7 +32307,7 @@
         <v>45800</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>45803.69228009259</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>45559.54706018518</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>44962</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>45089</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>45804.74479166666</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45549</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32711,7 +32711,7 @@
         <v>44813</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>44816</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32825,7 +32825,7 @@
         <v>45456</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45803.66587962963</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         <v>45617.58453703704</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>45121</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>45844.62609953704</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>45726.48152777777</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>45586</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>45844.91234953704</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>45131.666875</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33343,7 +33343,7 @@
         <v>44866.63775462963</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33400,7 +33400,7 @@
         <v>44649</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33457,7 +33457,7 @@
         <v>44155.69458333333</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>45847.37414351852</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33576,7 +33576,7 @@
         <v>45448.56746527777</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45257</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>45418.6968287037</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33747,7 +33747,7 @@
         <v>45232</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>45847.48436342592</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>45735.36594907408</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33918,7 +33918,7 @@
         <v>45729.71065972222</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>45376.55484953704</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34037,7 +34037,7 @@
         <v>44362.37172453704</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34099,7 +34099,7 @@
         <v>44819</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34156,7 +34156,7 @@
         <v>45063.35880787037</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34213,7 +34213,7 @@
         <v>45386.34175925926</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34270,7 +34270,7 @@
         <v>44956</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45183</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>44644</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>44472</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45119.57728009259</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>45810.42393518519</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34612,7 +34612,7 @@
         <v>44635</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>45463.80486111111</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>44656</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45687.5038425926</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>44670</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>45695.57881944445</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>45608</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35026,7 +35026,7 @@
         <v>45457</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>45468.45628472222</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>45617.62358796296</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>44076</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35259,7 +35259,7 @@
         <v>45069</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45208.58004629629</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35393,7 +35393,7 @@
         <v>45790.81410879629</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>45427.88731481481</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>45202.65660879629</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35564,7 +35564,7 @@
         <v>45810.5333912037</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>45664</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35678,7 +35678,7 @@
         <v>44470.72987268519</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         <v>44834.38636574074</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>44624.59434027778</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>44113</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>45147.65407407407</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>44687</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36025,7 +36025,7 @@
         <v>45757.65178240741</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45775.41451388889</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45524</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>44697</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45146</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>45341.39853009259</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45852.58030092593</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45522.44414351852</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45483.57244212963</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>44100</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>44869</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>45810.45236111111</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36714,7 +36714,7 @@
         <v>45810.45263888889</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         <v>45685.44592592592</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36828,7 +36828,7 @@
         <v>45376.54115740741</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>45757.62482638889</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>44474.62141203704</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -36999,7 +36999,7 @@
         <v>45174.68702546296</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>45169</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>45686.65545138889</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37180,7 +37180,7 @@
         <v>45721.40780092592</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37237,7 +37237,7 @@
         <v>45709.40231481481</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>44704</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>44952.57989583333</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>45469</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>45469</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>45810.45633101852</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>45811.60451388889</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37646,7 +37646,7 @@
         <v>45670.65921296296</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37703,7 +37703,7 @@
         <v>45208</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>45208</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>45237</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>45145.63584490741</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>45700</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>44680</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>44395</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>44132</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38164,7 +38164,7 @@
         <v>45245</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45855.68413194444</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>45855.57033564815</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>45813.63650462963</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38402,7 +38402,7 @@
         <v>44708</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38459,7 +38459,7 @@
         <v>44708.36708333333</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>45813.66961805556</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>45813.6799537037</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45855.69387731481</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38697,7 +38697,7 @@
         <v>45586</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45813.4709375</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38816,7 +38816,7 @@
         <v>44540</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>45414.65855324074</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
         <v>44133</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>44746.58530092592</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>45089</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39101,7 +39101,7 @@
         <v>44985</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39158,7 +39158,7 @@
         <v>44904</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>44143</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45376.55638888889</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39334,7 +39334,7 @@
         <v>44901</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>45679</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>44684</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>45127.69371527778</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>45817.2565625</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>45817.30329861111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45817.31085648148</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>45817.31708333334</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45817.31986111111</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45817.33503472222</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45859</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39971,7 +39971,7 @@
         <v>45859</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>44592</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>45721</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>45075.91148148148</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45245</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>45748.53761574074</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>44743.67418981482</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45075</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>44145</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45747.63471064815</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>45817.291875</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>45817.32538194444</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>45817.25471064815</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40717,7 +40717,7 @@
         <v>45610.47414351852</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40774,7 +40774,7 @@
         <v>44732</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>45817.34083333334</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>45208.70996527778</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>44993.66707175926</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44124</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>44511.70518518519</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>45531</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>44977</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41235,7 +41235,7 @@
         <v>44525</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45840</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>44181</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>44722</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>45188.41637731482</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45168.40565972222</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>45128</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45824.37275462963</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>45442.45686342593</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>45155</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41825,7 +41825,7 @@
         <v>44938</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41882,7 +41882,7 @@
         <v>45868.62267361111</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>44799.65013888889</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>45680.42665509259</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45293</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45219.56697916667</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>45845</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45728.38409722222</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>44813.59915509259</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>44325</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>44179</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>44162</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>44959.74533564815</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>44902</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>45831.51659722222</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>45831.65079861111</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45735</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45735.60863425926</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45254.41509259259</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>44690</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45687</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>45534.38240740741</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>44923.90159722222</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>44183</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>45412.4104050926</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43275,7 +43275,7 @@
         <v>45831.4844212963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45730.69502314815</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45832.66385416667</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>44585</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>45831.54618055555</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>44925</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>45706.40086805556</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>44111.44373842593</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>45552.52827546297</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43798,7 +43798,7 @@
         <v>44806.41576388889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45834</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>45876.45253472222</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>45834.6447337963</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44031,7 +44031,7 @@
         <v>45699.46283564815</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44088,7 +44088,7 @@
         <v>44783</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>44785</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44207,7 +44207,7 @@
         <v>45394.72869212963</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44264,7 +44264,7 @@
         <v>44945.67409722223</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44321,7 +44321,7 @@
         <v>45834.65538194445</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44378,7 +44378,7 @@
         <v>44937</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44435,7 +44435,7 @@
         <v>45145.51</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44492,7 +44492,7 @@
         <v>45835.68076388889</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         <v>45293</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44611,7 +44611,7 @@
         <v>45019.3959837963</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44668,7 +44668,7 @@
         <v>45835.4928125</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44730,7 +44730,7 @@
         <v>45345.6059837963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44787,7 +44787,7 @@
         <v>45215</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>45631.73952546297</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44901,7 +44901,7 @@
         <v>45631.74673611111</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44958,7 +44958,7 @@
         <v>44769</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>44629</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45077,7 +45077,7 @@
         <v>45880.46524305556</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45139,7 +45139,7 @@
         <v>44617</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>45692</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45253,7 +45253,7 @@
         <v>45880.46372685185</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>45835.46034722222</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45377,7 +45377,7 @@
         <v>44217.40149305556</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>44732</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>45401.3653125</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>45835</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>45837</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45837.94081018519</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45880.46189814815</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>45838.43261574074</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45843,7 +45843,7 @@
         <v>45208.69671296296</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45238</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
         <v>44698</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>45155</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46071,7 +46071,7 @@
         <v>45469</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46128,7 +46128,7 @@
         <v>45254</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46185,7 +46185,7 @@
         <v>45260.43225694444</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46242,7 +46242,7 @@
         <v>45260.4333449074</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>44146</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46356,7 +46356,7 @@
         <v>44714.56040509259</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45837.93730324074</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>44621</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46527,7 +46527,7 @@
         <v>45840.62755787037</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>45532</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>45839.62398148148</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46698,7 +46698,7 @@
         <v>45840.67829861111</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>45839</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46812,7 +46812,7 @@
         <v>45212</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46869,7 +46869,7 @@
         <v>45853</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46926,7 +46926,7 @@
         <v>45853</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46983,7 +46983,7 @@
         <v>45882.59722222222</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47040,7 +47040,7 @@
         <v>45640.58716435185</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47097,7 +47097,7 @@
         <v>45575</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47154,7 +47154,7 @@
         <v>45205</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47211,7 +47211,7 @@
         <v>45841.74596064815</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47268,7 +47268,7 @@
         <v>45629.65143518519</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47330,7 +47330,7 @@
         <v>45841.35611111111</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>45328.46336805556</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47444,7 +47444,7 @@
         <v>45884.48696759259</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>44888</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>44867.62090277778</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45589.6756712963</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45701.44372685185</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47729,7 +47729,7 @@
         <v>45223</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47786,7 +47786,7 @@
         <v>45642.63512731482</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>45721.65858796296</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47900,7 +47900,7 @@
         <v>45841.5737962963</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>45841.56996527778</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>45456</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48071,7 +48071,7 @@
         <v>44611</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>44152</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>44986.5887962963</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>45842.46885416667</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>45048</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>45525</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>45531</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>44319</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48532,7 +48532,7 @@
         <v>44691.5652662037</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45740.47055555556</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48646,7 +48646,7 @@
         <v>44326</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48703,7 +48703,7 @@
         <v>44908.77368055555</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48760,7 +48760,7 @@
         <v>44775</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48817,7 +48817,7 @@
         <v>45223</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48874,7 +48874,7 @@
         <v>44251</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45518</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48988,7 +48988,7 @@
         <v>45070</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49045,7 +49045,7 @@
         <v>44693</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49102,7 +49102,7 @@
         <v>45033</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49159,7 +49159,7 @@
         <v>44963</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49216,7 +49216,7 @@
         <v>45112</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49273,7 +49273,7 @@
         <v>44266</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49330,7 +49330,7 @@
         <v>44266</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49387,7 +49387,7 @@
         <v>44769.66864583334</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49444,7 +49444,7 @@
         <v>44306</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49506,7 +49506,7 @@
         <v>45183</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>44867</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49620,7 +49620,7 @@
         <v>44778</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49677,7 +49677,7 @@
         <v>45623.62563657408</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49739,7 +49739,7 @@
         <v>45075</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49796,7 +49796,7 @@
         <v>44854</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>45712</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49915,7 +49915,7 @@
         <v>44778.69210648148</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49972,7 +49972,7 @@
         <v>44747</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50029,7 +50029,7 @@
         <v>45348.46300925926</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50091,7 +50091,7 @@
         <v>44832</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50148,7 +50148,7 @@
         <v>44960.60469907407</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50205,7 +50205,7 @@
         <v>44803</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50262,7 +50262,7 @@
         <v>45581</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50319,7 +50319,7 @@
         <v>45693</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50376,7 +50376,7 @@
         <v>45730.42851851852</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50438,7 +50438,7 @@
         <v>45092</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50495,7 +50495,7 @@
         <v>45092</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50552,7 +50552,7 @@
         <v>45075.90817129629</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50609,7 +50609,7 @@
         <v>44682.78430555556</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50666,7 +50666,7 @@
         <v>44797</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50723,7 +50723,7 @@
         <v>44252</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50780,7 +50780,7 @@
         <v>45587</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50837,7 +50837,7 @@
         <v>45085.5309375</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50899,7 +50899,7 @@
         <v>44243.33587962963</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50956,7 +50956,7 @@
         <v>45636.41572916666</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51013,7 +51013,7 @@
         <v>45020</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51070,7 +51070,7 @@
         <v>45139.51457175926</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51127,7 +51127,7 @@
         <v>45370</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51184,7 +51184,7 @@
         <v>45614.39627314815</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51241,7 +51241,7 @@
         <v>44704</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51298,7 +51298,7 @@
         <v>45022</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51355,7 +51355,7 @@
         <v>44903</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51412,7 +51412,7 @@
         <v>44925</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51469,7 +51469,7 @@
         <v>45168.44489583333</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51531,7 +51531,7 @@
         <v>45733.82105324074</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>44528.91494212963</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51645,7 +51645,7 @@
         <v>44866.49827546296</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51702,7 +51702,7 @@
         <v>45446.4287962963</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51759,7 +51759,7 @@
         <v>44790</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51816,7 +51816,7 @@
         <v>45561.62141203704</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51873,7 +51873,7 @@
         <v>45414</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51930,7 +51930,7 @@
         <v>45411.54768518519</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>44922</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52049,7 +52049,7 @@
         <v>44953.70481481482</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52106,7 +52106,7 @@
         <v>44767.60601851852</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52163,7 +52163,7 @@
         <v>45519</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52220,7 +52220,7 @@
         <v>45107.42538194444</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52277,7 +52277,7 @@
         <v>45111</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52334,7 +52334,7 @@
         <v>44490.02482638889</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52391,7 +52391,7 @@
         <v>44490.03621527777</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52448,7 +52448,7 @@
         <v>44995</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52505,7 +52505,7 @@
         <v>44266</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52562,7 +52562,7 @@
         <v>44083</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52619,7 +52619,7 @@
         <v>44750.66068287037</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52676,7 +52676,7 @@
         <v>44750</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>45338</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52790,7 +52790,7 @@
         <v>45082</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52847,7 +52847,7 @@
         <v>45082.68922453704</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52904,7 +52904,7 @@
         <v>44771</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52966,7 +52966,7 @@
         <v>44974</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -53023,7 +53023,7 @@
         <v>44771</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -53080,7 +53080,7 @@
         <v>44813</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>44376.50728009259</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53194,7 +53194,7 @@
         <v>45609.70778935185</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53256,7 +53256,7 @@
         <v>45609.85146990741</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53313,7 +53313,7 @@
         <v>44743.59331018518</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53375,7 +53375,7 @@
         <v>45468.45877314815</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53432,7 +53432,7 @@
         <v>45261</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53489,7 +53489,7 @@
         <v>45427.89121527778</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53546,7 +53546,7 @@
         <v>45587.62565972222</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53603,7 +53603,7 @@
         <v>45259</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53660,7 +53660,7 @@
         <v>45253.61146990741</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53717,7 +53717,7 @@
         <v>45435.43466435185</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53774,7 +53774,7 @@
         <v>45435.43820601852</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53831,7 +53831,7 @@
         <v>45621.34425925926</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53893,7 +53893,7 @@
         <v>45621.35712962963</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53955,7 +53955,7 @@
         <v>45600.411875</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -54012,7 +54012,7 @@
         <v>45601.56726851852</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -54069,7 +54069,7 @@
         <v>45435.43123842592</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -54126,7 +54126,7 @@
         <v>45177.61498842593</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -54183,7 +54183,7 @@
         <v>45635.44788194444</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54240,7 +54240,7 @@
         <v>45282</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54297,7 +54297,7 @@
         <v>44938</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54354,7 +54354,7 @@
         <v>44763.40914351852</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54411,7 +54411,7 @@
         <v>44260</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54473,7 +54473,7 @@
         <v>45630.52866898148</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54530,7 +54530,7 @@
         <v>44753</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54587,7 +54587,7 @@
         <v>45728.38924768518</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54644,7 +54644,7 @@
         <v>44698</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54706,7 +54706,7 @@
         <v>45667.49878472222</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54763,7 +54763,7 @@
         <v>45729.72851851852</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54825,7 +54825,7 @@
         <v>44097</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54882,7 +54882,7 @@
         <v>44777</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54939,7 +54939,7 @@
         <v>44495.5893287037</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -54996,7 +54996,7 @@
         <v>45668.67446759259</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -55053,7 +55053,7 @@
         <v>45670.3079050926</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -55110,7 +55110,7 @@
         <v>44749.55258101852</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -55167,7 +55167,7 @@
         <v>44782</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55224,7 +55224,7 @@
         <v>44218</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55281,7 +55281,7 @@
         <v>45007</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55338,7 +55338,7 @@
         <v>44599.58428240741</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55395,7 +55395,7 @@
         <v>45713.92623842593</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55452,7 +55452,7 @@
         <v>44743.59765046297</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55514,7 +55514,7 @@
         <v>44743.64592592593</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55576,7 +55576,7 @@
         <v>45152</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55633,7 +55633,7 @@
         <v>45640.57305555556</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55690,7 +55690,7 @@
         <v>44719</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55747,7 +55747,7 @@
         <v>44326.61967592593</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55804,7 +55804,7 @@
         <v>44858</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55861,7 +55861,7 @@
         <v>44980</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55918,7 +55918,7 @@
         <v>45700</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55975,7 +55975,7 @@
         <v>45183</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -56032,7 +56032,7 @@
         <v>45638.5987037037</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -56094,7 +56094,7 @@
         <v>45453</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -56151,7 +56151,7 @@
         <v>45770</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -56208,7 +56208,7 @@
         <v>45310.40628472222</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56265,7 +56265,7 @@
         <v>45310</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56322,7 +56322,7 @@
         <v>45743.44953703704</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56379,7 +56379,7 @@
         <v>45707.84997685185</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56436,7 +56436,7 @@
         <v>44700.50659722222</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56493,7 +56493,7 @@
         <v>44777</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56550,7 +56550,7 @@
         <v>45085</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56607,7 +56607,7 @@
         <v>45243.45289351852</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56669,7 +56669,7 @@
         <v>45254</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56726,7 +56726,7 @@
         <v>44760</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56783,7 +56783,7 @@
         <v>45042.74291666667</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56840,7 +56840,7 @@
         <v>44375</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56897,7 +56897,7 @@
         <v>45219</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56954,7 +56954,7 @@
         <v>45089</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -57011,7 +57011,7 @@
         <v>45442</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -57068,7 +57068,7 @@
         <v>45159</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -57125,7 +57125,7 @@
         <v>45068.51783564815</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -57182,7 +57182,7 @@
         <v>45322</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57239,7 +57239,7 @@
         <v>45414.58650462963</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57296,7 +57296,7 @@
         <v>45063</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57353,7 +57353,7 @@
         <v>45162</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57415,7 +57415,7 @@
         <v>45679</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57472,7 +57472,7 @@
         <v>45706.61178240741</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57534,7 +57534,7 @@
         <v>45139</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57591,7 +57591,7 @@
         <v>44398</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57653,7 +57653,7 @@
         <v>45019.28847222222</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57710,7 +57710,7 @@
         <v>45082.69179398148</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57767,7 +57767,7 @@
         <v>45191</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>45482.53388888889</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57886,7 +57886,7 @@
         <v>44510.51422453704</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57948,7 +57948,7 @@
         <v>44815.74539351852</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -58005,7 +58005,7 @@
         <v>44956</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -58062,7 +58062,7 @@
         <v>44956</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -58119,7 +58119,7 @@
         <v>44380.77346064815</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45771</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58233,7 +58233,7 @@
         <v>45084.57695601852</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58295,7 +58295,7 @@
         <v>45257</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58352,7 +58352,7 @@
         <v>44803</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58409,7 +58409,7 @@
         <v>45740.47288194444</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58466,7 +58466,7 @@
         <v>45730.69143518519</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58523,7 +58523,7 @@
         <v>45554.55707175926</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58580,7 +58580,7 @@
         <v>44670.4190162037</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58637,7 +58637,7 @@
         <v>44687</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58694,7 +58694,7 @@
         <v>44851</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>45772.71221064815</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58808,7 +58808,7 @@
         <v>45215</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58865,7 +58865,7 @@
         <v>44110</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58927,7 +58927,7 @@
         <v>45054</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -58984,7 +58984,7 @@
         <v>45691.41101851852</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -59041,7 +59041,7 @@
         <v>45772.29622685185</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -59098,7 +59098,7 @@
         <v>45708.61761574074</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59155,7 +59155,7 @@
         <v>44456</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59212,7 +59212,7 @@
         <v>45729.60859953704</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59274,7 +59274,7 @@
         <v>45236.46369212963</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59331,7 +59331,7 @@
         <v>44732</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59388,7 +59388,7 @@
         <v>45056</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59445,7 +59445,7 @@
         <v>45530</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59502,7 +59502,7 @@
         <v>45055.43509259259</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59559,7 +59559,7 @@
         <v>45735.59287037037</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59616,7 +59616,7 @@
         <v>45218.65849537037</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59673,7 +59673,7 @@
         <v>44817.56120370371</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59730,7 +59730,7 @@
         <v>44390</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59787,7 +59787,7 @@
         <v>45075</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59844,7 +59844,7 @@
         <v>45735.36873842592</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59901,7 +59901,7 @@
         <v>45022</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59958,7 +59958,7 @@
         <v>45723</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -60020,7 +60020,7 @@
         <v>45764.6359837963</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -60077,7 +60077,7 @@
         <v>44596.66335648148</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>44841.52804398148</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60201,7 +60201,7 @@
         <v>45518</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60258,7 +60258,7 @@
         <v>45757.61421296297</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60315,7 +60315,7 @@
         <v>44549</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60372,7 +60372,7 @@
         <v>44145</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60429,7 +60429,7 @@
         <v>45063</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60486,7 +60486,7 @@
         <v>45065.55917824074</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60548,7 +60548,7 @@
         <v>45721.89123842592</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60605,7 +60605,7 @@
         <v>45490.45342592592</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60667,7 +60667,7 @@
         <v>45469</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60724,7 +60724,7 @@
         <v>45708</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60786,7 +60786,7 @@
         <v>44459</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60848,7 +60848,7 @@
         <v>44452</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60905,7 +60905,7 @@
         <v>44934</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60962,7 +60962,7 @@
         <v>44124</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -61024,7 +61024,7 @@
         <v>44778</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -61081,7 +61081,7 @@
         <v>44581</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -61138,7 +61138,7 @@
         <v>45376.55704861111</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -61195,7 +61195,7 @@
         <v>45293.37263888889</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -61252,7 +61252,7 @@
         <v>44760</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -61309,7 +61309,7 @@
         <v>44760</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61366,7 +61366,7 @@
         <v>45245</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61423,7 +61423,7 @@
         <v>45245</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61480,7 +61480,7 @@
         <v>44816</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61537,7 +61537,7 @@
         <v>44956.65920138889</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61594,7 +61594,7 @@
         <v>44931.65626157408</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61651,7 +61651,7 @@
         <v>45460.45523148148</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61708,7 +61708,7 @@
         <v>45293</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61765,7 +61765,7 @@
         <v>45089</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61822,7 +61822,7 @@
         <v>45726.48377314815</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61879,7 +61879,7 @@
         <v>44321</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61936,7 +61936,7 @@
         <v>45118</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -61998,7 +61998,7 @@
         <v>45723</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -62060,7 +62060,7 @@
         <v>45617.57439814815</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -62117,7 +62117,7 @@
         <v>45740.47550925926</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -62174,7 +62174,7 @@
         <v>45740.47724537037</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -62231,7 +62231,7 @@
         <v>45344</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62288,7 +62288,7 @@
         <v>45706.60130787037</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62350,7 +62350,7 @@
         <v>44900</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62407,7 +62407,7 @@
         <v>44714.92253472222</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62464,7 +62464,7 @@
         <v>44743.59504629629</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62526,7 +62526,7 @@
         <v>45548.72306712963</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62583,7 +62583,7 @@
         <v>45245</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62640,7 +62640,7 @@
         <v>45356.47784722222</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62697,7 +62697,7 @@
         <v>45092</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62754,7 +62754,7 @@
         <v>44637</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>44816</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62868,7 +62868,7 @@
         <v>45757.60658564815</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62925,7 +62925,7 @@
         <v>45231.34144675926</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -62982,7 +62982,7 @@
         <v>45104</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -63044,7 +63044,7 @@
         <v>44992</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -63101,7 +63101,7 @@
         <v>45760.91174768518</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -63158,7 +63158,7 @@
         <v>45075.90703703704</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -63215,7 +63215,7 @@
         <v>45490.60572916667</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63272,7 +63272,7 @@
         <v>44483</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63329,7 +63329,7 @@
         <v>45054.54091435186</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63386,7 +63386,7 @@
         <v>45054</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63443,7 +63443,7 @@
         <v>45638.59979166667</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63505,7 +63505,7 @@
         <v>45357</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63562,7 +63562,7 @@
         <v>45104</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63619,7 +63619,7 @@
         <v>45394.58778935186</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63681,7 +63681,7 @@
         <v>45022.61003472222</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63738,7 +63738,7 @@
         <v>45058.78607638889</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63795,7 +63795,7 @@
         <v>45600.86128472222</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>

--- a/Översikt NORRTÄLJE.xlsx
+++ b/Översikt NORRTÄLJE.xlsx
@@ -567,7 +567,7 @@
         <v>45135</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44757</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44249</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45757</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>44909</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45457</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45226</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45367</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45715</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44949</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45436</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>44263</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>45190</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>44550</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>44467</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45600</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>45586.88145833334</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45688.38224537037</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>45638</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>44846</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>44858</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>44447</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>45400.5958912037</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>44650</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>45800</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>44076</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>45068</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45831.53390046296</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>44544</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>45748.6521875</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44711</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>45783.58123842593</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>45784.32179398148</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44336</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>45722</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>44545</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44839</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>45847.47052083333</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44300</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44749</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>44843</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>44279</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>44866</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>45611.47233796296</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>45616.54866898148</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>44945</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>45821</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44698</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>44370</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>44489</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>44872</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>44763</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45219</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>44868</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>45226</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>44670</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45723</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45609.37094907407</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>45772.30234953704</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>45446.35888888889</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>45800</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45847.47685185185</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>45772.31609953703</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44573</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>44102</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>44564.66387731482</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44161</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>44363</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>44788.70217592592</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44680</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>45205</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>44993</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>45092</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44704</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>44855</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>44489</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>44956</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>45754</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45784.54878472222</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>45082</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>44620</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>45741.38688657407</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>45687.34177083334</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>44955.71322916666</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>45794.63298611111</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>44695.43527777777</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>44863</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>45803.62766203703</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>45532</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>45800</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>45146</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>45708</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>45468.45995370371</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>44965</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>45280</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>45826.46392361111</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>45225</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45798</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>45081</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>45065</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45841.5721875</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>44207</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45609.83747685186</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>45888.62712962963</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>44683</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>45450.63958333333</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>45735.54510416667</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>45474</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>44210</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>44209</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>44306</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44540</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>44642</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>44650.8699537037</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>44447</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>44833</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>44284.59546296296</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>44069</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>44330</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>44420</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>44420</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>44097</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>44728.73465277778</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>44777</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44810.85092592592</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44552</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>44560</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>44470.72148148148</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44634</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>44581.75819444445</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>44771</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>44111.45320601852</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>44477.94327546296</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>44380</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>44524</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44399.43450231481</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>44516.72827546296</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>44574.42978009259</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>44103</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>44868</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>44834</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>44309.47061342592</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>44400</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>44161</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>44252</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>44451</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>44858</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>44244</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>44496</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>44626</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>44690</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>44682.79203703703</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>44708</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>44642</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>44776</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>44103</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>44746</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>44176</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>44214</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>44306</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>44727</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>44543</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>44543</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>44845.47585648148</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>44694.57549768518</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>44495</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13864,7 +13864,7 @@
         <v>44749.61980324074</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>44882.44732638889</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>44882</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>44224</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>44545.4189699074</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>44279</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>44314</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>44300</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>44722</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>44742</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>44806.34577546296</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>44756.40881944444</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>44294</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>44124</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>44330</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>44330</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>44511.69885416667</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>44510</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>44447</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>44391.5580787037</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44435</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44067</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>44867</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>44571</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>44453</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>44511</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>44495</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44683</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>44201</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>44201</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>44375</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>44539</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>44516.5275462963</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>44496</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44299</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>44414.81494212963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>44380</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>44594.75950231482</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>44826</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>44326</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
         <v>44607</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         <v>44425</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>44425</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>44363.5784375</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>44712.83118055556</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>44309</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44769.62320601852</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>44575.52831018518</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>44845.47672453704</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>44251.43971064815</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>44270</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>44270</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>44698</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>44397</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>44543</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>44543</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         <v>44526</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>44572</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>44650.92714120371</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>44760</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>44609</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>44817.70516203704</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>44230</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>44230</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17532,7 +17532,7 @@
         <v>44477</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>44545</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>44545</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>44725.49491898148</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>44427</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>44868</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>44251</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>44621</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>44496.77542824074</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>44580</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>44300</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44665.66407407408</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>44658</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44777</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44100</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44584.91538194445</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44678</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44816.89569444444</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44637</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>44350</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>44143</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>44655.45373842592</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>44682.75924768519</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>44682.77616898148</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>44623</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>44502</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>44880.68423611111</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>44105</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>44637</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>44735</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>44595</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>44665.65474537037</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>44665.78351851852</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>44533</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44342</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>44642.55565972222</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>44153</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>44763.4182175926</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>44704</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>44543</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>44682.76528935185</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>44523.61635416667</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>44595</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20022,7 +20022,7 @@
         <v>44370.72197916666</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
         <v>44725</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>44744</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>44132</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>44333</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>44466.37496527778</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44076</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44815</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>44376</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44495</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>45713.92623842593</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44735</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44350</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44176</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44637</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44743.59765046297</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44670.4190162037</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>45757.61421296297</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>45435.43123842592</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>45518</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45443</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45621.34425925926</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>44938</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>44769.66039351852</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>45237</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>44284</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21519,7 +21519,7 @@
         <v>44869</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45089</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>44743.47407407407</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>44524</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>44379</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>44888</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>44326.61967592593</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44763.40914351852</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>44643</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>45600.411875</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>44747</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45022</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22203,7 +22203,7 @@
         <v>45639.47385416667</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>44833.40876157407</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45667.49878472222</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44252</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>45485</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>44806.41576388889</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>45208.69671296296</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>45691.41101851852</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>44934</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>44155.69458333333</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44959.74533564815</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45600.47275462963</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>45737.43347222222</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>45772.30436342592</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>45383</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>45223</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>45401.3653125</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>44510.51422453704</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>44799.65013888889</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45111</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44260</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>45749</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>45575</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>45063</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>45075.90817129629</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         <v>44704</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>45587.62565972222</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>45245</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>45245</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>44778.69210648148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45450.64643518518</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>45085.5309375</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44637</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>45625</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>45772.29622685185</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>45054</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45679</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>45664</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>45457</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>44319</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>45019.3959837963</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>45435</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>44750.66068287037</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>44750</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>45735.36873842592</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>45692</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>44272</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>44145</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>44510</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>44938</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>44956</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>44993.66707175926</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>45721.88684027778</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>45058.78607638889</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>44925</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>44098</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>45721.89123842592</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>44777</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>45070</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25616,7 +25616,7 @@
         <v>45418.6968287037</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>45640.57305555556</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>45533</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>45540</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45733.82105324074</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44621</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45273</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>45700</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
         <v>45075</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>44113</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>45706.60130787037</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>44285</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>45631.73952546297</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>45631.74673611111</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>45490.60572916667</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>45730.42851851852</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>44697</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45764.6359837963</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>44778</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>45338</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>44470</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>44953.67443287037</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>45175</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>45254</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>45177</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27061,7 +27061,7 @@
         <v>44456</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
         <v>45414</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>45608</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>45589.68289351852</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>44992</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>45469</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>45600.86128472222</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>44183</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>44841.52804398148</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         <v>45775.41451388889</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>44083</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27698,7 +27698,7 @@
         <v>44693</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>44777</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27812,7 +27812,7 @@
         <v>44474.62141203704</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>45112</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>44704</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>45621.34813657407</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>45723</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>45687.5038425926</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>44251</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28226,7 +28226,7 @@
         <v>44769</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
         <v>45456</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>45104</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>45104</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>44824.36069444445</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>44110</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28573,7 +28573,7 @@
         <v>45386.34175925926</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28630,7 +28630,7 @@
         <v>45644.47878472223</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>45113</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>45113</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>44145</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>45328.46336805556</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>45769</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>45376.54115740741</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>45345.6059837963</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29086,7 +29086,7 @@
         <v>45729.60859953704</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29148,7 +29148,7 @@
         <v>45770</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29205,7 +29205,7 @@
         <v>45636.41572916666</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>44076</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45600.4558912037</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>45376.55484953704</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>44832</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>45128</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29547,7 +29547,7 @@
         <v>45322</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>45455.33037037037</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>45245</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>45348.46300925926</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>45721.40780092592</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44783</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>45728.38409722222</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>45075.90270833333</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>45075.91042824074</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>45075.91265046296</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>45075.92153935185</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>45587</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30241,7 +30241,7 @@
         <v>44895</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30298,7 +30298,7 @@
         <v>45418</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30355,7 +30355,7 @@
         <v>44419</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         <v>44995</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44490.03621527777</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>45427.89121527778</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>45092</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>45092</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30697,7 +30697,7 @@
         <v>45776.47122685185</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30754,7 +30754,7 @@
         <v>45310.40628472222</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>45721</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>44904</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>45776.46369212963</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>44546</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>45610.47414351852</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31096,7 +31096,7 @@
         <v>45411.54768518519</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>45776.62563657408</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>45776.47346064815</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>45316.60306712963</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>45253.63089120371</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45190.55609953704</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>45776.59871527777</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44243.33587962963</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>44817.56120370371</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45561.62141203704</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>45219</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>45638.5987037037</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>44769.66864583334</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>45007</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>45700</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>45735.59287037037</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>45783</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>44380.77346064815</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>45783.66429398148</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32189,7 +32189,7 @@
         <v>45783.48878472222</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32246,7 +32246,7 @@
         <v>45239</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32303,7 +32303,7 @@
         <v>45450.64208333333</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>45450</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32427,7 +32427,7 @@
         <v>45414.58650462963</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>45785.65300925926</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>45223</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>45642.64634259259</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32655,7 +32655,7 @@
         <v>45208</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32712,7 +32712,7 @@
         <v>45208</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>44643</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32826,7 +32826,7 @@
         <v>45408.57707175926</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32883,7 +32883,7 @@
         <v>45831.56521990741</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>45589.6756712963</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32997,7 +32997,7 @@
         <v>45456</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33054,7 +33054,7 @@
         <v>45786.55645833333</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>44708</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>44708.36708333333</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>45020</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>45145.63584490741</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33349,7 +33349,7 @@
         <v>44900</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>45635.88849537037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>44963</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33520,7 +33520,7 @@
         <v>45433.58431712963</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>45019.28847222222</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33634,7 +33634,7 @@
         <v>44882</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>45215</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>44578</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>45482.53388888889</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>45075</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>45075</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>45075.90934027778</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>45075.91148148148</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>45536</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34147,7 +34147,7 @@
         <v>45735</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>44100</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34261,7 +34261,7 @@
         <v>45771</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34318,7 +34318,7 @@
         <v>45709.39361111111</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>45219.56697916667</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34437,7 +34437,7 @@
         <v>44596</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34494,7 +34494,7 @@
         <v>44596.66335648148</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>45531</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>45532</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>45537</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>44834.38636574074</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>44867</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>45187</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45385.38146990741</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>45572.57828703704</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>45772.71221064815</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>45208.58004629629</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>45460.44347222222</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>45549</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>45579</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>45352.74090277778</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>45552.52827546297</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35411,7 +35411,7 @@
         <v>44953.69298611111</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>44778.92797453704</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>44816</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>45183</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>45293</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>45760.91174768518</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>44325</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>44931.65626157408</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>44771</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35929,7 +35929,7 @@
         <v>45708.61761574074</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>44771</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45485.60261574074</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>45755.36583333334</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44952.57989583333</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44790</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>44879.70518518519</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36338,7 +36338,7 @@
         <v>45706.40086805556</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36400,7 +36400,7 @@
         <v>44687</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>45490.45342592592</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>45293.37263888889</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>45293</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>44775</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>44901</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>45709.40231481481</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>44179</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45272.64479166667</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>45272</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44797</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37042,7 +37042,7 @@
         <v>45475.61896990741</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>45162</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>44490.02482638889</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>44760</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37275,7 +37275,7 @@
         <v>45586</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>44132</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37389,7 +37389,7 @@
         <v>44581</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37446,7 +37446,7 @@
         <v>44321</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37503,7 +37503,7 @@
         <v>44648</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37560,7 +37560,7 @@
         <v>45610.39271990741</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37617,7 +37617,7 @@
         <v>45435.43466435185</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37674,7 +37674,7 @@
         <v>45435.43820601852</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37731,7 +37731,7 @@
         <v>45362.62811342593</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37788,7 +37788,7 @@
         <v>45518</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>45394.58778935186</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45147.65222222222</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>45147.65311342593</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>44708.67822916667</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45640.58716435185</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45436</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>44139.54078703704</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>45293</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45394.72869212963</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
         <v>45740.47550925926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38425,7 +38425,7 @@
         <v>45740.47724537037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>45712</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44611</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45085</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>45786</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45385.37922453704</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>44732</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>44592</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45713</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>45729.72851851852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>45729.7271875</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44813</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>44953.70481481482</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>45617.58453703704</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>45797.58350694444</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>45797.58399305555</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>45735</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>45547</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>45576</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>45065.55917824074</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>45068.51783564815</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>44644</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>45798.66767361111</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39756,7 +39756,7 @@
         <v>45798.66104166667</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>44746.58530092592</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39870,7 +39870,7 @@
         <v>45139</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>45218</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39984,7 +39984,7 @@
         <v>45798</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>44111.44373842593</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45469</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>44945.67409722223</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>45730.69502314815</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>45155</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40326,7 +40326,7 @@
         <v>44687</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>44649</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40440,7 +40440,7 @@
         <v>44732</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40497,7 +40497,7 @@
         <v>44162</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40559,7 +40559,7 @@
         <v>44803</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>44803</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>45483.57244212963</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>45414.65855324074</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40787,7 +40787,7 @@
         <v>44599.58428240741</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>45412.4104050926</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40901,7 +40901,7 @@
         <v>45701.44372685185</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40958,7 +40958,7 @@
         <v>44778</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41015,7 +41015,7 @@
         <v>45726.48152777777</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41072,7 +41072,7 @@
         <v>45205</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45147.65407407407</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41186,7 +41186,7 @@
         <v>45191</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>44398</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>44767.60601851852</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>44617</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45478.42887731481</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>45670.3079050926</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45694.68207175926</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>44867.62090277778</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>45104</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41714,7 +41714,7 @@
         <v>45799</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41771,7 +41771,7 @@
         <v>45127.69371527778</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>45740.47055555556</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41890,7 +41890,7 @@
         <v>45033</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>45084.54459490741</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>45798.67082175926</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>45840.70885416667</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         <v>45586</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>45121</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>45442.45686342593</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>44133</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>45800</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>45803.69228009259</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>45800</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>44525</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>45800</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45549</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>44540</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42750,7 +42750,7 @@
         <v>45803.4675</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42807,7 +42807,7 @@
         <v>45800</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42864,7 +42864,7 @@
         <v>44556</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42921,7 +42921,7 @@
         <v>45803.66587962963</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>45559.54706018518</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43035,7 +43035,7 @@
         <v>45800</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>45800</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43154,7 +43154,7 @@
         <v>44813</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43211,7 +43211,7 @@
         <v>45847.37414351852</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>45468.45541666666</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>45468.45747685185</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>44809</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45405.57927083333</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>45726.48377314815</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>45224</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>44858</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>44452</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>45139.51457175926</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>45804.74479166666</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>44266</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45236.46369212963</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>44525</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45092</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>44483</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45463.80486111111</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>44143</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45623.62563657408</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44304,7 +44304,7 @@
         <v>45707.84997685185</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44361,7 +44361,7 @@
         <v>44949</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44418,7 +44418,7 @@
         <v>44949</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>45636.38974537037</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44532,7 +44532,7 @@
         <v>45146</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>45810.45633101852</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44651,7 +44651,7 @@
         <v>44272</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44708,7 +44708,7 @@
         <v>45852.58030092593</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>44698</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>45468.45628472222</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>45063</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>45453</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45810.45236111111</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45810.45263888889</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>44218</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>45104</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>45790.81410879629</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>44395</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45345,7 +45345,7 @@
         <v>45243.45289351852</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>45811.60451388889</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>45810.5333912037</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45757.62482638889</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45578,7 +45578,7 @@
         <v>45525</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45635,7 +45635,7 @@
         <v>44691.5652662037</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>45177.61498842593</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>44146</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45356.47784722222</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>44816</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>44375</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>45107.42538194444</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45075.91362268518</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>45075.91971064815</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45708</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46210,7 +46210,7 @@
         <v>44584.91001157407</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46267,7 +46267,7 @@
         <v>45730.35026620371</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>45757.60658564815</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46381,7 +46381,7 @@
         <v>45086.3629050926</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45534.38240740741</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45810.42393518519</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46557,7 +46557,7 @@
         <v>45855.69387731481</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45855.57033564815</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45203.63303240741</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46738,7 +46738,7 @@
         <v>45813.4709375</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46800,7 +46800,7 @@
         <v>45813.63650462963</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46857,7 +46857,7 @@
         <v>45531</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46914,7 +46914,7 @@
         <v>45670.65921296296</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46971,7 +46971,7 @@
         <v>45271</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47028,7 +47028,7 @@
         <v>45813.6799537037</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>45855.68413194444</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45813.66961805556</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45705.66126157407</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>44629</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>44764</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45817.2565625</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>45817.30329861111</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>45817.31085648148</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47556,7 +47556,7 @@
         <v>45817.31708333334</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47613,7 +47613,7 @@
         <v>45817.31986111111</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47670,7 +47670,7 @@
         <v>45817.33503472222</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47732,7 +47732,7 @@
         <v>45238</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47789,7 +47789,7 @@
         <v>45261</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45679</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>45629.65143518519</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45208</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45735</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45817.25471064815</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>45524</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>45245</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>45454.65774305556</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>44580</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         <v>44956</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>45817.291875</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48478,7 +48478,7 @@
         <v>45817.32538194444</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>44315</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48597,7 +48597,7 @@
         <v>45203.83891203703</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>45817.34083333334</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48711,7 +48711,7 @@
         <v>44124</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>45218.65849537037</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48825,7 +48825,7 @@
         <v>44470.72987268519</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
         <v>44714.56040509259</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45747.63471064815</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48996,7 +48996,7 @@
         <v>45859</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>45859</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>45376.55638888889</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49172,7 +49172,7 @@
         <v>44845.48064814815</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49229,7 +49229,7 @@
         <v>44472</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49286,7 +49286,7 @@
         <v>45084.57695601852</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49348,7 +49348,7 @@
         <v>45208.70996527778</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49405,7 +49405,7 @@
         <v>45530</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49462,7 +49462,7 @@
         <v>44937</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49519,7 +49519,7 @@
         <v>45706.61178240741</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45188.41637731482</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49643,7 +49643,7 @@
         <v>45840</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49700,7 +49700,7 @@
         <v>45356.4722800926</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49757,7 +49757,7 @@
         <v>44785</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49819,7 +49819,7 @@
         <v>44105</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49876,7 +49876,7 @@
         <v>45231.34144675926</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>44705.60626157407</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49990,7 +49990,7 @@
         <v>44866.63775462963</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>45082</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45082.68922453704</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>45260.43225694444</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45260.4333449074</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50275,7 +50275,7 @@
         <v>45617.57439814815</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50332,7 +50332,7 @@
         <v>45063.35880787037</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50389,7 +50389,7 @@
         <v>45721.65858796296</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50446,7 +50446,7 @@
         <v>45581</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50503,7 +50503,7 @@
         <v>45824.37275462963</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>45055.43509259259</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>45614.39627314815</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45548.72306712963</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>44714.92253472222</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45687</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50855,7 +50855,7 @@
         <v>45341.39853009259</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50912,7 +50912,7 @@
         <v>45554.55707175926</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>45617.62358796296</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51026,7 +51026,7 @@
         <v>45075</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51083,7 +51083,7 @@
         <v>44181</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         <v>45260</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>45202</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51259,7 +51259,7 @@
         <v>44722</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51316,7 +51316,7 @@
         <v>45254</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51373,7 +51373,7 @@
         <v>45868.62267361111</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51430,7 +51430,7 @@
         <v>45253.55641203704</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>44851</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51544,7 +51544,7 @@
         <v>44124</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         <v>45254.41509259259</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>45042.74291666667</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51720,7 +51720,7 @@
         <v>44585</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51782,7 +51782,7 @@
         <v>45469</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>45385.36243055556</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51896,7 +51896,7 @@
         <v>45730.69143518519</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51953,7 +51953,7 @@
         <v>44962</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52010,7 +52010,7 @@
         <v>45831.65079861111</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52072,7 +52072,7 @@
         <v>44624.59434027778</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52129,7 +52129,7 @@
         <v>45442</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52186,7 +52186,7 @@
         <v>45446.4287962963</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52243,7 +52243,7 @@
         <v>45831.54618055555</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52300,7 +52300,7 @@
         <v>45202.65660879629</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52357,7 +52357,7 @@
         <v>45075</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52414,7 +52414,7 @@
         <v>45728.38924768518</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52471,7 +52471,7 @@
         <v>44743.59331018518</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52533,7 +52533,7 @@
         <v>45397</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52590,7 +52590,7 @@
         <v>44732</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>45831.4844212963</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>45831.51659722222</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52761,7 +52761,7 @@
         <v>44390</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52818,7 +52818,7 @@
         <v>45054.54091435186</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52875,7 +52875,7 @@
         <v>45054</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52932,7 +52932,7 @@
         <v>45639.45166666667</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52989,7 +52989,7 @@
         <v>45740.47288194444</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -53046,7 +53046,7 @@
         <v>44925</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -53103,7 +53103,7 @@
         <v>44760</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -53160,7 +53160,7 @@
         <v>44760</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53217,7 +53217,7 @@
         <v>45145.51</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53274,7 +53274,7 @@
         <v>44217.40149305556</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53331,7 +53331,7 @@
         <v>44362.37172453704</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53393,7 +53393,7 @@
         <v>45832.66385416667</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53450,7 +53450,7 @@
         <v>45644.90815972222</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53507,7 +53507,7 @@
         <v>44813.59915509259</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53564,7 +53564,7 @@
         <v>45834.65538194445</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53621,7 +53621,7 @@
         <v>45835.4928125</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53683,7 +53683,7 @@
         <v>44621</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53740,7 +53740,7 @@
         <v>44656</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53802,7 +53802,7 @@
         <v>45834.6447337963</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53859,7 +53859,7 @@
         <v>45699.46283564815</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53916,7 +53916,7 @@
         <v>44690</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53973,7 +53973,7 @@
         <v>45183</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -54030,7 +54030,7 @@
         <v>45089</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -54087,7 +54087,7 @@
         <v>44840</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -54144,7 +54144,7 @@
         <v>44819</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -54201,7 +54201,7 @@
         <v>44908.77368055555</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54258,7 +54258,7 @@
         <v>44719</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54315,7 +54315,7 @@
         <v>45835</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54372,7 +54372,7 @@
         <v>44698</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54429,7 +54429,7 @@
         <v>45168.44489583333</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54491,7 +54491,7 @@
         <v>44960.60469907407</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54548,7 +54548,7 @@
         <v>44528.91494212963</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54605,7 +54605,7 @@
         <v>45519</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54662,7 +54662,7 @@
         <v>45170</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54719,7 +54719,7 @@
         <v>44549</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54776,7 +54776,7 @@
         <v>45259</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54833,7 +54833,7 @@
         <v>45601.56726851852</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54890,7 +54890,7 @@
         <v>44266</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54947,7 +54947,7 @@
         <v>44266</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -55004,7 +55004,7 @@
         <v>44516</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -55066,7 +55066,7 @@
         <v>44516.40674768519</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -55128,7 +55128,7 @@
         <v>45448.56746527777</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -55185,7 +55185,7 @@
         <v>45051.455</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55242,7 +55242,7 @@
         <v>44782</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55299,7 +55299,7 @@
         <v>44753</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55356,7 +55356,7 @@
         <v>44306</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55418,7 +55418,7 @@
         <v>44680</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55475,7 +55475,7 @@
         <v>44673</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55532,7 +55532,7 @@
         <v>44637</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55589,7 +55589,7 @@
         <v>45835.68076388889</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55646,7 +55646,7 @@
         <v>45245</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55703,7 +55703,7 @@
         <v>44977</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55760,7 +55760,7 @@
         <v>45834</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55817,7 +55817,7 @@
         <v>44902</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55874,7 +55874,7 @@
         <v>45876.45253472222</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>44461</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55998,7 +55998,7 @@
         <v>45835.46034722222</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>45743.44953703704</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         <v>44795</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         <v>45518</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -56231,7 +56231,7 @@
         <v>44670</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56288,7 +56288,7 @@
         <v>45621.35712962963</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56350,7 +56350,7 @@
         <v>45215</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56407,7 +56407,7 @@
         <v>45089</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56464,7 +56464,7 @@
         <v>45695.57881944445</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56526,7 +56526,7 @@
         <v>45838.43261574074</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56588,7 +56588,7 @@
         <v>45376.55704861111</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56645,7 +56645,7 @@
         <v>45880.46524305556</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56707,7 +56707,7 @@
         <v>45839</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56764,7 +56764,7 @@
         <v>45839.62398148148</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56821,7 +56821,7 @@
         <v>45159</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56878,7 +56878,7 @@
         <v>45638.59979166667</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56940,7 +56940,7 @@
         <v>45837.93730324074</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56997,7 +56997,7 @@
         <v>45837</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -57054,7 +57054,7 @@
         <v>45837.94081018519</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -57111,7 +57111,7 @@
         <v>45880.46189814815</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>45880.46372685185</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -57235,7 +57235,7 @@
         <v>45685.44592592592</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57292,7 +57292,7 @@
         <v>45853</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57349,7 +57349,7 @@
         <v>45686.65545138889</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57406,7 +57406,7 @@
         <v>45522.44414351852</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57463,7 +57463,7 @@
         <v>45715</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57525,7 +57525,7 @@
         <v>45357</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57582,7 +57582,7 @@
         <v>45147</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57639,7 +57639,7 @@
         <v>44923.90159722222</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57696,7 +57696,7 @@
         <v>45841.74596064815</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57753,7 +57753,7 @@
         <v>45840.62755787037</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57810,7 +57810,7 @@
         <v>45212</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57867,7 +57867,7 @@
         <v>45119.57728009259</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57924,7 +57924,7 @@
         <v>45841.56996527778</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57981,7 +57981,7 @@
         <v>45668.67446759259</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -58038,7 +58038,7 @@
         <v>44682.78430555556</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -58095,7 +58095,7 @@
         <v>45882.59722222222</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -58152,7 +58152,7 @@
         <v>45840.67829861111</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -58209,7 +58209,7 @@
         <v>45082.69179398148</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58266,7 +58266,7 @@
         <v>45089</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58323,7 +58323,7 @@
         <v>45853</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58380,7 +58380,7 @@
         <v>45155</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58437,7 +58437,7 @@
         <v>45344</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58494,7 +58494,7 @@
         <v>44815.74539351852</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58551,7 +58551,7 @@
         <v>44986.5887962963</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58608,7 +58608,7 @@
         <v>45841.5737962963</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58665,7 +58665,7 @@
         <v>45089</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58722,7 +58722,7 @@
         <v>45841.35611111111</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58779,7 +58779,7 @@
         <v>45630.52866898148</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58836,7 +58836,7 @@
         <v>45842.46885416667</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58893,7 +58893,7 @@
         <v>44511.70518518519</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58950,7 +58950,7 @@
         <v>44459</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -59012,7 +59012,7 @@
         <v>45469</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -59069,7 +59069,7 @@
         <v>45772.3078125</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -59126,7 +59126,7 @@
         <v>45772.51127314815</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59183,7 +59183,7 @@
         <v>45844.62609953704</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59240,7 +59240,7 @@
         <v>45845</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59297,7 +59297,7 @@
         <v>45092</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>44694.57413194444</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45844.91234953704</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59473,7 +59473,7 @@
         <v>45118</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59535,7 +59535,7 @@
         <v>44903</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45310</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59649,7 +59649,7 @@
         <v>45391.3395949074</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59706,7 +59706,7 @@
         <v>44749.55258101852</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59763,7 +59763,7 @@
         <v>45757.65178240741</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59820,7 +59820,7 @@
         <v>44866.49827546296</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59877,7 +59877,7 @@
         <v>44868.45741898148</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59934,7 +59934,7 @@
         <v>45884.48696759259</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59991,7 +59991,7 @@
         <v>44495.5893287037</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -60048,7 +60048,7 @@
         <v>45152</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -60105,7 +60105,7 @@
         <v>44963</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60162,7 +60162,7 @@
         <v>45581</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60219,7 +60219,7 @@
         <v>45245</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60276,7 +60276,7 @@
         <v>45886.72702546296</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60333,7 +60333,7 @@
         <v>45056</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60390,7 +60390,7 @@
         <v>45729.71065972222</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60452,7 +60452,7 @@
         <v>45069</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60529,7 +60529,7 @@
         <v>44816</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60586,7 +60586,7 @@
         <v>45888.61357638889</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60643,7 +60643,7 @@
         <v>45693</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60700,7 +60700,7 @@
         <v>45376.64532407407</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60757,7 +60757,7 @@
         <v>45680.42665509259</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60814,7 +60814,7 @@
         <v>44743.59504629629</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60876,7 +60876,7 @@
         <v>45888.60714120371</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60933,7 +60933,7 @@
         <v>45635.44788194444</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60990,7 +60990,7 @@
         <v>45847.48436342592</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -61047,7 +61047,7 @@
         <v>44326</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -61104,7 +61104,7 @@
         <v>45558.46283564815</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -61161,7 +61161,7 @@
         <v>45890.56001157407</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -61218,7 +61218,7 @@
         <v>44974</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -61275,7 +61275,7 @@
         <v>45748</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -61332,7 +61332,7 @@
         <v>45460.45523148148</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61389,7 +61389,7 @@
         <v>45282</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61446,7 +61446,7 @@
         <v>45890.68083333333</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61503,7 +61503,7 @@
         <v>44956.65920138889</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61560,7 +61560,7 @@
         <v>44956</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61617,7 +61617,7 @@
         <v>45735.36594907408</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61674,7 +61674,7 @@
         <v>45609.70778935185</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61736,7 +61736,7 @@
         <v>45609.85146990741</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61793,7 +61793,7 @@
         <v>45048</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61850,7 +61850,7 @@
         <v>44152</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61912,7 +61912,7 @@
         <v>45223</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61969,7 +61969,7 @@
         <v>44684</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -62026,7 +62026,7 @@
         <v>44325</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -62083,7 +62083,7 @@
         <v>45253.61146990741</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -62140,7 +62140,7 @@
         <v>45257</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -62197,7 +62197,7 @@
         <v>44985</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -62254,7 +62254,7 @@
         <v>44980</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62311,7 +62311,7 @@
         <v>44108</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62368,7 +62368,7 @@
         <v>45640.60240740741</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62425,7 +62425,7 @@
         <v>45370</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62482,7 +62482,7 @@
         <v>45174.68702546296</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62544,7 +62544,7 @@
         <v>45131.666875</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62601,7 +62601,7 @@
         <v>44376.50728009259</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62658,7 +62658,7 @@
         <v>44376</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62715,7 +62715,7 @@
         <v>45022</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62772,7 +62772,7 @@
         <v>44743.64592592593</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62834,7 +62834,7 @@
         <v>45183</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62891,7 +62891,7 @@
         <v>45022.61003472222</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62948,7 +62948,7 @@
         <v>44231</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -63010,7 +63010,7 @@
         <v>45232</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -63067,7 +63067,7 @@
         <v>45427.88731481481</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -63124,7 +63124,7 @@
         <v>44854</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -63181,7 +63181,7 @@
         <v>45259</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -63238,7 +63238,7 @@
         <v>44922</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63295,7 +63295,7 @@
         <v>44700.50659722222</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63352,7 +63352,7 @@
         <v>44266</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63409,7 +63409,7 @@
         <v>45169</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63471,7 +63471,7 @@
         <v>45473.94501157408</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63528,7 +63528,7 @@
         <v>44635</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63585,7 +63585,7 @@
         <v>45723</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63647,7 +63647,7 @@
         <v>44743.67418981482</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63709,7 +63709,7 @@
         <v>45075.90703703704</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63766,7 +63766,7 @@
         <v>44097</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63823,7 +63823,7 @@
         <v>45468.45877314815</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63880,7 +63880,7 @@
         <v>45257</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63937,7 +63937,7 @@
         <v>45330.50098379629</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>

--- a/Översikt NORRTÄLJE.xlsx
+++ b/Översikt NORRTÄLJE.xlsx
@@ -567,7 +567,7 @@
         <v>45135</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44757</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44249</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45757</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>44909</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45457</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45226</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45367</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45715</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44949</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45436</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>44263</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>45190</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>44550</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>44467</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45600</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>45586.88145833334</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45688.38224537037</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>45638</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>44846</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>44858</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>44447</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>45400.5958912037</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>44650</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>45800</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>44076</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>45068</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45831.53390046296</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>44544</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>45748.6521875</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44711</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>45783.58123842593</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>45784.32179398148</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44336</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>45722</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>44545</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44839</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>45847.47052083333</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>44300</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>44749</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>44843</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         <v>44279</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         <v>44866</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4850,7 +4850,7 @@
         <v>45611.47233796296</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>45616.54866898148</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>44945</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5115,7 +5115,7 @@
         <v>45821</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>44698</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>44370</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>44489</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>44872</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>44763</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45219</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>44868</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         <v>45226</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>44670</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5995,7 +5995,7 @@
         <v>45723</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45609.37094907407</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>45772.30234953704</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>45446.35888888889</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         <v>45800</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45847.47685185185</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>45772.31609953703</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44573</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>44102</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6793,7 +6793,7 @@
         <v>44564.66387731482</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>44161</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>44363</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>44788.70217592592</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44680</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>45205</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7307,7 +7307,7 @@
         <v>44993</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>45092</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44704</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>44855</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>44489</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>44956</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>45754</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>45784.54878472222</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>45082</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>44620</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>45741.38688657407</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>45687.34177083334</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>44955.71322916666</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>45794.63298611111</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>44695.43527777777</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
         <v>44863</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>45803.62766203703</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>45532</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>45800</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>45146</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>45708</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>45468.45995370371</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>44965</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>45280</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9384,7 +9384,7 @@
         <v>45826.46392361111</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>45225</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45798</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>45081</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>45065</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>45841.5721875</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>44207</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45609.83747685186</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>45888.62712962963</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>44683</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>45450.63958333333</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>45735.54510416667</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>45474</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>44210</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>44209</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>44306</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10684,7 +10684,7 @@
         <v>44540</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>44642</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>44650.8699537037</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>44447</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>44833</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>44284.59546296296</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>44069</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>44330</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>44420</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>44420</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>44097</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>44728.73465277778</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>44777</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44810.85092592592</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44552</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11559,7 +11559,7 @@
         <v>44560</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11616,7 +11616,7 @@
         <v>44470.72148148148</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44634</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>44581.75819444445</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>44771</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>44111.45320601852</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>44477.94327546296</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>44380</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>44524</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44399.43450231481</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>44516.72827546296</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>44574.42978009259</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>44103</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>44868</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12367,7 +12367,7 @@
         <v>44834</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         <v>44309.47061342592</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12486,7 +12486,7 @@
         <v>44400</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
         <v>44161</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12600,7 +12600,7 @@
         <v>44252</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>44451</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>44858</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>44244</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>44496</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>44626</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>44690</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>44682.79203703703</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13061,7 +13061,7 @@
         <v>44708</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>44642</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>44776</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>44103</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>44746</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>44176</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>44214</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>44306</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>44727</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13579,7 +13579,7 @@
         <v>44543</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13636,7 +13636,7 @@
         <v>44543</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>44845.47585648148</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         <v>44694.57549768518</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>44495</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13864,7 +13864,7 @@
         <v>44749.61980324074</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>44882.44732638889</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>44882</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>44224</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>44545.4189699074</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>44279</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14206,7 +14206,7 @@
         <v>44314</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>44300</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>44722</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14382,7 +14382,7 @@
         <v>44742</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>44806.34577546296</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>44756.40881944444</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>44294</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>44124</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>44330</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>44330</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14781,7 +14781,7 @@
         <v>44511.69885416667</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14838,7 +14838,7 @@
         <v>44510</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>44447</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14952,7 +14952,7 @@
         <v>44391.5580787037</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15009,7 +15009,7 @@
         <v>44435</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15066,7 +15066,7 @@
         <v>44067</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>44867</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15180,7 +15180,7 @@
         <v>44571</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>44453</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>44511</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>44495</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44683</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>44201</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15522,7 +15522,7 @@
         <v>44201</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>44375</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>44539</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>44516.5275462963</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>44496</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15807,7 +15807,7 @@
         <v>44299</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>44414.81494212963</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>44380</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>44594.75950231482</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>44826</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>44326</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
         <v>44607</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         <v>44425</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>44425</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>44363.5784375</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>44712.83118055556</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>44309</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44769.62320601852</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>44575.52831018518</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>44845.47672453704</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>44251.43971064815</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>44270</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16786,7 +16786,7 @@
         <v>44270</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>44698</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>44397</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>44543</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>44543</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         <v>44526</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>44572</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>44650.92714120371</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>44760</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>44609</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>44817.70516203704</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17418,7 +17418,7 @@
         <v>44230</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
         <v>44230</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17532,7 +17532,7 @@
         <v>44477</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>44545</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>44545</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>44725.49491898148</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>44427</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>44868</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>44251</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>44621</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>44496.77542824074</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>44580</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>44300</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44665.66407407408</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>44658</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44777</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>44100</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>44584.91538194445</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44678</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>44816.89569444444</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18592,7 +18592,7 @@
         <v>44637</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>44350</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>44143</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>44655.45373842592</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>44682.75924768519</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18877,7 +18877,7 @@
         <v>44682.77616898148</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>44623</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>44502</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>44880.68423611111</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>44105</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>44637</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19219,7 +19219,7 @@
         <v>44735</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>44595</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>44665.65474537037</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>44665.78351851852</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>44533</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>44342</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19566,7 +19566,7 @@
         <v>44642.55565972222</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>44153</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>44763.4182175926</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>44704</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>44543</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>44682.76528935185</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>44523.61635416667</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>44595</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20022,7 +20022,7 @@
         <v>44370.72197916666</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
         <v>44725</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>44744</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>44132</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>44333</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>44466.37496527778</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>44076</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>44815</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>44376</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>44495</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>45713.92623842593</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20654,7 +20654,7 @@
         <v>44735</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20711,7 +20711,7 @@
         <v>44350</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20768,7 +20768,7 @@
         <v>44176</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44637</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>44743.59765046297</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44670.4190162037</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21001,7 +21001,7 @@
         <v>45757.61421296297</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>45435.43123842592</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>45518</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>45443</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45621.34425925926</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>44938</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>44769.66039351852</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>45237</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>44284</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21519,7 +21519,7 @@
         <v>44869</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45089</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>44743.47407407407</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>44524</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>44379</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>44888</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>44326.61967592593</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44763.40914351852</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>44643</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>45600.411875</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>44747</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45022</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22203,7 +22203,7 @@
         <v>45639.47385416667</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>44833.40876157407</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45667.49878472222</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44252</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>45485</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>44806.41576388889</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>45208.69671296296</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>45691.41101851852</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>44934</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>44155.69458333333</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44959.74533564815</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22830,7 +22830,7 @@
         <v>45600.47275462963</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>45737.43347222222</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>45772.30436342592</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>45383</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>45223</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>45401.3653125</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>44510.51422453704</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>44799.65013888889</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45111</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44260</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23415,7 +23415,7 @@
         <v>45749</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>45575</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>45063</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>45075.90817129629</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         <v>44704</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>45587.62565972222</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>45245</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>45245</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>44778.69210648148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45450.64643518518</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23995,7 +23995,7 @@
         <v>45085.5309375</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24057,7 +24057,7 @@
         <v>44637</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>45625</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24176,7 +24176,7 @@
         <v>45772.29622685185</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24233,7 +24233,7 @@
         <v>45054</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45679</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>45664</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>45457</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>44319</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>45019.3959837963</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>45435</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>44750.66068287037</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>44750</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>45735.36873842592</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>45692</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>44272</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>44145</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24979,7 +24979,7 @@
         <v>44510</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>44938</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25098,7 +25098,7 @@
         <v>44956</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>44993.66707175926</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>45721.88684027778</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>45058.78607638889</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>44925</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>44098</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>45721.89123842592</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>44777</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>45070</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25616,7 +25616,7 @@
         <v>45418.6968287037</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>45640.57305555556</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>45533</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>45540</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45733.82105324074</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>44621</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45273</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>45700</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26082,7 +26082,7 @@
         <v>45075</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26139,7 +26139,7 @@
         <v>44113</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>45706.60130787037</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>44285</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26315,7 +26315,7 @@
         <v>45631.73952546297</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>45631.74673611111</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>45490.60572916667</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>45730.42851851852</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>44697</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45764.6359837963</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>44778</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>45338</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>44470</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>44953.67443287037</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>45175</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26947,7 +26947,7 @@
         <v>45254</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27004,7 +27004,7 @@
         <v>45177</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27061,7 +27061,7 @@
         <v>44456</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27118,7 +27118,7 @@
         <v>45414</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>45608</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27232,7 +27232,7 @@
         <v>45589.68289351852</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>44992</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>45469</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>45600.86128472222</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>44183</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>44841.52804398148</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         <v>45775.41451388889</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>44083</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27698,7 +27698,7 @@
         <v>44693</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27755,7 +27755,7 @@
         <v>44777</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27812,7 +27812,7 @@
         <v>44474.62141203704</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>45112</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>44704</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>45621.34813657407</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>45723</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28107,7 +28107,7 @@
         <v>45687.5038425926</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>44251</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28226,7 +28226,7 @@
         <v>44769</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
         <v>45456</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>45104</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>45104</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>44824.36069444445</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28511,7 +28511,7 @@
         <v>44110</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28573,7 +28573,7 @@
         <v>45386.34175925926</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28630,7 +28630,7 @@
         <v>45644.47878472223</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>45113</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>45113</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>44145</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>45328.46336805556</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>45769</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>45376.54115740741</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29029,7 +29029,7 @@
         <v>45345.6059837963</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29086,7 +29086,7 @@
         <v>45729.60859953704</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29148,7 +29148,7 @@
         <v>45770</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29205,7 +29205,7 @@
         <v>45636.41572916666</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>44076</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45600.4558912037</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>45376.55484953704</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>44832</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>45128</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29547,7 +29547,7 @@
         <v>45322</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29604,7 +29604,7 @@
         <v>45455.33037037037</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>45245</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>45348.46300925926</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>45721.40780092592</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>44783</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>45728.38409722222</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>45075.90270833333</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>45075.91042824074</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>45075.91265046296</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>45075.92153935185</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>45587</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30241,7 +30241,7 @@
         <v>44895</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30298,7 +30298,7 @@
         <v>45418</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30355,7 +30355,7 @@
         <v>44419</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30412,7 +30412,7 @@
         <v>44995</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>44490.03621527777</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>45427.89121527778</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>45092</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>45092</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30697,7 +30697,7 @@
         <v>45776.47122685185</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30754,7 +30754,7 @@
         <v>45310.40628472222</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30811,7 +30811,7 @@
         <v>45721</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30868,7 +30868,7 @@
         <v>44904</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30925,7 +30925,7 @@
         <v>45776.46369212963</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         <v>44546</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>45610.47414351852</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31096,7 +31096,7 @@
         <v>45411.54768518519</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31158,7 +31158,7 @@
         <v>45776.62563657408</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>45776.47346064815</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>45316.60306712963</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>45253.63089120371</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45190.55609953704</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>45776.59871527777</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44243.33587962963</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>44817.56120370371</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45561.62141203704</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>45219</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>45638.5987037037</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>44769.66864583334</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>45007</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>45700</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>45735.59287037037</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>45783</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>44380.77346064815</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>45783.66429398148</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32189,7 +32189,7 @@
         <v>45783.48878472222</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32246,7 +32246,7 @@
         <v>45239</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32303,7 +32303,7 @@
         <v>45450.64208333333</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32365,7 +32365,7 @@
         <v>45450</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32427,7 +32427,7 @@
         <v>45414.58650462963</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>45785.65300925926</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>45223</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>45642.64634259259</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32655,7 +32655,7 @@
         <v>45208</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32712,7 +32712,7 @@
         <v>45208</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>44643</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32826,7 +32826,7 @@
         <v>45408.57707175926</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32883,7 +32883,7 @@
         <v>45831.56521990741</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>45589.6756712963</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32997,7 +32997,7 @@
         <v>45456</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33054,7 +33054,7 @@
         <v>45786.55645833333</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33116,7 +33116,7 @@
         <v>44708</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33173,7 +33173,7 @@
         <v>44708.36708333333</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>45020</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>45145.63584490741</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33349,7 +33349,7 @@
         <v>44900</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>45635.88849537037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>44963</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33520,7 +33520,7 @@
         <v>45433.58431712963</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>45019.28847222222</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33634,7 +33634,7 @@
         <v>44882</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>45215</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33748,7 +33748,7 @@
         <v>44578</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>45482.53388888889</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>45075</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>45075</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>45075.90934027778</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>45075.91148148148</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>45536</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34147,7 +34147,7 @@
         <v>45735</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>44100</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34261,7 +34261,7 @@
         <v>45771</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34318,7 +34318,7 @@
         <v>45709.39361111111</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>45219.56697916667</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34437,7 +34437,7 @@
         <v>44596</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34494,7 +34494,7 @@
         <v>44596.66335648148</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>45531</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>45532</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34670,7 +34670,7 @@
         <v>45537</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34727,7 +34727,7 @@
         <v>44834.38636574074</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34784,7 +34784,7 @@
         <v>44867</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>45187</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>45385.38146990741</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>45572.57828703704</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>45772.71221064815</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>45208.58004629629</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35126,7 +35126,7 @@
         <v>45460.44347222222</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35183,7 +35183,7 @@
         <v>45549</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35240,7 +35240,7 @@
         <v>45579</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>45352.74090277778</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>45552.52827546297</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35411,7 +35411,7 @@
         <v>44953.69298611111</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>44778.92797453704</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>44816</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>45183</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>45293</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>45760.91174768518</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>44325</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35815,7 +35815,7 @@
         <v>44931.65626157408</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>44771</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35929,7 +35929,7 @@
         <v>45708.61761574074</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -35986,7 +35986,7 @@
         <v>44771</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36048,7 +36048,7 @@
         <v>45485.60261574074</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>45755.36583333334</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>44952.57989583333</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>44790</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>44879.70518518519</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36338,7 +36338,7 @@
         <v>45706.40086805556</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36400,7 +36400,7 @@
         <v>44687</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>45490.45342592592</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>45293.37263888889</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36581,7 +36581,7 @@
         <v>45293</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36638,7 +36638,7 @@
         <v>44775</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36695,7 +36695,7 @@
         <v>44901</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36752,7 +36752,7 @@
         <v>45709.40231481481</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>44179</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>45272.64479166667</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36928,7 +36928,7 @@
         <v>45272</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44797</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37042,7 +37042,7 @@
         <v>45475.61896990741</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>45162</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37161,7 +37161,7 @@
         <v>44490.02482638889</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37218,7 +37218,7 @@
         <v>44760</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37275,7 +37275,7 @@
         <v>45586</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>44132</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37389,7 +37389,7 @@
         <v>44581</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37446,7 +37446,7 @@
         <v>44321</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37503,7 +37503,7 @@
         <v>44648</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37560,7 +37560,7 @@
         <v>45610.39271990741</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37617,7 +37617,7 @@
         <v>45435.43466435185</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37674,7 +37674,7 @@
         <v>45435.43820601852</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37731,7 +37731,7 @@
         <v>45362.62811342593</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37788,7 +37788,7 @@
         <v>45518</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>45394.58778935186</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45147.65222222222</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>45147.65311342593</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>44708.67822916667</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38078,7 +38078,7 @@
         <v>45640.58716435185</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38135,7 +38135,7 @@
         <v>45436</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38192,7 +38192,7 @@
         <v>44139.54078703704</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>45293</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45394.72869212963</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
         <v>45740.47550925926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38425,7 +38425,7 @@
         <v>45740.47724537037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>45712</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38544,7 +38544,7 @@
         <v>44611</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45085</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>45786</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>45385.37922453704</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>44732</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38829,7 +38829,7 @@
         <v>44592</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38886,7 +38886,7 @@
         <v>45713</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>45729.72851851852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>45729.7271875</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>44813</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>44953.70481481482</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>45617.58453703704</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>45797.58350694444</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39295,7 +39295,7 @@
         <v>45797.58399305555</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>45735</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>45547</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39466,7 +39466,7 @@
         <v>45576</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39523,7 +39523,7 @@
         <v>45065.55917824074</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>45068.51783564815</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39642,7 +39642,7 @@
         <v>44644</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>45798.66767361111</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39756,7 +39756,7 @@
         <v>45798.66104166667</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>44746.58530092592</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39870,7 +39870,7 @@
         <v>45139</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39927,7 +39927,7 @@
         <v>45218</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -39984,7 +39984,7 @@
         <v>45798</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>44111.44373842593</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45469</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>44945.67409722223</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>45730.69502314815</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>45155</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40326,7 +40326,7 @@
         <v>44687</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>44649</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40440,7 +40440,7 @@
         <v>44732</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40497,7 +40497,7 @@
         <v>44162</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40559,7 +40559,7 @@
         <v>44803</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>44803</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>45483.57244212963</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>45414.65855324074</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40787,7 +40787,7 @@
         <v>44599.58428240741</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>45412.4104050926</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40901,7 +40901,7 @@
         <v>45701.44372685185</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -40958,7 +40958,7 @@
         <v>44778</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41015,7 +41015,7 @@
         <v>45726.48152777777</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41072,7 +41072,7 @@
         <v>45205</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41129,7 +41129,7 @@
         <v>45147.65407407407</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41186,7 +41186,7 @@
         <v>45191</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41248,7 +41248,7 @@
         <v>44398</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>44767.60601851852</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41367,7 +41367,7 @@
         <v>44617</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>45478.42887731481</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41481,7 +41481,7 @@
         <v>45670.3079050926</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41538,7 +41538,7 @@
         <v>45694.68207175926</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>44867.62090277778</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>45104</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41714,7 +41714,7 @@
         <v>45799</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41771,7 +41771,7 @@
         <v>45127.69371527778</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>45740.47055555556</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41890,7 +41890,7 @@
         <v>45033</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -41947,7 +41947,7 @@
         <v>45084.54459490741</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42004,7 +42004,7 @@
         <v>45798.67082175926</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>45840.70885416667</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42118,7 +42118,7 @@
         <v>45586</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>45121</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>45442.45686342593</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42289,7 +42289,7 @@
         <v>44133</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>45800</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>45803.69228009259</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42460,7 +42460,7 @@
         <v>45800</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42517,7 +42517,7 @@
         <v>44525</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>45800</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42636,7 +42636,7 @@
         <v>45549</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42693,7 +42693,7 @@
         <v>44540</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42750,7 +42750,7 @@
         <v>45803.4675</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42807,7 +42807,7 @@
         <v>45800</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42864,7 +42864,7 @@
         <v>44556</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42921,7 +42921,7 @@
         <v>45803.66587962963</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>45559.54706018518</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43035,7 +43035,7 @@
         <v>45800</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>45800</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43154,7 +43154,7 @@
         <v>44813</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43211,7 +43211,7 @@
         <v>45847.37414351852</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>45468.45541666666</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>45468.45747685185</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>44809</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45405.57927083333</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>45726.48377314815</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>45224</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>44858</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>44452</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>45139.51457175926</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>45804.74479166666</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43843,7 +43843,7 @@
         <v>44266</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45236.46369212963</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>44525</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>45092</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>44483</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>45463.80486111111</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>44143</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>45623.62563657408</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44304,7 +44304,7 @@
         <v>45707.84997685185</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44361,7 +44361,7 @@
         <v>44949</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44418,7 +44418,7 @@
         <v>44949</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44475,7 +44475,7 @@
         <v>45636.38974537037</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44532,7 +44532,7 @@
         <v>45146</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>45810.45633101852</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44651,7 +44651,7 @@
         <v>44272</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44708,7 +44708,7 @@
         <v>45852.58030092593</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>44698</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44827,7 +44827,7 @@
         <v>45468.45628472222</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44884,7 +44884,7 @@
         <v>45063</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -44941,7 +44941,7 @@
         <v>45453</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -44998,7 +44998,7 @@
         <v>45810.45236111111</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45055,7 +45055,7 @@
         <v>45810.45263888889</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>44218</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>45104</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>45790.81410879629</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>44395</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45345,7 +45345,7 @@
         <v>45243.45289351852</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>45811.60451388889</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45464,7 +45464,7 @@
         <v>45810.5333912037</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>45757.62482638889</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45578,7 +45578,7 @@
         <v>45525</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45635,7 +45635,7 @@
         <v>44691.5652662037</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>45177.61498842593</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45749,7 +45749,7 @@
         <v>44146</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45806,7 +45806,7 @@
         <v>45356.47784722222</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>44816</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -45920,7 +45920,7 @@
         <v>44375</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -45977,7 +45977,7 @@
         <v>45107.42538194444</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>45075.91362268518</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>45075.91971064815</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46148,7 +46148,7 @@
         <v>45708</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46210,7 +46210,7 @@
         <v>44584.91001157407</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46267,7 +46267,7 @@
         <v>45730.35026620371</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46324,7 +46324,7 @@
         <v>45757.60658564815</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46381,7 +46381,7 @@
         <v>45086.3629050926</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46438,7 +46438,7 @@
         <v>45534.38240740741</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45810.42393518519</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46557,7 +46557,7 @@
         <v>45855.69387731481</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46619,7 +46619,7 @@
         <v>45855.57033564815</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45203.63303240741</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46738,7 +46738,7 @@
         <v>45813.4709375</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46800,7 +46800,7 @@
         <v>45813.63650462963</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46857,7 +46857,7 @@
         <v>45531</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46914,7 +46914,7 @@
         <v>45670.65921296296</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -46971,7 +46971,7 @@
         <v>45271</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47028,7 +47028,7 @@
         <v>45813.6799537037</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47085,7 +47085,7 @@
         <v>45855.68413194444</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45813.66961805556</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45705.66126157407</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47266,7 +47266,7 @@
         <v>44629</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>44764</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47385,7 +47385,7 @@
         <v>45817.2565625</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47442,7 +47442,7 @@
         <v>45817.30329861111</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47499,7 +47499,7 @@
         <v>45817.31085648148</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47556,7 +47556,7 @@
         <v>45817.31708333334</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47613,7 +47613,7 @@
         <v>45817.31986111111</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47670,7 +47670,7 @@
         <v>45817.33503472222</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47732,7 +47732,7 @@
         <v>45238</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47789,7 +47789,7 @@
         <v>45261</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>45679</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>45629.65143518519</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45208</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45735</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45817.25471064815</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>45524</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48193,7 +48193,7 @@
         <v>45245</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>45454.65774305556</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>44580</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         <v>44956</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48421,7 +48421,7 @@
         <v>45817.291875</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48478,7 +48478,7 @@
         <v>45817.32538194444</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>44315</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48597,7 +48597,7 @@
         <v>45203.83891203703</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>45817.34083333334</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48711,7 +48711,7 @@
         <v>44124</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48768,7 +48768,7 @@
         <v>45218.65849537037</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48825,7 +48825,7 @@
         <v>44470.72987268519</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48882,7 +48882,7 @@
         <v>44714.56040509259</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -48939,7 +48939,7 @@
         <v>45747.63471064815</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -48996,7 +48996,7 @@
         <v>45859</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49053,7 +49053,7 @@
         <v>45859</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>45376.55638888889</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49172,7 +49172,7 @@
         <v>44845.48064814815</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49229,7 +49229,7 @@
         <v>44472</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49286,7 +49286,7 @@
         <v>45084.57695601852</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49348,7 +49348,7 @@
         <v>45208.70996527778</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49405,7 +49405,7 @@
         <v>45530</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49462,7 +49462,7 @@
         <v>44937</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49519,7 +49519,7 @@
         <v>45706.61178240741</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49581,7 +49581,7 @@
         <v>45188.41637731482</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49643,7 +49643,7 @@
         <v>45840</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49700,7 +49700,7 @@
         <v>45356.4722800926</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49757,7 +49757,7 @@
         <v>44785</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49819,7 +49819,7 @@
         <v>44105</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49876,7 +49876,7 @@
         <v>45231.34144675926</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>44705.60626157407</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -49990,7 +49990,7 @@
         <v>44866.63775462963</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>45082</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45082.68922453704</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>45260.43225694444</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45260.4333449074</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50275,7 +50275,7 @@
         <v>45617.57439814815</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50332,7 +50332,7 @@
         <v>45063.35880787037</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50389,7 +50389,7 @@
         <v>45721.65858796296</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50446,7 +50446,7 @@
         <v>45581</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50503,7 +50503,7 @@
         <v>45824.37275462963</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>45055.43509259259</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>45614.39627314815</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45548.72306712963</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>44714.92253472222</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>45687</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50855,7 +50855,7 @@
         <v>45341.39853009259</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50912,7 +50912,7 @@
         <v>45554.55707175926</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>45617.62358796296</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51026,7 +51026,7 @@
         <v>45075</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51083,7 +51083,7 @@
         <v>44181</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51140,7 +51140,7 @@
         <v>45260</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51197,7 +51197,7 @@
         <v>45202</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51259,7 +51259,7 @@
         <v>44722</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51316,7 +51316,7 @@
         <v>45254</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51373,7 +51373,7 @@
         <v>45868.62267361111</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51430,7 +51430,7 @@
         <v>45253.55641203704</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51487,7 +51487,7 @@
         <v>44851</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51544,7 +51544,7 @@
         <v>44124</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51606,7 +51606,7 @@
         <v>45254.41509259259</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>45042.74291666667</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51720,7 +51720,7 @@
         <v>44585</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51782,7 +51782,7 @@
         <v>45469</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>45385.36243055556</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51896,7 +51896,7 @@
         <v>45730.69143518519</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51953,7 +51953,7 @@
         <v>44962</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52010,7 +52010,7 @@
         <v>45831.65079861111</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52072,7 +52072,7 @@
         <v>44624.59434027778</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52129,7 +52129,7 @@
         <v>45442</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52186,7 +52186,7 @@
         <v>45446.4287962963</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52243,7 +52243,7 @@
         <v>45831.54618055555</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52300,7 +52300,7 @@
         <v>45202.65660879629</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52357,7 +52357,7 @@
         <v>45075</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52414,7 +52414,7 @@
         <v>45728.38924768518</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52471,7 +52471,7 @@
         <v>44743.59331018518</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52533,7 +52533,7 @@
         <v>45397</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52590,7 +52590,7 @@
         <v>44732</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52647,7 +52647,7 @@
         <v>45831.4844212963</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>45831.51659722222</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52761,7 +52761,7 @@
         <v>44390</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52818,7 +52818,7 @@
         <v>45054.54091435186</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52875,7 +52875,7 @@
         <v>45054</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52932,7 +52932,7 @@
         <v>45639.45166666667</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -52989,7 +52989,7 @@
         <v>45740.47288194444</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -53046,7 +53046,7 @@
         <v>44925</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -53103,7 +53103,7 @@
         <v>44760</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -53160,7 +53160,7 @@
         <v>44760</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53217,7 +53217,7 @@
         <v>45145.51</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53274,7 +53274,7 @@
         <v>44217.40149305556</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53331,7 +53331,7 @@
         <v>44362.37172453704</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53393,7 +53393,7 @@
         <v>45832.66385416667</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53450,7 +53450,7 @@
         <v>45644.90815972222</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53507,7 +53507,7 @@
         <v>44813.59915509259</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53564,7 +53564,7 @@
         <v>45834.65538194445</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53621,7 +53621,7 @@
         <v>45835.4928125</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53683,7 +53683,7 @@
         <v>44621</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53740,7 +53740,7 @@
         <v>44656</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53802,7 +53802,7 @@
         <v>45834.6447337963</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53859,7 +53859,7 @@
         <v>45699.46283564815</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53916,7 +53916,7 @@
         <v>44690</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -53973,7 +53973,7 @@
         <v>45183</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -54030,7 +54030,7 @@
         <v>45089</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -54087,7 +54087,7 @@
         <v>44840</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -54144,7 +54144,7 @@
         <v>44819</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -54201,7 +54201,7 @@
         <v>44908.77368055555</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54258,7 +54258,7 @@
         <v>44719</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54315,7 +54315,7 @@
         <v>45835</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54372,7 +54372,7 @@
         <v>44698</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54429,7 +54429,7 @@
         <v>45168.44489583333</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54491,7 +54491,7 @@
         <v>44960.60469907407</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54548,7 +54548,7 @@
         <v>44528.91494212963</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54605,7 +54605,7 @@
         <v>45519</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54662,7 +54662,7 @@
         <v>45170</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54719,7 +54719,7 @@
         <v>44549</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54776,7 +54776,7 @@
         <v>45259</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54833,7 +54833,7 @@
         <v>45601.56726851852</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54890,7 +54890,7 @@
         <v>44266</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -54947,7 +54947,7 @@
         <v>44266</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -55004,7 +55004,7 @@
         <v>44516</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -55066,7 +55066,7 @@
         <v>44516.40674768519</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -55128,7 +55128,7 @@
         <v>45448.56746527777</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -55185,7 +55185,7 @@
         <v>45051.455</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55242,7 +55242,7 @@
         <v>44782</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55299,7 +55299,7 @@
         <v>44753</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55356,7 +55356,7 @@
         <v>44306</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55418,7 +55418,7 @@
         <v>44680</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55475,7 +55475,7 @@
         <v>44673</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55532,7 +55532,7 @@
         <v>44637</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55589,7 +55589,7 @@
         <v>45835.68076388889</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55646,7 +55646,7 @@
         <v>45245</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55703,7 +55703,7 @@
         <v>44977</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55760,7 +55760,7 @@
         <v>45834</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55817,7 +55817,7 @@
         <v>44902</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55874,7 +55874,7 @@
         <v>45876.45253472222</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>44461</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -55998,7 +55998,7 @@
         <v>45835.46034722222</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -56060,7 +56060,7 @@
         <v>45743.44953703704</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         <v>44795</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -56174,7 +56174,7 @@
         <v>45518</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -56231,7 +56231,7 @@
         <v>44670</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56288,7 +56288,7 @@
         <v>45621.35712962963</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56350,7 +56350,7 @@
         <v>45215</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56407,7 +56407,7 @@
         <v>45089</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56464,7 +56464,7 @@
         <v>45695.57881944445</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56526,7 +56526,7 @@
         <v>45838.43261574074</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56588,7 +56588,7 @@
         <v>45376.55704861111</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56645,7 +56645,7 @@
         <v>45880.46524305556</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56707,7 +56707,7 @@
         <v>45839</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56764,7 +56764,7 @@
         <v>45839.62398148148</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56821,7 +56821,7 @@
         <v>45159</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56878,7 +56878,7 @@
         <v>45638.59979166667</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56940,7 +56940,7 @@
         <v>45837.93730324074</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -56997,7 +56997,7 @@
         <v>45837</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -57054,7 +57054,7 @@
         <v>45837.94081018519</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -57111,7 +57111,7 @@
         <v>45880.46189814815</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>45880.46372685185</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -57235,7 +57235,7 @@
         <v>45685.44592592592</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57292,7 +57292,7 @@
         <v>45853</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57349,7 +57349,7 @@
         <v>45686.65545138889</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57406,7 +57406,7 @@
         <v>45522.44414351852</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57463,7 +57463,7 @@
         <v>45715</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57525,7 +57525,7 @@
         <v>45357</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57582,7 +57582,7 @@
         <v>45147</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57639,7 +57639,7 @@
         <v>44923.90159722222</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57696,7 +57696,7 @@
         <v>45841.74596064815</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57753,7 +57753,7 @@
         <v>45840.62755787037</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57810,7 +57810,7 @@
         <v>45212</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57867,7 +57867,7 @@
         <v>45119.57728009259</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57924,7 +57924,7 @@
         <v>45841.56996527778</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -57981,7 +57981,7 @@
         <v>45668.67446759259</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -58038,7 +58038,7 @@
         <v>44682.78430555556</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -58095,7 +58095,7 @@
         <v>45882.59722222222</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -58152,7 +58152,7 @@
         <v>45840.67829861111</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -58209,7 +58209,7 @@
         <v>45082.69179398148</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58266,7 +58266,7 @@
         <v>45089</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58323,7 +58323,7 @@
         <v>45853</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58380,7 +58380,7 @@
         <v>45155</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58437,7 +58437,7 @@
         <v>45344</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58494,7 +58494,7 @@
         <v>44815.74539351852</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58551,7 +58551,7 @@
         <v>44986.5887962963</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58608,7 +58608,7 @@
         <v>45841.5737962963</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58665,7 +58665,7 @@
         <v>45089</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58722,7 +58722,7 @@
         <v>45841.35611111111</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58779,7 +58779,7 @@
         <v>45630.52866898148</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58836,7 +58836,7 @@
         <v>45842.46885416667</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58893,7 +58893,7 @@
         <v>44511.70518518519</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58950,7 +58950,7 @@
         <v>44459</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -59012,7 +59012,7 @@
         <v>45469</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -59069,7 +59069,7 @@
         <v>45772.3078125</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -59126,7 +59126,7 @@
         <v>45772.51127314815</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59183,7 +59183,7 @@
         <v>45844.62609953704</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59240,7 +59240,7 @@
         <v>45845</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59297,7 +59297,7 @@
         <v>45092</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59354,7 +59354,7 @@
         <v>44694.57413194444</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45844.91234953704</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59473,7 +59473,7 @@
         <v>45118</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59535,7 +59535,7 @@
         <v>44903</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45310</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59649,7 +59649,7 @@
         <v>45391.3395949074</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59706,7 +59706,7 @@
         <v>44749.55258101852</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59763,7 +59763,7 @@
         <v>45757.65178240741</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59820,7 +59820,7 @@
         <v>44866.49827546296</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59877,7 +59877,7 @@
         <v>44868.45741898148</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59934,7 +59934,7 @@
         <v>45884.48696759259</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -59991,7 +59991,7 @@
         <v>44495.5893287037</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -60048,7 +60048,7 @@
         <v>45152</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -60105,7 +60105,7 @@
         <v>44963</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60162,7 +60162,7 @@
         <v>45581</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60219,7 +60219,7 @@
         <v>45245</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60276,7 +60276,7 @@
         <v>45886.72702546296</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60333,7 +60333,7 @@
         <v>45056</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60390,7 +60390,7 @@
         <v>45729.71065972222</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60452,7 +60452,7 @@
         <v>45069</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60529,7 +60529,7 @@
         <v>44816</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60586,7 +60586,7 @@
         <v>45888.61357638889</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60643,7 +60643,7 @@
         <v>45693</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60700,7 +60700,7 @@
         <v>45376.64532407407</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60757,7 +60757,7 @@
         <v>45680.42665509259</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60814,7 +60814,7 @@
         <v>44743.59504629629</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60876,7 +60876,7 @@
         <v>45888.60714120371</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60933,7 +60933,7 @@
         <v>45635.44788194444</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -60990,7 +60990,7 @@
         <v>45847.48436342592</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -61047,7 +61047,7 @@
         <v>44326</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -61104,7 +61104,7 @@
         <v>45558.46283564815</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -61161,7 +61161,7 @@
         <v>45890.56001157407</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -61218,7 +61218,7 @@
         <v>44974</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -61275,7 +61275,7 @@
         <v>45748</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -61332,7 +61332,7 @@
         <v>45460.45523148148</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61389,7 +61389,7 @@
         <v>45282</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61446,7 +61446,7 @@
         <v>45890.68083333333</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61503,7 +61503,7 @@
         <v>44956.65920138889</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61560,7 +61560,7 @@
         <v>44956</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61617,7 +61617,7 @@
         <v>45735.36594907408</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61674,7 +61674,7 @@
         <v>45609.70778935185</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61736,7 +61736,7 @@
         <v>45609.85146990741</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61793,7 +61793,7 @@
         <v>45048</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61850,7 +61850,7 @@
         <v>44152</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61912,7 +61912,7 @@
         <v>45223</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -61969,7 +61969,7 @@
         <v>44684</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -62026,7 +62026,7 @@
         <v>44325</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -62083,7 +62083,7 @@
         <v>45253.61146990741</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -62140,7 +62140,7 @@
         <v>45257</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -62197,7 +62197,7 @@
         <v>44985</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -62254,7 +62254,7 @@
         <v>44980</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62311,7 +62311,7 @@
         <v>44108</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62368,7 +62368,7 @@
         <v>45640.60240740741</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62425,7 +62425,7 @@
         <v>45370</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62482,7 +62482,7 @@
         <v>45174.68702546296</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62544,7 +62544,7 @@
         <v>45131.666875</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62601,7 +62601,7 @@
         <v>44376.50728009259</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62658,7 +62658,7 @@
         <v>44376</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62715,7 +62715,7 @@
         <v>45022</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62772,7 +62772,7 @@
         <v>44743.64592592593</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62834,7 +62834,7 @@
         <v>45183</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62891,7 +62891,7 @@
         <v>45022.61003472222</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -62948,7 +62948,7 @@
         <v>44231</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -63010,7 +63010,7 @@
         <v>45232</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -63067,7 +63067,7 @@
         <v>45427.88731481481</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -63124,7 +63124,7 @@
         <v>44854</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -63181,7 +63181,7 @@
         <v>45259</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -63238,7 +63238,7 @@
         <v>44922</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63295,7 +63295,7 @@
         <v>44700.50659722222</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63352,7 +63352,7 @@
         <v>44266</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63409,7 +63409,7 @@
         <v>45169</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63471,7 +63471,7 @@
         <v>45473.94501157408</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63528,7 +63528,7 @@
         <v>44635</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63585,7 +63585,7 @@
         <v>45723</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63647,7 +63647,7 @@
         <v>44743.67418981482</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63709,7 +63709,7 @@
         <v>45075.90703703704</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63766,7 +63766,7 @@
         <v>44097</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63823,7 +63823,7 @@
         <v>45468.45877314815</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63880,7 +63880,7 @@
         <v>45257</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63937,7 +63937,7 @@
         <v>45330.50098379629</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>

--- a/Översikt NORRTÄLJE.xlsx
+++ b/Översikt NORRTÄLJE.xlsx
@@ -567,7 +567,7 @@
         <v>45135</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44757</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44249</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45757</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>44909</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45457</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45226</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45367</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45715</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44949</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45436</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>45190</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44263</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>44550</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>45586.88145833334</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>44467</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>45600</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45638</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45688.38224537037</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>44846</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>44858</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>44447</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>45400.5958912037</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>44650</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>45800</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>45748.6521875</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>45831.53390046296</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>45068</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>44076</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>44544</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44711</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>45784.32179398148</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>45783.58123842593</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44545</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>45722</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>44336</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44839</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>45847.47052083333</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>45898.62723379629</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>44300</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>44749</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>44843</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>44279</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>45616.54866898148</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45611.47233796296</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45821</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>44866</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>44945</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44698</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>45847.47685185185</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>45847.48436342592</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>44370</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>44489</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>45723</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>45219</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>44763</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>45609.37094907407</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>44670</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>45446.35888888889</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>45226</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>45800</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>45772.30234953704</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>44868</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44872</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>44573</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>44102</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>44564.66387731482</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44161</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>44363</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44788.70217592592</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>44680</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>44695.43527777777</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45784.54878472222</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>44855</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44620</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>44956</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>45794.63298611111</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         <v>45800</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>45146</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>45532</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>45803.62766203703</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>44965</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>45687.34177083334</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>45826.46392361111</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>45754</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>44489</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>45798</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>45741.38688657407</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>44704</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>45841.5721875</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>45888.62712962963</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>44207</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>45065</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>44683</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>45468.45995370371</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>45897.56356481482</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>45708</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>45450.63958333333</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>44993</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>44863</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>45474</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>45735.54510416667</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>44955.71322916666</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>45280</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>45081</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>45082</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>45092</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>45609.83747685186</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45225</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>45205</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>44210</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>44209</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>44306</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>44642</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>44540</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>44650.8699537037</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>44447</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>44833</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>44284.59546296296</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>44420</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>44420</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>44330</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11373,7 +11373,7 @@
         <v>44097</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>44728.73465277778</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44777</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>44810.85092592592</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>44552</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44560</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>44470.72148148148</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>44634</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>44581.75819444445</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>44771</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>44111.45320601852</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>44477.94327546296</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44380</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>44524</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>44574.42978009259</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
         <v>44516.72827546296</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>44103</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>44868</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>44309.47061342592</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>44834</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>44400</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>44161</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>44252</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>44451</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>44858</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>44244</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>44496</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>44626</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>44682.79203703703</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>44690</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>44708</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>44642</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>44776</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>44103</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>44176</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>44746</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>44214</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>44306</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
         <v>44727</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>44845.47585648148</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>44543</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>44543</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>44694.57549768518</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>44495</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         <v>44749.61980324074</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>44882.44732638889</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>44882</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>44224</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>44545.4189699074</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
         <v>44314</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>44279</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>44300</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>44722</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>44742</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>44756.40881944444</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>44124</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>44294</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>44806.34577546296</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>44330</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>44330</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         <v>44511.69885416667</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44510</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>44447</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>44391.5580787037</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>44435</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>44867</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>44571</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>44453</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>44511</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>44495</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>44683</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>44201</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>44201</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>44375</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44539</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44516.5275462963</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>44496</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>44414.81494212963</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>44299</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>44380</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>44594.75950231482</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>44363.5784375</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>44712.83118055556</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16144,7 +16144,7 @@
         <v>44769.62320601852</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>44309</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>44251.43971064815</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>44572</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>44698</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>44845.47672453704</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>44397</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44543</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>44543</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>44650.92714120371</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>44270</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>44270</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>44526</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>44760</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>44545</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>44545</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>44609</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>44725.49491898148</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>44427</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>44817.70516203704</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>44230</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>44230</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>44477</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>44621</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>44496.77542824074</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>44580</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>44868</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>44251</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
         <v>44665.66407407408</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
         <v>44777</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>44880.68423611111</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>44637</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>44735</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>44637</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>44300</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44655.45373842592</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>44658</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>44100</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>44584.91538194445</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>44678</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>44350</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>44143</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>44763.4182175926</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>44816.89569444444</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>44682.75924768519</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>44682.77616898148</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>44623</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>44502</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>44132</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>44595</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44466.37496527778</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>44076</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>44105</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>44376</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>44642.55565972222</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>44153</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>44665.65474537037</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>44665.78351851852</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         <v>44735</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44533</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>44176</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>44744</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>44342</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44704</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44333</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44543</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44682.76528935185</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44523.61635416667</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44595</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44370.72197916666</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44725</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44284</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44350</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44826</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>44326</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>44637</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44524</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>44607</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>44425</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>44425</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>44815</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>44379</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>44495</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45203.63303240741</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>44824.36069444445</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>44419</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45772.3078125</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45625</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45208</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44879.70518518519</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>45621.34813657407</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>44231</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>44949</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>45092</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>44833.40876157407</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>44575.52831018518</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>44643</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>45730.35026620371</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>44272</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>45644.47878472223</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>44743.47407407407</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>44949</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>44953.67443287037</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>44266</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>44376</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>45772.51127314815</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45405.57927083333</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45086.3629050926</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>45772.30436342592</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>45253.55641203704</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>45737.43347222222</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>44963</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>45273</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>45075.91362268518</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45075.91971064815</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44315</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>44764</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45051.455</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>45175</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44098</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>45749</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>45705.66126157407</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>45362.62811342593</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44778.92797453704</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>45694.68207175926</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45330.50098379629</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>45084.54459490741</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>45218</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>44882</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>45473.94501157408</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         <v>45356.4722800926</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>45259</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>44285</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>45455.33037037037</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45147.65222222222</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45147.65311342593</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>45147</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45253.63089120371</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>45776.62563657408</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>44840</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>45433.58431712963</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45316.60306712963</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>45776.47346064815</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>45776.46369212963</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>44556</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>45776.59871527777</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24560,7 +24560,7 @@
         <v>45383</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>45435</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>45190.55609953704</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>45776.47122685185</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>44705.60626157407</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>44895</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>45397</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>44470</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44621</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>45391.3395949074</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>45450.64208333333</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>45450</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>44868.45741898148</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45755.36583333334</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45223</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44272</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>45239</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45485</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25596,7 +25596,7 @@
         <v>44845.48064814815</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>45783</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>45558.46283564815</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>45454.65774305556</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>45104</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>45104</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>45783.66429398148</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>45783.48878472222</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>45769</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45385.38146990741</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26166,7 +26166,7 @@
         <v>44809</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>45202</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>45549</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26342,7 +26342,7 @@
         <v>45376.64532407407</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26399,7 +26399,7 @@
         <v>45187</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>45735</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>45075.90270833333</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>45075.91042824074</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>45075.91265046296</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>45075.92153935185</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>44962</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45709.39361111111</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45089</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>44510</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>45131.666875</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>45576</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44866.63775462963</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>44105</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>45448.56746527777</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>45257</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         <v>45572.57828703704</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27383,7 +27383,7 @@
         <v>45418.6968287037</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>44362.37172453704</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>45460.44347222222</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>45418</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>45785.65300925926</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>45063.35880787037</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>44956</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>45385.36243055556</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>44472</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>45537</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>45579</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>45485.60261574074</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>45119.57728009259</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45536</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>45463.80486111111</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>45831.56521990741</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>45457</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45468.45628472222</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>44076</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45170</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>45352.74090277778</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>44525</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>44578</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>44546</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28761,7 +28761,7 @@
         <v>44516</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>44516.40674768519</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>45468.45541666666</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>45468.45747685185</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28999,7 +28999,7 @@
         <v>45610.39271990741</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>45408.57707175926</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29113,7 +29113,7 @@
         <v>44769.66039351852</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>45786.55645833333</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>44470.72987268519</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>44834.38636574074</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>44113</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>45635.88849537037</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>45271</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>45642.64634259259</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29574,7 +29574,7 @@
         <v>45260</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>44637</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29693,7 +29693,7 @@
         <v>45524</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>44325</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>44461</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>45443</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>45245</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>45715</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30045,7 +30045,7 @@
         <v>44108</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>44953.69298611111</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>45533</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>45547</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>44139.54078703704</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30330,7 +30330,7 @@
         <v>45341.39853009259</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>45483.57244212963</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30444,7 +30444,7 @@
         <v>44100</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30501,7 +30501,7 @@
         <v>45272.64479166667</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30558,7 +30558,7 @@
         <v>45272</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>44869</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>45385.37922453704</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>45729.7271875</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>44474.62141203704</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30843,7 +30843,7 @@
         <v>45169</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>44584.91001157407</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>45177</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>45721.88684027778</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>45713</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>45436</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>45518</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>45735</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>44952.57989583333</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>45475.61896990741</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>45469</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>45469</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>45600.4558912037</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>45540</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31661,7 +31661,7 @@
         <v>44708.67822916667</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31718,7 +31718,7 @@
         <v>44795</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>45840.70885416667</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>45798.66767361111</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31889,7 +31889,7 @@
         <v>45075</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>45075</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>45075.90934027778</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45786</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>45089</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32174,7 +32174,7 @@
         <v>44395</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32231,7 +32231,7 @@
         <v>45798.67082175926</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>45798</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>45798.66104166667</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>45797.58399305555</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>44132</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>45203.83891203703</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>45589.68289351852</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32630,7 +32630,7 @@
         <v>45797.58350694444</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>45586</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         <v>45478.42887731481</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>44540</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>45414.65855324074</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>44133</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>44596</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>45089</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>45800</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33143,7 +33143,7 @@
         <v>45800</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>45800</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33257,7 +33257,7 @@
         <v>44985</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33314,7 +33314,7 @@
         <v>45799</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>45636.38974537037</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33428,7 +33428,7 @@
         <v>44904</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33485,7 +33485,7 @@
         <v>44143</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>44901</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>45800</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>45800</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45803.4675</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>45224</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33827,7 +33827,7 @@
         <v>45800</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>44592</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33946,7 +33946,7 @@
         <v>45639.45166666667</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>45803.69228009259</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>45559.54706018518</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>45804.74479166666</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>45075.91148148148</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34231,7 +34231,7 @@
         <v>45075</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>45639.47385416667</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>45549</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34402,7 +34402,7 @@
         <v>44813</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>44145</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>45803.66587962963</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>45610.47414351852</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34630,7 +34630,7 @@
         <v>45586</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34687,7 +34687,7 @@
         <v>45644.90815972222</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34744,7 +34744,7 @@
         <v>45450.64643518518</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34806,7 +34806,7 @@
         <v>45640.60240740741</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>45600.47275462963</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34920,7 +34920,7 @@
         <v>44580</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34977,7 +34977,7 @@
         <v>44993.66707175926</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35039,7 +35039,7 @@
         <v>44124</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>44511.70518518519</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35153,7 +35153,7 @@
         <v>45531</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35210,7 +35210,7 @@
         <v>45847.37414351852</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35272,7 +35272,7 @@
         <v>45113</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35329,7 +35329,7 @@
         <v>45113</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>44673</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
         <v>44977</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35500,7 +35500,7 @@
         <v>44525</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35562,7 +35562,7 @@
         <v>45810.42393518519</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35619,7 +35619,7 @@
         <v>44648</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>44643</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35733,7 +35733,7 @@
         <v>45442.45686342593</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>45155</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>45790.81410879629</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35904,7 +35904,7 @@
         <v>45810.5333912037</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35961,7 +35961,7 @@
         <v>44816</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36018,7 +36018,7 @@
         <v>45456</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36075,7 +36075,7 @@
         <v>45617.58453703704</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>45121</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36189,7 +36189,7 @@
         <v>45726.48152777777</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>45810.45236111111</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>45810.45263888889</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36360,7 +36360,7 @@
         <v>44649</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36417,7 +36417,7 @@
         <v>44155.69458333333</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>45810.45633101852</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36531,7 +36531,7 @@
         <v>45811.60451388889</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36588,7 +36588,7 @@
         <v>44938</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36645,7 +36645,7 @@
         <v>45232</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>45735.36594907408</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>45729.71065972222</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>45376.55484953704</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>44179</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>44162</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>45386.34175925926</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37054,7 +37054,7 @@
         <v>45183</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>45813.63650462963</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45813.66961805556</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>44959.74533564815</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>45813.6799537037</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         <v>44644</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>45813.4709375</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>44902</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37515,7 +37515,7 @@
         <v>44635</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37572,7 +37572,7 @@
         <v>44656</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>45376.55638888889</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37696,7 +37696,7 @@
         <v>45687.5038425926</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>45735</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>44670</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37872,7 +37872,7 @@
         <v>45695.57881944445</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>45608</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>45817.2565625</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>45817.30329861111</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38105,7 +38105,7 @@
         <v>45817.31085648148</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38162,7 +38162,7 @@
         <v>45817.31708333334</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>45817.31986111111</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>45817.33503472222</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>45859</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>45859</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>45687</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38514,7 +38514,7 @@
         <v>45617.62358796296</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38571,7 +38571,7 @@
         <v>45069</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>45208.58004629629</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38705,7 +38705,7 @@
         <v>45747.63471064815</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38762,7 +38762,7 @@
         <v>45534.38240740741</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38824,7 +38824,7 @@
         <v>44923.90159722222</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         <v>45817.291875</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38938,7 +38938,7 @@
         <v>44183</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>45817.32538194444</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39052,7 +39052,7 @@
         <v>45412.4104050926</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>45817.25471064815</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         <v>44585</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>45427.88731481481</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>45202.65660879629</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>45817.34083333334</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>45664</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>45840</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>45706.40086805556</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39575,7 +39575,7 @@
         <v>45552.52827546297</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>44624.59434027778</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>44945.67409722223</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>44937</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>45145.51</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>45188.41637731482</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>45215</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         <v>44629</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>44617</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45692</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>45147.65407407407</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>44687</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40274,7 +40274,7 @@
         <v>45757.65178240741</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>45824.37275462963</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40393,7 +40393,7 @@
         <v>45775.41451388889</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40450,7 +40450,7 @@
         <v>45155</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>45254</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>45260.43225694444</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>45260.4333449074</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>44714.56040509259</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>44697</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>45146</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45522.44414351852</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>45868.62267361111</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>45685.44592592592</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45376.54115740741</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45757.62482638889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45205</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45629.65143518519</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41258,7 +41258,7 @@
         <v>44888</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41315,7 +41315,7 @@
         <v>44867.62090277778</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45174.68702546296</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>45701.44372685185</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>45223</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>45686.65545138889</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>45721.40780092592</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>45709.40231481481</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>44704</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>44611</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>45831.51659722222</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41895,7 +41895,7 @@
         <v>45831.65079861111</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41957,7 +41957,7 @@
         <v>44986.5887962963</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42014,7 +42014,7 @@
         <v>45048</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42071,7 +42071,7 @@
         <v>45670.65921296296</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>45208</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42185,7 +42185,7 @@
         <v>45208</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42242,7 +42242,7 @@
         <v>45237</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42299,7 +42299,7 @@
         <v>45145.63584490741</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42356,7 +42356,7 @@
         <v>45740.47055555556</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42413,7 +42413,7 @@
         <v>44775</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>45223</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42527,7 +42527,7 @@
         <v>45700</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>45831.4844212963</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>45832.66385416667</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>45831.54618055555</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>44680</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>45070</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>44693</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>45245</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>44963</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>45112</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44708</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>44708.36708333333</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43221,7 +43221,7 @@
         <v>44746.58530092592</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>45834</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43335,7 +43335,7 @@
         <v>44266</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43392,7 +43392,7 @@
         <v>44266</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43449,7 +43449,7 @@
         <v>44867</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>45876.45253472222</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>45679</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>44684</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>45127.69371527778</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>45245</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43801,7 +43801,7 @@
         <v>44743.67418981482</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>44778</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45623.62563657408</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43982,7 +43982,7 @@
         <v>44732</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>45834.6447337963</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>45075</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44153,7 +44153,7 @@
         <v>45208.70996527778</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44210,7 +44210,7 @@
         <v>45712</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44272,7 +44272,7 @@
         <v>45348.46300925926</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45699.46283564815</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>44803</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44448,7 +44448,7 @@
         <v>45581</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44505,7 +44505,7 @@
         <v>45834.65538194445</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>44181</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45693</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45730.42851851852</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44738,7 +44738,7 @@
         <v>45835.68076388889</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44795,7 +44795,7 @@
         <v>45092</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45092</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44909,7 +44909,7 @@
         <v>45835.4928125</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>44722</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45028,7 +45028,7 @@
         <v>45075.90817129629</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         <v>45880.46524305556</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45147,7 +45147,7 @@
         <v>45880.46372685185</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>44797</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45835.46034722222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>45835</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45837</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45837.94081018519</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45880.46189814815</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45838.43261574074</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>45128</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>44243.33587962963</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45737,7 +45737,7 @@
         <v>45837.93730324074</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45794,7 +45794,7 @@
         <v>45636.41572916666</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45851,7 +45851,7 @@
         <v>45020</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45908,7 +45908,7 @@
         <v>45139.51457175926</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45840.62755787037</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>45614.39627314815</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45839.62398148148</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45840.67829861111</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45839</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>44799.65013888889</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45882.59722222222</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45680.42665509259</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>45293</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46483,7 +46483,7 @@
         <v>45219.56697916667</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46540,7 +46540,7 @@
         <v>45728.38409722222</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>44813.59915509259</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>44325</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46711,7 +46711,7 @@
         <v>44704</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46768,7 +46768,7 @@
         <v>45841.74596064815</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46825,7 +46825,7 @@
         <v>45254.41509259259</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>45841.35611111111</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         <v>45022</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46996,7 +46996,7 @@
         <v>44903</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47053,7 +47053,7 @@
         <v>45884.48696759259</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47110,7 +47110,7 @@
         <v>45168.44489583333</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>44690</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47229,7 +47229,7 @@
         <v>45446.4287962963</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47286,7 +47286,7 @@
         <v>44790</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45841.5737962963</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>45841.56996527778</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47457,7 +47457,7 @@
         <v>45414</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47514,7 +47514,7 @@
         <v>45411.54768518519</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47576,7 +47576,7 @@
         <v>45842.46885416667</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47633,7 +47633,7 @@
         <v>44953.70481481482</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47690,7 +47690,7 @@
         <v>45519</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45107.42538194444</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45111</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>45888.60714120371</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>45730.69502314815</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>45581</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48032,7 +48032,7 @@
         <v>44266</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>44925</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45152</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>45845</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>45844.62609953704</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
         <v>44974</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>44111.44373842593</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48431,7 +48431,7 @@
         <v>44771</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48488,7 +48488,7 @@
         <v>45844.91234953704</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48550,7 +48550,7 @@
         <v>45888.61357638889</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>44694.57413194444</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>44806.41576388889</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>45890.56001157407</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>45609.70778935185</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45609.85146990741</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>44743.59331018518</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48959,7 +48959,7 @@
         <v>45427.89121527778</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49016,7 +49016,7 @@
         <v>44783</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49073,7 +49073,7 @@
         <v>44785</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49135,7 +49135,7 @@
         <v>45587.62565972222</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49192,7 +49192,7 @@
         <v>45748</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>45394.72869212963</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49306,7 +49306,7 @@
         <v>45890.68083333333</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>45894.48322916667</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49420,7 +49420,7 @@
         <v>45601.56726851852</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>45177.61498842593</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45293</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49596,7 +49596,7 @@
         <v>45635.44788194444</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>45019.3959837963</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>45893</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45894.68864583333</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49824,7 +49824,7 @@
         <v>44763.40914351852</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>45893</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>45345.6059837963</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>45631.73952546297</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50052,7 +50052,7 @@
         <v>45631.74673611111</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>44769</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>45894.6353125</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50223,7 +50223,7 @@
         <v>45630.52866898148</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45728.38924768518</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45852.58030092593</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45667.49878472222</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>44217.40149305556</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>44097</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>44732</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>45401.3653125</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45894.70854166667</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45894.71101851852</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>44495.5893287037</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45895.3867824074</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45208.69671296296</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45238</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>44698</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>44749.55258101852</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51135,7 +51135,7 @@
         <v>45853</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>44782</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45895.38778935185</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>45469</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>44146</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51420,7 +51420,7 @@
         <v>44621</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>45532</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>45853</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45896.38466435186</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51648,7 +51648,7 @@
         <v>45212</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45897.50802083333</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>44719</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>45897.51077546296</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45897.51328703704</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45855.69387731481</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51995,7 +51995,7 @@
         <v>45898.54921296296</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>45898.61054398148</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52109,7 +52109,7 @@
         <v>45898.62625</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52166,7 +52166,7 @@
         <v>45640.58716435185</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45898.38552083333</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52285,7 +52285,7 @@
         <v>45898.40480324074</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52347,7 +52347,7 @@
         <v>45898.45636574074</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52404,7 +52404,7 @@
         <v>45855.57033564815</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45855.68413194444</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45898.68826388889</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>44980</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52642,7 +52642,7 @@
         <v>45886</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52699,7 +52699,7 @@
         <v>45700</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52756,7 +52756,7 @@
         <v>45898.45976851852</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52818,7 +52818,7 @@
         <v>45575</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52875,7 +52875,7 @@
         <v>45898.37636574074</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52937,7 +52937,7 @@
         <v>45898.5315625</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52994,7 +52994,7 @@
         <v>45898.62373842593</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -53051,7 +53051,7 @@
         <v>45743.44953703704</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -53108,7 +53108,7 @@
         <v>45707.84997685185</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -53165,7 +53165,7 @@
         <v>45328.46336805556</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -53222,7 +53222,7 @@
         <v>45589.6756712963</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53279,7 +53279,7 @@
         <v>44777</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53336,7 +53336,7 @@
         <v>45085</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53393,7 +53393,7 @@
         <v>45243.45289351852</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53455,7 +53455,7 @@
         <v>45721.65858796296</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53512,7 +53512,7 @@
         <v>45456</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53569,7 +53569,7 @@
         <v>44760</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53626,7 +53626,7 @@
         <v>45042.74291666667</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53683,7 +53683,7 @@
         <v>44375</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53740,7 +53740,7 @@
         <v>44152</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53802,7 +53802,7 @@
         <v>45219</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53859,7 +53859,7 @@
         <v>45442</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53916,7 +53916,7 @@
         <v>45525</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53973,7 +53973,7 @@
         <v>45068.51783564815</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -54030,7 +54030,7 @@
         <v>45531</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -54087,7 +54087,7 @@
         <v>45063</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -54144,7 +54144,7 @@
         <v>44319</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -54201,7 +54201,7 @@
         <v>44691.5652662037</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -54258,7 +54258,7 @@
         <v>45706.61178240741</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54320,7 +54320,7 @@
         <v>44398</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54382,7 +54382,7 @@
         <v>44326</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54439,7 +54439,7 @@
         <v>44908.77368055555</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54496,7 +54496,7 @@
         <v>44251</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54553,7 +54553,7 @@
         <v>45191</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54615,7 +54615,7 @@
         <v>45518</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54672,7 +54672,7 @@
         <v>44510.51422453704</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54734,7 +54734,7 @@
         <v>44815.74539351852</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54791,7 +54791,7 @@
         <v>44380.77346064815</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54848,7 +54848,7 @@
         <v>45771</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>45033</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>45740.47288194444</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -55019,7 +55019,7 @@
         <v>45730.69143518519</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -55076,7 +55076,7 @@
         <v>45554.55707175926</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -55133,7 +55133,7 @@
         <v>44769.66864583334</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -55190,7 +55190,7 @@
         <v>44670.4190162037</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -55247,7 +55247,7 @@
         <v>44306</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55309,7 +55309,7 @@
         <v>45183</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55366,7 +55366,7 @@
         <v>44851</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55423,7 +55423,7 @@
         <v>45772.71221064815</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55480,7 +55480,7 @@
         <v>45215</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         <v>44854</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55594,7 +55594,7 @@
         <v>44778.69210648148</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55651,7 +55651,7 @@
         <v>44747</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55708,7 +55708,7 @@
         <v>45054</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>44832</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55822,7 +55822,7 @@
         <v>44960.60469907407</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55879,7 +55879,7 @@
         <v>45691.41101851852</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>45772.29622685185</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55993,7 +55993,7 @@
         <v>45708.61761574074</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -56050,7 +56050,7 @@
         <v>44682.78430555556</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -56107,7 +56107,7 @@
         <v>44252</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -56164,7 +56164,7 @@
         <v>45587</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45729.60859953704</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -56283,7 +56283,7 @@
         <v>45085.5309375</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         <v>45370</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56402,7 +56402,7 @@
         <v>45236.46369212963</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         <v>45055.43509259259</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56516,7 +56516,7 @@
         <v>44925</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>45735.59287037037</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56630,7 +56630,7 @@
         <v>45733.82105324074</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56687,7 +56687,7 @@
         <v>45075</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>44528.91494212963</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>44866.49827546296</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56858,7 +56858,7 @@
         <v>45735.36873842592</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56915,7 +56915,7 @@
         <v>45561.62141203704</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56972,7 +56972,7 @@
         <v>45764.6359837963</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -57029,7 +57029,7 @@
         <v>44596.66335648148</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -57091,7 +57091,7 @@
         <v>44549</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -57148,7 +57148,7 @@
         <v>44922</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -57205,7 +57205,7 @@
         <v>44145</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -57262,7 +57262,7 @@
         <v>45063</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57319,7 +57319,7 @@
         <v>45065.55917824074</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57381,7 +57381,7 @@
         <v>44767.60601851852</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57438,7 +57438,7 @@
         <v>44490.02482638889</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57495,7 +57495,7 @@
         <v>44490.03621527777</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57552,7 +57552,7 @@
         <v>44995</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57609,7 +57609,7 @@
         <v>45490.45342592592</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57671,7 +57671,7 @@
         <v>45469</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57728,7 +57728,7 @@
         <v>44459</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>44083</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>44452</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>44750.66068287037</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>44750</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>45338</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>44124</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -58137,7 +58137,7 @@
         <v>45082</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -58194,7 +58194,7 @@
         <v>45082.68922453704</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -58251,7 +58251,7 @@
         <v>44771</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>44760</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>44760</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>44816</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58484,7 +58484,7 @@
         <v>44813</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58541,7 +58541,7 @@
         <v>45089</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58598,7 +58598,7 @@
         <v>44376.50728009259</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>45468.45877314815</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45261</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58769,7 +58769,7 @@
         <v>45259</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45253.61146990741</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58883,7 +58883,7 @@
         <v>45740.47550925926</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45740.47724537037</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>45344</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -59054,7 +59054,7 @@
         <v>45435.43466435185</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45435.43820601852</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45621.34425925926</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45621.35712962963</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>45600.411875</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45548.72306712963</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>45435.43123842592</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45282</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>44938</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59577,7 +59577,7 @@
         <v>44260</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59639,7 +59639,7 @@
         <v>44753</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59696,7 +59696,7 @@
         <v>45231.34144675926</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59753,7 +59753,7 @@
         <v>45104</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59815,7 +59815,7 @@
         <v>44698</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59877,7 +59877,7 @@
         <v>44992</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59934,7 +59934,7 @@
         <v>45729.72851851852</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         <v>44483</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         <v>45054.54091435186</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         <v>45054</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -60167,7 +60167,7 @@
         <v>44777</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         <v>45104</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         <v>45394.58778935186</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60343,7 +60343,7 @@
         <v>45022.61003472222</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60400,7 +60400,7 @@
         <v>45668.67446759259</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60457,7 +60457,7 @@
         <v>45670.3079050926</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60514,7 +60514,7 @@
         <v>44218</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60571,7 +60571,7 @@
         <v>45007</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60628,7 +60628,7 @@
         <v>44599.58428240741</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60685,7 +60685,7 @@
         <v>45713.92623842593</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60742,7 +60742,7 @@
         <v>44743.59765046297</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60804,7 +60804,7 @@
         <v>44743.64592592593</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60866,7 +60866,7 @@
         <v>45640.57305555556</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60923,7 +60923,7 @@
         <v>44326.61967592593</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60980,7 +60980,7 @@
         <v>44858</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -61037,7 +61037,7 @@
         <v>45183</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -61094,7 +61094,7 @@
         <v>45638.5987037037</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -61156,7 +61156,7 @@
         <v>45453</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -61213,7 +61213,7 @@
         <v>45770</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -61270,7 +61270,7 @@
         <v>45310.40628472222</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -61327,7 +61327,7 @@
         <v>45310</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -61384,7 +61384,7 @@
         <v>44700.50659722222</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61441,7 +61441,7 @@
         <v>45254</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61498,7 +61498,7 @@
         <v>45089</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61555,7 +61555,7 @@
         <v>45159</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61612,7 +61612,7 @@
         <v>45322</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61669,7 +61669,7 @@
         <v>45414.58650462963</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61726,7 +61726,7 @@
         <v>45162</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61788,7 +61788,7 @@
         <v>45679</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61845,7 +61845,7 @@
         <v>45139</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61902,7 +61902,7 @@
         <v>45019.28847222222</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61959,7 +61959,7 @@
         <v>45082.69179398148</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -62016,7 +62016,7 @@
         <v>45482.53388888889</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -62073,7 +62073,7 @@
         <v>44956</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -62130,7 +62130,7 @@
         <v>44956</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -62187,7 +62187,7 @@
         <v>45084.57695601852</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -62249,7 +62249,7 @@
         <v>45257</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -62306,7 +62306,7 @@
         <v>44803</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62363,7 +62363,7 @@
         <v>44687</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62420,7 +62420,7 @@
         <v>44110</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62482,7 +62482,7 @@
         <v>44456</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62539,7 +62539,7 @@
         <v>44732</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62596,7 +62596,7 @@
         <v>45056</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62653,7 +62653,7 @@
         <v>45530</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62710,7 +62710,7 @@
         <v>45218.65849537037</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62767,7 +62767,7 @@
         <v>44817.56120370371</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62824,7 +62824,7 @@
         <v>44390</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62881,7 +62881,7 @@
         <v>45022</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62938,7 +62938,7 @@
         <v>45723</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -63000,7 +63000,7 @@
         <v>44841.52804398148</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -63062,7 +63062,7 @@
         <v>45518</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -63119,7 +63119,7 @@
         <v>45757.61421296297</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -63176,7 +63176,7 @@
         <v>45721.89123842592</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -63233,7 +63233,7 @@
         <v>45708</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -63295,7 +63295,7 @@
         <v>44934</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63352,7 +63352,7 @@
         <v>44778</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63409,7 +63409,7 @@
         <v>44581</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63466,7 +63466,7 @@
         <v>45376.55704861111</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63523,7 +63523,7 @@
         <v>45293.37263888889</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63580,7 +63580,7 @@
         <v>45245</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63637,7 +63637,7 @@
         <v>45245</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63694,7 +63694,7 @@
         <v>44956.65920138889</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63751,7 +63751,7 @@
         <v>44931.65626157408</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63808,7 +63808,7 @@
         <v>45460.45523148148</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63865,7 +63865,7 @@
         <v>45293</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63922,7 +63922,7 @@
         <v>45726.48377314815</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63979,7 +63979,7 @@
         <v>44321</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -64036,7 +64036,7 @@
         <v>45118</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -64098,7 +64098,7 @@
         <v>45723</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -64160,7 +64160,7 @@
         <v>45617.57439814815</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -64217,7 +64217,7 @@
         <v>45706.60130787037</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -64279,7 +64279,7 @@
         <v>44900</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -64336,7 +64336,7 @@
         <v>44714.92253472222</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64393,7 +64393,7 @@
         <v>44743.59504629629</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64455,7 +64455,7 @@
         <v>45245</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64512,7 +64512,7 @@
         <v>45356.47784722222</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64569,7 +64569,7 @@
         <v>45092</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64626,7 +64626,7 @@
         <v>44637</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64683,7 +64683,7 @@
         <v>44816</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64740,7 +64740,7 @@
         <v>45757.60658564815</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -64797,7 +64797,7 @@
         <v>45760.91174768518</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -64854,7 +64854,7 @@
         <v>45075.90703703704</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -64911,7 +64911,7 @@
         <v>45490.60572916667</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -64968,7 +64968,7 @@
         <v>45638.59979166667</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -65030,7 +65030,7 @@
         <v>45357</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -65087,7 +65087,7 @@
         <v>45058.78607638889</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -65144,7 +65144,7 @@
         <v>45600.86128472222</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>

--- a/Översikt NORRTÄLJE.xlsx
+++ b/Översikt NORRTÄLJE.xlsx
@@ -567,7 +567,7 @@
         <v>45135</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44757</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44249</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45757</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>44909</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45457</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45226</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45367</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45715</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44949</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45436</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>45190</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44263</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>44550</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>45586.88145833334</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>44467</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>45600</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45638</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45688.38224537037</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>44846</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>44858</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>44447</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>45400.5958912037</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>44650</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>45800</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>45748.6521875</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>45831.53390046296</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>45068</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>44076</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>44544</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44711</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>45784.32179398148</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         <v>45783.58123842593</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>44545</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>45722</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>44336</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44839</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>45847.47052083333</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         <v>45898.62723379629</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>44300</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>44749</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>44843</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>44279</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>45616.54866898148</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45611.47233796296</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45821</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>44866</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>44945</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44698</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         <v>45847.47685185185</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>45847.48436342592</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>44370</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>44489</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>45723</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
         <v>45219</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>44763</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>45609.37094907407</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>44670</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>45446.35888888889</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>45226</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>45800</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>45772.30234953704</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>44868</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44872</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>44573</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>44102</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>44564.66387731482</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44161</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>44363</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>44788.70217592592</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>44680</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>44695.43527777777</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>45784.54878472222</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>44855</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>44620</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>44956</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>45794.63298611111</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         <v>45800</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>45146</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7988,7 +7988,7 @@
         <v>45532</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>45803.62766203703</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>44965</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         <v>45687.34177083334</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>45826.46392361111</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>45754</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>44489</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>45798</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>45741.38688657407</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>44704</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>45841.5721875</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>45888.62712962963</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         <v>44207</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>45065</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>44683</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>45468.45995370371</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>45897.56356481482</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>45708</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9560,7 +9560,7 @@
         <v>45450.63958333333</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>44993</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9735,7 +9735,7 @@
         <v>44863</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>45474</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>45735.54510416667</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         <v>44955.71322916666</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>45280</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>45081</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>45082</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>45092</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>45609.83747685186</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45225</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>45205</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>44210</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>44209</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10793,7 +10793,7 @@
         <v>44306</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>44642</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10912,7 +10912,7 @@
         <v>44540</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>44650.8699537037</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>44447</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>44833</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11145,7 +11145,7 @@
         <v>44284.59546296296</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>44420</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11259,7 +11259,7 @@
         <v>44420</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>44330</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11373,7 +11373,7 @@
         <v>44097</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>44728.73465277778</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44777</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>44810.85092592592</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>44552</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>44560</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>44470.72148148148</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>44634</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>44581.75819444445</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>44771</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>44111.45320601852</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12015,7 +12015,7 @@
         <v>44477.94327546296</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44380</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>44524</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>44574.42978009259</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
         <v>44516.72827546296</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>44103</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12362,7 +12362,7 @@
         <v>44868</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>44309.47061342592</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>44834</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>44400</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>44161</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12652,7 +12652,7 @@
         <v>44252</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12714,7 +12714,7 @@
         <v>44451</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>44858</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>44244</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>44496</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>44626</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>44682.79203703703</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>44690</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>44708</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>44642</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>44776</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         <v>44103</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>44176</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>44746</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>44214</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>44306</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
         <v>44727</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>44845.47585648148</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13688,7 +13688,7 @@
         <v>44543</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>44543</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>44694.57549768518</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>44495</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13916,7 +13916,7 @@
         <v>44749.61980324074</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>44882.44732638889</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14030,7 +14030,7 @@
         <v>44882</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14087,7 +14087,7 @@
         <v>44224</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>44545.4189699074</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
         <v>44314</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>44279</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>44300</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>44722</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>44742</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>44756.40881944444</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>44124</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>44294</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>44806.34577546296</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14719,7 +14719,7 @@
         <v>44330</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>44330</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         <v>44511.69885416667</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14890,7 +14890,7 @@
         <v>44510</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>44447</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>44391.5580787037</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>44435</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>44867</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>44571</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>44453</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>44511</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>44495</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15403,7 +15403,7 @@
         <v>44683</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>44201</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>44201</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>44375</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44539</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44516.5275462963</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>44496</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>44414.81494212963</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>44299</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>44380</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15973,7 +15973,7 @@
         <v>44594.75950231482</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>44363.5784375</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>44712.83118055556</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16144,7 +16144,7 @@
         <v>44769.62320601852</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16201,7 +16201,7 @@
         <v>44309</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>44251.43971064815</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>44572</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>44698</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>44845.47672453704</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>44397</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44543</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>44543</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>44650.92714120371</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16724,7 +16724,7 @@
         <v>44270</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>44270</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>44526</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>44760</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>44545</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>44545</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>44609</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>44725.49491898148</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>44427</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>44817.70516203704</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>44230</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17351,7 +17351,7 @@
         <v>44230</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>44477</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>44621</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17527,7 +17527,7 @@
         <v>44496.77542824074</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>44580</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>44868</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17698,7 +17698,7 @@
         <v>44251</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
         <v>44665.66407407408</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17817,7 +17817,7 @@
         <v>44777</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17874,7 +17874,7 @@
         <v>44880.68423611111</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17931,7 +17931,7 @@
         <v>44637</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17988,7 +17988,7 @@
         <v>44735</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>44637</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18102,7 +18102,7 @@
         <v>44300</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44655.45373842592</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>44658</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18297,7 +18297,7 @@
         <v>44100</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>44584.91538194445</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>44678</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>44350</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18525,7 +18525,7 @@
         <v>44143</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>44763.4182175926</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>44816.89569444444</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>44682.75924768519</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18753,7 +18753,7 @@
         <v>44682.77616898148</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>44623</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18867,7 +18867,7 @@
         <v>44502</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>44132</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>44595</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>44466.37496527778</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>44076</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19157,7 +19157,7 @@
         <v>44105</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>44376</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>44642.55565972222</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         <v>44153</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>44665.65474537037</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>44665.78351851852</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19499,7 +19499,7 @@
         <v>44735</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>44533</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>44176</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>44744</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>44342</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>44704</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>44333</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>44543</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44682.76528935185</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44523.61635416667</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>44595</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>44370.72197916666</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44725</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>44284</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>44350</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44826</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>44326</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20478,7 +20478,7 @@
         <v>44637</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20535,7 +20535,7 @@
         <v>44524</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>44607</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>44425</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>44425</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>44815</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>44379</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>44495</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45203.63303240741</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>44824.36069444445</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>44419</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45772.3078125</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45625</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45208</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44879.70518518519</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>45621.34813657407</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>44231</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>44949</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>45092</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>44833.40876157407</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>44575.52831018518</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>44643</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>45730.35026620371</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>44272</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>45644.47878472223</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21913,7 +21913,7 @@
         <v>44743.47407407407</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>44949</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22027,7 +22027,7 @@
         <v>44953.67443287037</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>44266</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>44376</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>45772.51127314815</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45405.57927083333</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45086.3629050926</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>45772.30436342592</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>45253.55641203704</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22483,7 +22483,7 @@
         <v>45737.43347222222</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>44963</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>45273</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>45075.91362268518</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22716,7 +22716,7 @@
         <v>45075.91971064815</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22773,7 +22773,7 @@
         <v>44315</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>44764</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45051.455</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>45175</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44098</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>45749</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>45705.66126157407</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23187,7 +23187,7 @@
         <v>45362.62811342593</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>44778.92797453704</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>45694.68207175926</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23363,7 +23363,7 @@
         <v>45330.50098379629</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23420,7 +23420,7 @@
         <v>45084.54459490741</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>45218</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>44882</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>45473.94501157408</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23648,7 +23648,7 @@
         <v>45356.4722800926</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>45259</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>44285</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23819,7 +23819,7 @@
         <v>45455.33037037037</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45147.65222222222</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45147.65311342593</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>45147</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>45253.63089120371</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>45776.62563657408</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>44840</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>45433.58431712963</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45316.60306712963</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>45776.47346064815</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>45776.46369212963</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>44556</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>45776.59871527777</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24560,7 +24560,7 @@
         <v>45383</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>45435</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>45190.55609953704</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>45776.47122685185</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>44705.60626157407</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>44895</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>45397</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>44470</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>44621</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>45391.3395949074</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>45450.64208333333</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>45450</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25254,7 +25254,7 @@
         <v>44868.45741898148</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45755.36583333334</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45223</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25425,7 +25425,7 @@
         <v>44272</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>45239</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45485</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25596,7 +25596,7 @@
         <v>44845.48064814815</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>45783</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>45558.46283564815</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>45454.65774305556</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>45104</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>45104</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>45783.66429398148</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>45783.48878472222</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>45769</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45385.38146990741</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26166,7 +26166,7 @@
         <v>44809</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>45202</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26285,7 +26285,7 @@
         <v>45549</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26342,7 +26342,7 @@
         <v>45376.64532407407</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26399,7 +26399,7 @@
         <v>45187</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>45735</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>45075.90270833333</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26575,7 +26575,7 @@
         <v>45075.91042824074</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>45075.91265046296</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>45075.92153935185</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>44962</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45709.39361111111</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26865,7 +26865,7 @@
         <v>45089</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         <v>44510</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>45131.666875</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>45576</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27098,7 +27098,7 @@
         <v>44866.63775462963</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>44105</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27212,7 +27212,7 @@
         <v>45448.56746527777</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27269,7 +27269,7 @@
         <v>45257</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27326,7 +27326,7 @@
         <v>45572.57828703704</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27383,7 +27383,7 @@
         <v>45418.6968287037</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>44362.37172453704</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>45460.44347222222</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>45418</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>45785.65300925926</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>45063.35880787037</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>44956</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27787,7 +27787,7 @@
         <v>45385.36243055556</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27844,7 +27844,7 @@
         <v>44472</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27901,7 +27901,7 @@
         <v>45537</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>45579</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>45485.60261574074</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>45119.57728009259</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45536</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>45463.80486111111</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>45831.56521990741</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>45457</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28362,7 +28362,7 @@
         <v>45468.45628472222</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>44076</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45170</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>45352.74090277778</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>44525</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>44578</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>44546</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28761,7 +28761,7 @@
         <v>44516</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>44516.40674768519</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         <v>45468.45541666666</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28942,7 +28942,7 @@
         <v>45468.45747685185</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28999,7 +28999,7 @@
         <v>45610.39271990741</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>45408.57707175926</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29113,7 +29113,7 @@
         <v>44769.66039351852</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>45786.55645833333</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>44470.72987268519</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>44834.38636574074</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>44113</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>45635.88849537037</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>45271</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>45642.64634259259</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29574,7 +29574,7 @@
         <v>45260</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29631,7 +29631,7 @@
         <v>44637</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29693,7 +29693,7 @@
         <v>45524</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>44325</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>44461</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>45443</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>45245</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>45715</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30045,7 +30045,7 @@
         <v>44108</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30102,7 +30102,7 @@
         <v>44953.69298611111</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>45533</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>45547</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>44139.54078703704</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30330,7 +30330,7 @@
         <v>45341.39853009259</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>45483.57244212963</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30444,7 +30444,7 @@
         <v>44100</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30501,7 +30501,7 @@
         <v>45272.64479166667</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30558,7 +30558,7 @@
         <v>45272</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30615,7 +30615,7 @@
         <v>44869</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>45385.37922453704</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>45729.7271875</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>44474.62141203704</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30843,7 +30843,7 @@
         <v>45169</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>44584.91001157407</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>45177</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>45721.88684027778</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31076,7 +31076,7 @@
         <v>45713</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>45436</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>45518</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31252,7 +31252,7 @@
         <v>45735</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31309,7 +31309,7 @@
         <v>44952.57989583333</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>45475.61896990741</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>45469</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>45469</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>45600.4558912037</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>45540</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31661,7 +31661,7 @@
         <v>44708.67822916667</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31718,7 +31718,7 @@
         <v>44795</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>45840.70885416667</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>45798.66767361111</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31889,7 +31889,7 @@
         <v>45075</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31946,7 +31946,7 @@
         <v>45075</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32003,7 +32003,7 @@
         <v>45075.90934027778</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45786</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>45089</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32174,7 +32174,7 @@
         <v>44395</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32231,7 +32231,7 @@
         <v>45798.67082175926</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>45798</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>45798.66104166667</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>45797.58399305555</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>44132</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>45203.83891203703</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>45589.68289351852</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32630,7 +32630,7 @@
         <v>45797.58350694444</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>45586</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         <v>45478.42887731481</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>44540</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>45414.65855324074</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>44133</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>44596</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>45089</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>45800</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33143,7 +33143,7 @@
         <v>45800</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>45800</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33257,7 +33257,7 @@
         <v>44985</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33314,7 +33314,7 @@
         <v>45799</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>45636.38974537037</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33428,7 +33428,7 @@
         <v>44904</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33485,7 +33485,7 @@
         <v>44143</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>44901</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33599,7 +33599,7 @@
         <v>45800</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33656,7 +33656,7 @@
         <v>45800</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45803.4675</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33770,7 +33770,7 @@
         <v>45224</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33827,7 +33827,7 @@
         <v>45800</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>44592</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33946,7 +33946,7 @@
         <v>45639.45166666667</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>45803.69228009259</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>45559.54706018518</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34117,7 +34117,7 @@
         <v>45804.74479166666</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34174,7 +34174,7 @@
         <v>45075.91148148148</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34231,7 +34231,7 @@
         <v>45075</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>45639.47385416667</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34345,7 +34345,7 @@
         <v>45549</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34402,7 +34402,7 @@
         <v>44813</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>44145</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>45803.66587962963</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>45610.47414351852</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34630,7 +34630,7 @@
         <v>45586</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34687,7 +34687,7 @@
         <v>45644.90815972222</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34744,7 +34744,7 @@
         <v>45450.64643518518</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34806,7 +34806,7 @@
         <v>45640.60240740741</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>45600.47275462963</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34920,7 +34920,7 @@
         <v>44580</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34977,7 +34977,7 @@
         <v>44993.66707175926</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35039,7 +35039,7 @@
         <v>44124</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35096,7 +35096,7 @@
         <v>44511.70518518519</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35153,7 +35153,7 @@
         <v>45531</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35210,7 +35210,7 @@
         <v>45847.37414351852</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35272,7 +35272,7 @@
         <v>45113</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35329,7 +35329,7 @@
         <v>45113</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>44673</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35443,7 +35443,7 @@
         <v>44977</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35500,7 +35500,7 @@
         <v>44525</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35562,7 +35562,7 @@
         <v>45810.42393518519</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35619,7 +35619,7 @@
         <v>44648</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>44643</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35733,7 +35733,7 @@
         <v>45442.45686342593</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35790,7 +35790,7 @@
         <v>45155</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>45790.81410879629</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35904,7 +35904,7 @@
         <v>45810.5333912037</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35961,7 +35961,7 @@
         <v>44816</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36018,7 +36018,7 @@
         <v>45456</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36075,7 +36075,7 @@
         <v>45617.58453703704</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>45121</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36189,7 +36189,7 @@
         <v>45726.48152777777</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36246,7 +36246,7 @@
         <v>45810.45236111111</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>45810.45263888889</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36360,7 +36360,7 @@
         <v>44649</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36417,7 +36417,7 @@
         <v>44155.69458333333</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>45810.45633101852</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36531,7 +36531,7 @@
         <v>45811.60451388889</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36588,7 +36588,7 @@
         <v>44938</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36645,7 +36645,7 @@
         <v>45232</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>45735.36594907408</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>45729.71065972222</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>45376.55484953704</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>44179</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>44162</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>45386.34175925926</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37054,7 +37054,7 @@
         <v>45183</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>45813.63650462963</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45813.66961805556</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>44959.74533564815</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>45813.6799537037</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         <v>44644</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>45813.4709375</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37458,7 +37458,7 @@
         <v>44902</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37515,7 +37515,7 @@
         <v>44635</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37572,7 +37572,7 @@
         <v>44656</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37634,7 +37634,7 @@
         <v>45376.55638888889</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37696,7 +37696,7 @@
         <v>45687.5038425926</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>45735</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>44670</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37872,7 +37872,7 @@
         <v>45695.57881944445</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>45608</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>45817.2565625</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38048,7 +38048,7 @@
         <v>45817.30329861111</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38105,7 +38105,7 @@
         <v>45817.31085648148</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38162,7 +38162,7 @@
         <v>45817.31708333334</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38219,7 +38219,7 @@
         <v>45817.31986111111</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>45817.33503472222</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>45859</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38395,7 +38395,7 @@
         <v>45859</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>45687</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38514,7 +38514,7 @@
         <v>45617.62358796296</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38571,7 +38571,7 @@
         <v>45069</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38648,7 +38648,7 @@
         <v>45208.58004629629</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38705,7 +38705,7 @@
         <v>45747.63471064815</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38762,7 +38762,7 @@
         <v>45534.38240740741</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38824,7 +38824,7 @@
         <v>44923.90159722222</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38881,7 +38881,7 @@
         <v>45817.291875</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38938,7 +38938,7 @@
         <v>44183</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>45817.32538194444</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39052,7 +39052,7 @@
         <v>45412.4104050926</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>45817.25471064815</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         <v>44585</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>45427.88731481481</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>45202.65660879629</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39342,7 +39342,7 @@
         <v>45817.34083333334</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>45664</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>45840</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>45706.40086805556</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39575,7 +39575,7 @@
         <v>45552.52827546297</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>44624.59434027778</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>44945.67409722223</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>44937</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>45145.51</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>45188.41637731482</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39922,7 +39922,7 @@
         <v>45215</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -39979,7 +39979,7 @@
         <v>44629</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40041,7 +40041,7 @@
         <v>44617</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>45692</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>45147.65407407407</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>44687</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40274,7 +40274,7 @@
         <v>45757.65178240741</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40331,7 +40331,7 @@
         <v>45824.37275462963</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40393,7 +40393,7 @@
         <v>45775.41451388889</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40450,7 +40450,7 @@
         <v>45155</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40507,7 +40507,7 @@
         <v>45254</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40564,7 +40564,7 @@
         <v>45260.43225694444</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>45260.4333449074</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>44714.56040509259</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>44697</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>45146</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40854,7 +40854,7 @@
         <v>45522.44414351852</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>45868.62267361111</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -40968,7 +40968,7 @@
         <v>45685.44592592592</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45376.54115740741</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>45757.62482638889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45205</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45629.65143518519</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41258,7 +41258,7 @@
         <v>44888</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41315,7 +41315,7 @@
         <v>44867.62090277778</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45174.68702546296</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>45701.44372685185</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>45223</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>45686.65545138889</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>45721.40780092592</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>45709.40231481481</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>44704</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>44611</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>45831.51659722222</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41895,7 +41895,7 @@
         <v>45831.65079861111</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -41957,7 +41957,7 @@
         <v>44986.5887962963</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42014,7 +42014,7 @@
         <v>45048</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42071,7 +42071,7 @@
         <v>45670.65921296296</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>45208</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42185,7 +42185,7 @@
         <v>45208</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42242,7 +42242,7 @@
         <v>45237</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42299,7 +42299,7 @@
         <v>45145.63584490741</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42356,7 +42356,7 @@
         <v>45740.47055555556</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42413,7 +42413,7 @@
         <v>44775</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>45223</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42527,7 +42527,7 @@
         <v>45700</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>45831.4844212963</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>45832.66385416667</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>45831.54618055555</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>44680</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>45070</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
         <v>44693</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -42931,7 +42931,7 @@
         <v>45245</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>44963</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>45112</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>44708</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>44708.36708333333</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43221,7 +43221,7 @@
         <v>44746.58530092592</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>45834</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43335,7 +43335,7 @@
         <v>44266</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43392,7 +43392,7 @@
         <v>44266</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43449,7 +43449,7 @@
         <v>44867</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43506,7 +43506,7 @@
         <v>45876.45253472222</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>45679</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>44684</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>45127.69371527778</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>45245</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43801,7 +43801,7 @@
         <v>44743.67418981482</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>44778</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45623.62563657408</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -43982,7 +43982,7 @@
         <v>44732</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44039,7 +44039,7 @@
         <v>45834.6447337963</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>45075</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44153,7 +44153,7 @@
         <v>45208.70996527778</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44210,7 +44210,7 @@
         <v>45712</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44272,7 +44272,7 @@
         <v>45348.46300925926</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44334,7 +44334,7 @@
         <v>45699.46283564815</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44391,7 +44391,7 @@
         <v>44803</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44448,7 +44448,7 @@
         <v>45581</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44505,7 +44505,7 @@
         <v>45834.65538194445</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>44181</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45693</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44676,7 +44676,7 @@
         <v>45730.42851851852</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44738,7 +44738,7 @@
         <v>45835.68076388889</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44795,7 +44795,7 @@
         <v>45092</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44852,7 +44852,7 @@
         <v>45092</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -44909,7 +44909,7 @@
         <v>45835.4928125</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -44971,7 +44971,7 @@
         <v>44722</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45028,7 +45028,7 @@
         <v>45075.90817129629</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45085,7 +45085,7 @@
         <v>45880.46524305556</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45147,7 +45147,7 @@
         <v>45880.46372685185</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45209,7 +45209,7 @@
         <v>44797</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45266,7 +45266,7 @@
         <v>45835.46034722222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>45835</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45385,7 +45385,7 @@
         <v>45837</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>45837.94081018519</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45499,7 +45499,7 @@
         <v>45880.46189814815</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45838.43261574074</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>45128</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>44243.33587962963</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45737,7 +45737,7 @@
         <v>45837.93730324074</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45794,7 +45794,7 @@
         <v>45636.41572916666</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45851,7 +45851,7 @@
         <v>45020</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -45908,7 +45908,7 @@
         <v>45139.51457175926</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45840.62755787037</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46022,7 +46022,7 @@
         <v>45614.39627314815</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46079,7 +46079,7 @@
         <v>45839.62398148148</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45840.67829861111</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>45839</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>44799.65013888889</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46307,7 +46307,7 @@
         <v>45882.59722222222</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>45680.42665509259</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46421,7 +46421,7 @@
         <v>45293</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46483,7 +46483,7 @@
         <v>45219.56697916667</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46540,7 +46540,7 @@
         <v>45728.38409722222</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46597,7 +46597,7 @@
         <v>44813.59915509259</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46654,7 +46654,7 @@
         <v>44325</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46711,7 +46711,7 @@
         <v>44704</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46768,7 +46768,7 @@
         <v>45841.74596064815</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46825,7 +46825,7 @@
         <v>45254.41509259259</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -46882,7 +46882,7 @@
         <v>45841.35611111111</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         <v>45022</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -46996,7 +46996,7 @@
         <v>44903</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47053,7 +47053,7 @@
         <v>45884.48696759259</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47110,7 +47110,7 @@
         <v>45168.44489583333</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>44690</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47229,7 +47229,7 @@
         <v>45446.4287962963</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47286,7 +47286,7 @@
         <v>44790</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47343,7 +47343,7 @@
         <v>45841.5737962963</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47400,7 +47400,7 @@
         <v>45841.56996527778</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47457,7 +47457,7 @@
         <v>45414</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47514,7 +47514,7 @@
         <v>45411.54768518519</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47576,7 +47576,7 @@
         <v>45842.46885416667</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47633,7 +47633,7 @@
         <v>44953.70481481482</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47690,7 +47690,7 @@
         <v>45519</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47747,7 +47747,7 @@
         <v>45107.42538194444</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>45111</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47861,7 +47861,7 @@
         <v>45888.60714120371</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -47918,7 +47918,7 @@
         <v>45730.69502314815</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -47975,7 +47975,7 @@
         <v>45581</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48032,7 +48032,7 @@
         <v>44266</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48089,7 +48089,7 @@
         <v>44925</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45152</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>45845</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>45844.62609953704</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48317,7 +48317,7 @@
         <v>44974</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>44111.44373842593</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48431,7 +48431,7 @@
         <v>44771</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48488,7 +48488,7 @@
         <v>45844.91234953704</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48550,7 +48550,7 @@
         <v>45888.61357638889</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>44694.57413194444</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>44806.41576388889</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>45890.56001157407</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>45609.70778935185</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48840,7 +48840,7 @@
         <v>45609.85146990741</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>44743.59331018518</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -48959,7 +48959,7 @@
         <v>45427.89121527778</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49016,7 +49016,7 @@
         <v>44783</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49073,7 +49073,7 @@
         <v>44785</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49135,7 +49135,7 @@
         <v>45587.62565972222</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49192,7 +49192,7 @@
         <v>45748</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>45394.72869212963</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49306,7 +49306,7 @@
         <v>45890.68083333333</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>45894.48322916667</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49420,7 +49420,7 @@
         <v>45601.56726851852</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49477,7 +49477,7 @@
         <v>45177.61498842593</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49534,7 +49534,7 @@
         <v>45293</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49596,7 +49596,7 @@
         <v>45635.44788194444</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49653,7 +49653,7 @@
         <v>45019.3959837963</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>45893</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49767,7 +49767,7 @@
         <v>45894.68864583333</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49824,7 +49824,7 @@
         <v>44763.40914351852</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49881,7 +49881,7 @@
         <v>45893</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>45345.6059837963</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -49995,7 +49995,7 @@
         <v>45631.73952546297</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50052,7 +50052,7 @@
         <v>45631.74673611111</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>44769</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50166,7 +50166,7 @@
         <v>45894.6353125</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50223,7 +50223,7 @@
         <v>45630.52866898148</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45728.38924768518</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45852.58030092593</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45667.49878472222</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50451,7 +50451,7 @@
         <v>44217.40149305556</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50508,7 +50508,7 @@
         <v>44097</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50565,7 +50565,7 @@
         <v>44732</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50622,7 +50622,7 @@
         <v>45401.3653125</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>45894.70854166667</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         <v>45894.71101851852</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50793,7 +50793,7 @@
         <v>44495.5893287037</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50850,7 +50850,7 @@
         <v>45895.3867824074</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -50907,7 +50907,7 @@
         <v>45208.69671296296</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45238</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51021,7 +51021,7 @@
         <v>44698</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>44749.55258101852</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51135,7 +51135,7 @@
         <v>45853</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51192,7 +51192,7 @@
         <v>44782</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51249,7 +51249,7 @@
         <v>45895.38778935185</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51306,7 +51306,7 @@
         <v>45469</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>44146</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51420,7 +51420,7 @@
         <v>44621</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>45532</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>45853</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51591,7 +51591,7 @@
         <v>45896.38466435186</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51648,7 +51648,7 @@
         <v>45212</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51705,7 +51705,7 @@
         <v>45897.50802083333</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>44719</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>45897.51077546296</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45897.51328703704</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45855.69387731481</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -51995,7 +51995,7 @@
         <v>45898.54921296296</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>45898.61054398148</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52109,7 +52109,7 @@
         <v>45898.62625</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52166,7 +52166,7 @@
         <v>45640.58716435185</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52223,7 +52223,7 @@
         <v>45898.38552083333</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52285,7 +52285,7 @@
         <v>45898.40480324074</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52347,7 +52347,7 @@
         <v>45898.45636574074</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52404,7 +52404,7 @@
         <v>45855.57033564815</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45855.68413194444</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45898.68826388889</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52585,7 +52585,7 @@
         <v>44980</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52642,7 +52642,7 @@
         <v>45886</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52699,7 +52699,7 @@
         <v>45700</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52756,7 +52756,7 @@
         <v>45898.45976851852</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52818,7 +52818,7 @@
         <v>45575</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -52875,7 +52875,7 @@
         <v>45898.37636574074</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -52937,7 +52937,7 @@
         <v>45898.5315625</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -52994,7 +52994,7 @@
         <v>45898.62373842593</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -53051,7 +53051,7 @@
         <v>45743.44953703704</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -53108,7 +53108,7 @@
         <v>45707.84997685185</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -53165,7 +53165,7 @@
         <v>45328.46336805556</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -53222,7 +53222,7 @@
         <v>45589.6756712963</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53279,7 +53279,7 @@
         <v>44777</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53336,7 +53336,7 @@
         <v>45085</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53393,7 +53393,7 @@
         <v>45243.45289351852</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53455,7 +53455,7 @@
         <v>45721.65858796296</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53512,7 +53512,7 @@
         <v>45456</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53569,7 +53569,7 @@
         <v>44760</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53626,7 +53626,7 @@
         <v>45042.74291666667</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53683,7 +53683,7 @@
         <v>44375</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53740,7 +53740,7 @@
         <v>44152</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53802,7 +53802,7 @@
         <v>45219</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53859,7 +53859,7 @@
         <v>45442</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -53916,7 +53916,7 @@
         <v>45525</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -53973,7 +53973,7 @@
         <v>45068.51783564815</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -54030,7 +54030,7 @@
         <v>45531</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -54087,7 +54087,7 @@
         <v>45063</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -54144,7 +54144,7 @@
         <v>44319</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -54201,7 +54201,7 @@
         <v>44691.5652662037</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -54258,7 +54258,7 @@
         <v>45706.61178240741</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54320,7 +54320,7 @@
         <v>44398</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54382,7 +54382,7 @@
         <v>44326</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54439,7 +54439,7 @@
         <v>44908.77368055555</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54496,7 +54496,7 @@
         <v>44251</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54553,7 +54553,7 @@
         <v>45191</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54615,7 +54615,7 @@
         <v>45518</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54672,7 +54672,7 @@
         <v>44510.51422453704</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54734,7 +54734,7 @@
         <v>44815.74539351852</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54791,7 +54791,7 @@
         <v>44380.77346064815</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54848,7 +54848,7 @@
         <v>45771</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -54905,7 +54905,7 @@
         <v>45033</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>45740.47288194444</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -55019,7 +55019,7 @@
         <v>45730.69143518519</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -55076,7 +55076,7 @@
         <v>45554.55707175926</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -55133,7 +55133,7 @@
         <v>44769.66864583334</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -55190,7 +55190,7 @@
         <v>44670.4190162037</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -55247,7 +55247,7 @@
         <v>44306</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55309,7 +55309,7 @@
         <v>45183</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55366,7 +55366,7 @@
         <v>44851</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55423,7 +55423,7 @@
         <v>45772.71221064815</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55480,7 +55480,7 @@
         <v>45215</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55537,7 +55537,7 @@
         <v>44854</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55594,7 +55594,7 @@
         <v>44778.69210648148</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55651,7 +55651,7 @@
         <v>44747</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55708,7 +55708,7 @@
         <v>45054</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>44832</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55822,7 +55822,7 @@
         <v>44960.60469907407</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55879,7 +55879,7 @@
         <v>45691.41101851852</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>45772.29622685185</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -55993,7 +55993,7 @@
         <v>45708.61761574074</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -56050,7 +56050,7 @@
         <v>44682.78430555556</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -56107,7 +56107,7 @@
         <v>44252</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -56164,7 +56164,7 @@
         <v>45587</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>45729.60859953704</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -56283,7 +56283,7 @@
         <v>45085.5309375</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         <v>45370</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56402,7 +56402,7 @@
         <v>45236.46369212963</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         <v>45055.43509259259</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56516,7 +56516,7 @@
         <v>44925</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>45735.59287037037</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56630,7 +56630,7 @@
         <v>45733.82105324074</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56687,7 +56687,7 @@
         <v>45075</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56744,7 +56744,7 @@
         <v>44528.91494212963</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56801,7 +56801,7 @@
         <v>44866.49827546296</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56858,7 +56858,7 @@
         <v>45735.36873842592</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -56915,7 +56915,7 @@
         <v>45561.62141203704</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -56972,7 +56972,7 @@
         <v>45764.6359837963</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -57029,7 +57029,7 @@
         <v>44596.66335648148</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -57091,7 +57091,7 @@
         <v>44549</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -57148,7 +57148,7 @@
         <v>44922</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -57205,7 +57205,7 @@
         <v>44145</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -57262,7 +57262,7 @@
         <v>45063</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57319,7 +57319,7 @@
         <v>45065.55917824074</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57381,7 +57381,7 @@
         <v>44767.60601851852</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57438,7 +57438,7 @@
         <v>44490.02482638889</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57495,7 +57495,7 @@
         <v>44490.03621527777</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57552,7 +57552,7 @@
         <v>44995</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57609,7 +57609,7 @@
         <v>45490.45342592592</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57671,7 +57671,7 @@
         <v>45469</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57728,7 +57728,7 @@
         <v>44459</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>44083</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>44452</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -57904,7 +57904,7 @@
         <v>44750.66068287037</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -57961,7 +57961,7 @@
         <v>44750</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -58018,7 +58018,7 @@
         <v>45338</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>44124</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -58137,7 +58137,7 @@
         <v>45082</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -58194,7 +58194,7 @@
         <v>45082.68922453704</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -58251,7 +58251,7 @@
         <v>44771</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58313,7 +58313,7 @@
         <v>44760</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58370,7 +58370,7 @@
         <v>44760</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>44816</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58484,7 +58484,7 @@
         <v>44813</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58541,7 +58541,7 @@
         <v>45089</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58598,7 +58598,7 @@
         <v>44376.50728009259</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58655,7 +58655,7 @@
         <v>45468.45877314815</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45261</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58769,7 +58769,7 @@
         <v>45259</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58826,7 +58826,7 @@
         <v>45253.61146990741</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -58883,7 +58883,7 @@
         <v>45740.47550925926</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -58940,7 +58940,7 @@
         <v>45740.47724537037</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -58997,7 +58997,7 @@
         <v>45344</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -59054,7 +59054,7 @@
         <v>45435.43466435185</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -59111,7 +59111,7 @@
         <v>45435.43820601852</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -59168,7 +59168,7 @@
         <v>45621.34425925926</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59230,7 +59230,7 @@
         <v>45621.35712962963</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59292,7 +59292,7 @@
         <v>45600.411875</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45548.72306712963</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59406,7 +59406,7 @@
         <v>45435.43123842592</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>45282</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>44938</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59577,7 +59577,7 @@
         <v>44260</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59639,7 +59639,7 @@
         <v>44753</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59696,7 +59696,7 @@
         <v>45231.34144675926</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59753,7 +59753,7 @@
         <v>45104</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59815,7 +59815,7 @@
         <v>44698</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -59877,7 +59877,7 @@
         <v>44992</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -59934,7 +59934,7 @@
         <v>45729.72851851852</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         <v>44483</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         <v>45054.54091435186</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         <v>45054</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -60167,7 +60167,7 @@
         <v>44777</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60224,7 +60224,7 @@
         <v>45104</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60281,7 +60281,7 @@
         <v>45394.58778935186</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60343,7 +60343,7 @@
         <v>45022.61003472222</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60400,7 +60400,7 @@
         <v>45668.67446759259</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60457,7 +60457,7 @@
         <v>45670.3079050926</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60514,7 +60514,7 @@
         <v>44218</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60571,7 +60571,7 @@
         <v>45007</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60628,7 +60628,7 @@
         <v>44599.58428240741</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60685,7 +60685,7 @@
         <v>45713.92623842593</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60742,7 +60742,7 @@
         <v>44743.59765046297</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60804,7 +60804,7 @@
         <v>44743.64592592593</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60866,7 +60866,7 @@
         <v>45640.57305555556</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -60923,7 +60923,7 @@
         <v>44326.61967592593</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -60980,7 +60980,7 @@
         <v>44858</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -61037,7 +61037,7 @@
         <v>45183</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -61094,7 +61094,7 @@
         <v>45638.5987037037</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -61156,7 +61156,7 @@
         <v>45453</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -61213,7 +61213,7 @@
         <v>45770</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -61270,7 +61270,7 @@
         <v>45310.40628472222</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -61327,7 +61327,7 @@
         <v>45310</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -61384,7 +61384,7 @@
         <v>44700.50659722222</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61441,7 +61441,7 @@
         <v>45254</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61498,7 +61498,7 @@
         <v>45089</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61555,7 +61555,7 @@
         <v>45159</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61612,7 +61612,7 @@
         <v>45322</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61669,7 +61669,7 @@
         <v>45414.58650462963</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61726,7 +61726,7 @@
         <v>45162</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61788,7 +61788,7 @@
         <v>45679</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61845,7 +61845,7 @@
         <v>45139</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -61902,7 +61902,7 @@
         <v>45019.28847222222</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -61959,7 +61959,7 @@
         <v>45082.69179398148</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -62016,7 +62016,7 @@
         <v>45482.53388888889</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -62073,7 +62073,7 @@
         <v>44956</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -62130,7 +62130,7 @@
         <v>44956</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -62187,7 +62187,7 @@
         <v>45084.57695601852</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -62249,7 +62249,7 @@
         <v>45257</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -62306,7 +62306,7 @@
         <v>44803</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62363,7 +62363,7 @@
         <v>44687</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62420,7 +62420,7 @@
         <v>44110</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62482,7 +62482,7 @@
         <v>44456</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62539,7 +62539,7 @@
         <v>44732</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62596,7 +62596,7 @@
         <v>45056</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62653,7 +62653,7 @@
         <v>45530</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62710,7 +62710,7 @@
         <v>45218.65849537037</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62767,7 +62767,7 @@
         <v>44817.56120370371</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62824,7 +62824,7 @@
         <v>44390</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -62881,7 +62881,7 @@
         <v>45022</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -62938,7 +62938,7 @@
         <v>45723</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -63000,7 +63000,7 @@
         <v>44841.52804398148</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -63062,7 +63062,7 @@
         <v>45518</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -63119,7 +63119,7 @@
         <v>45757.61421296297</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -63176,7 +63176,7 @@
         <v>45721.89123842592</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -63233,7 +63233,7 @@
         <v>45708</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -63295,7 +63295,7 @@
         <v>44934</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63352,7 +63352,7 @@
         <v>44778</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63409,7 +63409,7 @@
         <v>44581</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63466,7 +63466,7 @@
         <v>45376.55704861111</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63523,7 +63523,7 @@
         <v>45293.37263888889</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63580,7 +63580,7 @@
         <v>45245</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63637,7 +63637,7 @@
         <v>45245</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63694,7 +63694,7 @@
         <v>44956.65920138889</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63751,7 +63751,7 @@
         <v>44931.65626157408</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63808,7 +63808,7 @@
         <v>45460.45523148148</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63865,7 +63865,7 @@
         <v>45293</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -63922,7 +63922,7 @@
         <v>45726.48377314815</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -63979,7 +63979,7 @@
         <v>44321</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -64036,7 +64036,7 @@
         <v>45118</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -64098,7 +64098,7 @@
         <v>45723</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -64160,7 +64160,7 @@
         <v>45617.57439814815</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -64217,7 +64217,7 @@
         <v>45706.60130787037</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -64279,7 +64279,7 @@
         <v>44900</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -64336,7 +64336,7 @@
         <v>44714.92253472222</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64393,7 +64393,7 @@
         <v>44743.59504629629</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64455,7 +64455,7 @@
         <v>45245</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64512,7 +64512,7 @@
         <v>45356.47784722222</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64569,7 +64569,7 @@
         <v>45092</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64626,7 +64626,7 @@
         <v>44637</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64683,7 +64683,7 @@
         <v>44816</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64740,7 +64740,7 @@
         <v>45757.60658564815</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -64797,7 +64797,7 @@
         <v>45760.91174768518</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -64854,7 +64854,7 @@
         <v>45075.90703703704</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -64911,7 +64911,7 @@
         <v>45490.60572916667</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -64968,7 +64968,7 @@
         <v>45638.59979166667</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -65030,7 +65030,7 @@
         <v>45357</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -65087,7 +65087,7 @@
         <v>45058.78607638889</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -65144,7 +65144,7 @@
         <v>45600.86128472222</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>

--- a/Översikt NORRTÄLJE.xlsx
+++ b/Översikt NORRTÄLJE.xlsx
@@ -567,7 +567,7 @@
         <v>45135</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44757</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44249</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45757</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>44909</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45457</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45226</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45367</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45715</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44949</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45436</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>45190</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44263</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>44550</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>44467</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45600</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>45586.88145833334</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45638</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45688.38224537037</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>44846</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>44858</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>44447</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>45400.5958912037</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>44650</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>45847.48436342592</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45800</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>45748.6521875</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45831.53390046296</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>45068</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>44544</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45784.32179398148</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>45783.58123842593</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>44711</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>44545</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44336</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>44839</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>45847.47052083333</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>45898.62723379629</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>45722</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>44300</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>44749</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>44843</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>44279</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>45611.47233796296</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>45616.54866898148</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>44866</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>45821</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>44945</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44698</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>45847.47685185185</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>44743.64592592593</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44370</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>44489</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45723</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>45219</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>44763</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>45609.37094907407</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>44670</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>45446.35888888889</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>45226</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>45772.30234953704</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>45800</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>44868</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>44872</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>44573</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>44102</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44564.66387731482</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>44161</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>44363</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>44788.70217592592</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>44680</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>44778.92797453704</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>44695.43527777777</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>45784.54878472222</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>44855</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>44620</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>44956</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>45794.63298611111</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>45800</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>45146</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>45532</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>45803.62766203703</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>45687.34177083334</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>45754</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>44965</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>45826.46392361111</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>45741.38688657407</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>44704</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>44489</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>45798</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>45065</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>44207</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>44683</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>45841.5721875</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>45708</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>45450.63958333333</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>45468.45995370371</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>45841.56996527778</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>45474</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>45735.54510416667</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>44955.71322916666</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>45081</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>45082</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>45888.62712962963</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>44993</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>45092</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>44863</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>45280</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>45897.56356481482</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>45904.6575</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>45609.83747685186</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>45225</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>45205</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>44743.59504629629</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>44210</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>44209</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>44306</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>44642</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>44650.8699537037</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         <v>44540</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>44447</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>44833</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>44284.59546296296</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>44420</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>44420</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>44330</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>44097</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>44777</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>44728.73465277778</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44810.85092592592</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44552</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>44560</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>44470.72148148148</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>44634</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>44581.75819444445</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>44771</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>44111.45320601852</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>44477.94327546296</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>44380</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>44524</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>44574.42978009259</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>44516.72827546296</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>44103</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44868</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>44309.47061342592</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44834</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44400</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>44161</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44252</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44451</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>44496</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>44626</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>44690</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>44682.79203703703</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>44858</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>44244</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>44708</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>44642</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44776</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44103</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44746</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>44176</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>44214</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>44306</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>44727</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>44845.47585648148</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>44543</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44543</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>44495</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>44749.61980324074</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>44882</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>44224</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>44545.4189699074</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>44882.44732638889</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44314</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>44279</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>44300</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>44722</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>44742</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>44756.40881944444</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>44806.34577546296</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>44124</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>44294</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>44330</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>44330</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>44511.69885416667</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>44510</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>44447</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>44391.5580787037</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44435</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>44867</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>44571</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>44453</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>44511</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>44495</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>44201</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>44683</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>44201</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>44375</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>44539</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>44516.5275462963</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>44496</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>44414.81494212963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>44299</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>44380</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>44594.75950231482</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>44363.5784375</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>44712.83118055556</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>44769.62320601852</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>44572</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>44698</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>44251.43971064815</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>44397</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>44650.92714120371</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>44543</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>44543</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>44309</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>44760</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>44609</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>44817.70516203704</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>44725.49491898148</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>44427</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>44545</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>44545</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>44477</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>44845.47672453704</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>44270</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>44270</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>44621</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>44496.77542824074</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44526</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>44658</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>44100</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>44580</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>44584.91538194445</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>44678</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>44816.89569444444</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>44682.75924768519</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>44682.77616898148</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>44623</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>44665.66407407408</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>44880.68423611111</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>44637</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>44777</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>44735</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>44230</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>44230</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>44637</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>44655.45373842592</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>44105</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>44763.4182175926</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>44665.65474537037</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>44665.78351851852</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>44533</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>44132</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>44342</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>44704</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>44595</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>44466.37496527778</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>44543</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>44682.76528935185</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>44523.61635416667</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         <v>44376</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
         <v>44595</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>44370.72197916666</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>44725</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>44744</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>44735</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>44176</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>44815</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>44826</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>44326</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>44495</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>45075.91362268518</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>45075.91971064815</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>44764</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>45051.455</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>44098</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>45749</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>45362.62811342593</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>44868</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>44284</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45203.63303240741</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>44824.36069444445</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>44251</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45621.34813657407</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44419</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45772.3078125</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>44524</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>45625</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>45208</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>44879.70518518519</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>44379</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>44833.40876157407</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45730.35026620371</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45772.51127314815</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45405.57927083333</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>44272</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>44743.47407407407</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21665,7 +21665,7 @@
         <v>44315</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>45705.66126157407</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>45330.50098379629</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>44266</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>44376</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>45218</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>45772.30436342592</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>44300</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>44575.52831018518</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22212,7 +22212,7 @@
         <v>45273</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>45644.47878472223</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22326,7 +22326,7 @@
         <v>45356.4722800926</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>44231</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>44949</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>44285</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>44643</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>45086.3629050926</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>45253.55641203704</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>45737.43347222222</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>44949</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>44953.67443287037</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>45175</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>44963</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44840</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>45433.58431712963</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>45694.68207175926</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>45383</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45435</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45084.54459490741</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>44895</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>44350</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>44143</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>45397</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>44882</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>45473.94501157408</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45259</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>45455.33037037037</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45147.65222222222</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>45147.65311342593</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>45147</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45450.64208333333</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>45450</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45755.36583333334</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>45253.63089120371</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24232,7 +24232,7 @@
         <v>45776.62563657408</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>45316.60306712963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44556</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45223</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44272</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45239</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45776.47346064815</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45776.46369212963</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45776.59871527777</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44705.60626157407</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>45190.55609953704</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44845.48064814815</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>44470</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>45558.46283564815</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>44621</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45391.3395949074</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>45454.65774305556</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>44868.45741898148</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45485</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>44502</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>45104</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>45104</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>45783</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>45769</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44809</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>45202</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>45376.64532407407</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>45783.66429398148</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44510</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>45075.90270833333</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>45075.91042824074</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26014,7 +26014,7 @@
         <v>45075.91265046296</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>45075.92153935185</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>45576</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>44105</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>44962</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>45385.38146990741</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>45089</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45131.666875</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45549</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44866.63775462963</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>45187</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45735</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>45709.39361111111</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26760,7 +26760,7 @@
         <v>45418</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>45448.56746527777</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>45385.36243055556</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>45485.60261574074</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>45257</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
         <v>45536</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>45418.6968287037</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>45170</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>44362.37172453704</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>44525</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>44546</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45572.57828703704</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>44516</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>44516.40674768519</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27573,7 +27573,7 @@
         <v>45063.35880787037</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>44956</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>45468.45541666666</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>45468.45747685185</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
         <v>45460.44347222222</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>44642.55565972222</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>44472</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>45785.65300925926</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>45610.39271990741</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>44153</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         <v>45537</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>45579</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>45119.57728009259</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28314,7 +28314,7 @@
         <v>44769.66039351852</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>45463.80486111111</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>45831.56521990741</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>45457</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>45271</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28604,7 +28604,7 @@
         <v>45642.64634259259</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>45468.45628472222</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28718,7 +28718,7 @@
         <v>45352.74090277778</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45260</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28832,7 +28832,7 @@
         <v>44637</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>44325</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28951,7 +28951,7 @@
         <v>44578</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29008,7 +29008,7 @@
         <v>44461</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>45443</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>45408.57707175926</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>44470.72987268519</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>44834.38636574074</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>44113</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29355,7 +29355,7 @@
         <v>45245</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>44333</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>45786.55645833333</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29531,7 +29531,7 @@
         <v>45715</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45635.88849537037</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>44108</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>44953.69298611111</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>45533</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45547</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>44139.54078703704</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45524</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>44350</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45341.39853009259</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>44584.91001157407</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45177</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>45721.88684027778</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>45483.57244212963</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>44100</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>44869</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45600.4558912037</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45540</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>45272.64479166667</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>45272</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>44637</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>44474.62141203704</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>45169</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>45385.37922453704</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>45729.7271875</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>44952.57989583333</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44795</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>45469</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>45469</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>45075</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>45075</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>45075.90934027778</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>45713</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>45089</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>45436</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>45518</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>45735</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>45475.61896990741</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>45203.83891203703</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45589.68289351852</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>44596</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>45636.38974537037</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>44395</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>44708.67822916667</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>45840.70885416667</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>45798.66767361111</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32178,7 +32178,7 @@
         <v>44132</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32235,7 +32235,7 @@
         <v>45786</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32292,7 +32292,7 @@
         <v>45639.45166666667</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>45798.67082175926</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32406,7 +32406,7 @@
         <v>45798</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>45798.66104166667</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45797.58399305555</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>44607</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>45639.47385416667</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32691,7 +32691,7 @@
         <v>45586</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>45644.90815972222</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>44540</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32862,7 +32862,7 @@
         <v>45797.58350694444</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32919,7 +32919,7 @@
         <v>45414.65855324074</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32976,7 +32976,7 @@
         <v>44425</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>44425</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>45450.64643518518</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>44133</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33209,7 +33209,7 @@
         <v>45640.60240740741</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>45600.47275462963</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>44580</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>45089</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>45478.42887731481</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>45113</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>45113</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>44673</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>44985</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44904</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>45800</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>44648</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>44643</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33950,7 +33950,7 @@
         <v>45800</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>45800</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>44143</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34121,7 +34121,7 @@
         <v>44901</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34178,7 +34178,7 @@
         <v>45799</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>45800</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>45800</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34349,7 +34349,7 @@
         <v>45803.4675</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44816</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34463,7 +34463,7 @@
         <v>45456</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>45617.58453703704</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45224</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>45800</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34696,7 +34696,7 @@
         <v>44592</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>45803.69228009259</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>45559.54706018518</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>45121</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>45075.91148148148</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>45804.74479166666</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>45726.48152777777</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>45549</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44813</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>45075</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>45803.66587962963</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>44145</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>45586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>44649</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>44155.69458333333</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>45610.47414351852</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45847.37414351852</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>45232</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>44993.66707175926</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>45735.36594907408</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>44124</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45729.71065972222</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35965,7 +35965,7 @@
         <v>44511.70518518519</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36022,7 +36022,7 @@
         <v>45531</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>45376.55484953704</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36136,7 +36136,7 @@
         <v>44977</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>45386.34175925926</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36250,7 +36250,7 @@
         <v>45183</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36307,7 +36307,7 @@
         <v>44525</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44644</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>44635</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>44656</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45687.5038425926</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>45810.42393518519</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44670</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>45695.57881944445</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45608</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45617.62358796296</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>45069</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36974,7 +36974,7 @@
         <v>45442.45686342593</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37031,7 +37031,7 @@
         <v>45208.58004629629</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37088,7 +37088,7 @@
         <v>45155</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37145,7 +37145,7 @@
         <v>45790.81410879629</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>44938</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>45810.5333912037</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45427.88731481481</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45202.65660879629</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>45664</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>45810.45236111111</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         <v>45810.45263888889</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>44624.59434027778</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>44179</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>44162</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37777,7 +37777,7 @@
         <v>45810.45633101852</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45147.65407407407</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>44687</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45811.60451388889</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>45757.65178240741</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38067,7 +38067,7 @@
         <v>45775.41451388889</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>44959.74533564815</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>44902</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38238,7 +38238,7 @@
         <v>44697</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38295,7 +38295,7 @@
         <v>45735</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38352,7 +38352,7 @@
         <v>45146</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38414,7 +38414,7 @@
         <v>45522.44414351852</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>45687</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38533,7 +38533,7 @@
         <v>45813.63650462963</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45813.66961805556</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45813.6799537037</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45813.4709375</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>45685.44592592592</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>45757.62482638889</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38880,7 +38880,7 @@
         <v>45534.38240740741</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>44923.90159722222</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>44183</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45174.68702546296</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>45412.4104050926</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45376.55638888889</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>45686.65545138889</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>45721.40780092592</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>44585</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>45709.40231481481</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>44704</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39532,7 +39532,7 @@
         <v>45817.2565625</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39589,7 +39589,7 @@
         <v>45817.30329861111</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>45817.31085648148</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>45817.31708333334</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39760,7 +39760,7 @@
         <v>45817.31986111111</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39817,7 +39817,7 @@
         <v>45817.33503472222</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>45747.63471064815</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39936,7 +39936,7 @@
         <v>45706.40086805556</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>45670.65921296296</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40055,7 +40055,7 @@
         <v>45817.291875</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40112,7 +40112,7 @@
         <v>45817.32538194444</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40169,7 +40169,7 @@
         <v>45552.52827546297</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40226,7 +40226,7 @@
         <v>45208</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40283,7 +40283,7 @@
         <v>45208</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>45817.25471064815</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45237</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45145.63584490741</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>44945.67409722223</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40568,7 +40568,7 @@
         <v>44937</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40625,7 +40625,7 @@
         <v>45817.34083333334</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45145.51</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>45700</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40801,7 +40801,7 @@
         <v>45215</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40858,7 +40858,7 @@
         <v>44680</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40915,7 +40915,7 @@
         <v>44629</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40977,7 +40977,7 @@
         <v>44617</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41034,7 +41034,7 @@
         <v>45692</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41091,7 +41091,7 @@
         <v>45188.41637731482</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41153,7 +41153,7 @@
         <v>45245</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>45155</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41267,7 +41267,7 @@
         <v>45254</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41324,7 +41324,7 @@
         <v>45260.43225694444</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41381,7 +41381,7 @@
         <v>44708</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>44708.36708333333</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>45260.4333449074</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>44746.58530092592</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41614,7 +41614,7 @@
         <v>44714.56040509259</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41671,7 +41671,7 @@
         <v>45824.37275462963</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>45679</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>44684</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>45127.69371527778</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41909,7 +41909,7 @@
         <v>45245</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41966,7 +41966,7 @@
         <v>44743.67418981482</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42028,7 +42028,7 @@
         <v>44732</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         <v>45208.70996527778</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42142,7 +42142,7 @@
         <v>45205</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45629.65143518519</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>44181</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42318,7 +42318,7 @@
         <v>44888</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42375,7 +42375,7 @@
         <v>44867.62090277778</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42432,7 +42432,7 @@
         <v>45701.44372685185</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42489,7 +42489,7 @@
         <v>45223</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42546,7 +42546,7 @@
         <v>44722</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42603,7 +42603,7 @@
         <v>45831.51659722222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>45831.65079861111</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42722,7 +42722,7 @@
         <v>44611</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42779,7 +42779,7 @@
         <v>45128</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42836,7 +42836,7 @@
         <v>44986.5887962963</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>45048</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42950,7 +42950,7 @@
         <v>45831.4844212963</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43007,7 +43007,7 @@
         <v>45832.66385416667</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43064,7 +43064,7 @@
         <v>45831.54618055555</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>45740.47055555556</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43178,7 +43178,7 @@
         <v>44775</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43235,7 +43235,7 @@
         <v>44799.65013888889</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43292,7 +43292,7 @@
         <v>45223</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43349,7 +43349,7 @@
         <v>45680.42665509259</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45293</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>45219.56697916667</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>45834</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43582,7 +43582,7 @@
         <v>45876.45253472222</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>45728.38409722222</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>44813.59915509259</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43758,7 +43758,7 @@
         <v>44325</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>45834.6447337963</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>45699.46283564815</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>45070</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43986,7 +43986,7 @@
         <v>45834.65538194445</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44043,7 +44043,7 @@
         <v>44693</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>44963</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44157,7 +44157,7 @@
         <v>45112</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44214,7 +44214,7 @@
         <v>44266</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44271,7 +44271,7 @@
         <v>44266</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44328,7 +44328,7 @@
         <v>44867</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44385,7 +44385,7 @@
         <v>44778</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44442,7 +44442,7 @@
         <v>45623.62563657408</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44504,7 +44504,7 @@
         <v>45075</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44561,7 +44561,7 @@
         <v>45712</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44623,7 +44623,7 @@
         <v>45348.46300925926</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44685,7 +44685,7 @@
         <v>44803</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44742,7 +44742,7 @@
         <v>45581</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44799,7 +44799,7 @@
         <v>45254.41509259259</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44856,7 +44856,7 @@
         <v>45835.68076388889</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44913,7 +44913,7 @@
         <v>45693</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -44970,7 +44970,7 @@
         <v>45835.4928125</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45032,7 +45032,7 @@
         <v>44690</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>45730.42851851852</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>45092</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45208,7 +45208,7 @@
         <v>45092</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45265,7 +45265,7 @@
         <v>45880.46524305556</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>45880.46372685185</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45835.46034722222</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>45075.90817129629</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>45835</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45565,7 +45565,7 @@
         <v>45837</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45837.94081018519</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45679,7 +45679,7 @@
         <v>45880.46189814815</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45741,7 +45741,7 @@
         <v>44797</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>45838.43261574074</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45860,7 +45860,7 @@
         <v>45730.69502314815</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45917,7 +45917,7 @@
         <v>44925</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>44243.33587962963</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46031,7 +46031,7 @@
         <v>45636.41572916666</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46088,7 +46088,7 @@
         <v>45020</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46145,7 +46145,7 @@
         <v>45139.51457175926</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46202,7 +46202,7 @@
         <v>45614.39627314815</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46259,7 +46259,7 @@
         <v>44704</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46316,7 +46316,7 @@
         <v>45022</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46373,7 +46373,7 @@
         <v>44903</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46430,7 +46430,7 @@
         <v>45168.44489583333</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46492,7 +46492,7 @@
         <v>44790</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46549,7 +46549,7 @@
         <v>45414</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46606,7 +46606,7 @@
         <v>44111.44373842593</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46663,7 +46663,7 @@
         <v>45411.54768518519</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46725,7 +46725,7 @@
         <v>44953.70481481482</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46782,7 +46782,7 @@
         <v>45837.93730324074</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46839,7 +46839,7 @@
         <v>44806.41576388889</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46896,7 +46896,7 @@
         <v>45519</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>45107.42538194444</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47010,7 +47010,7 @@
         <v>45111</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>45840.62755787037</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>44783</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>44266</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47238,7 +47238,7 @@
         <v>44785</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47300,7 +47300,7 @@
         <v>45394.72869212963</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47357,7 +47357,7 @@
         <v>45839.62398148148</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         <v>45840.67829861111</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>44974</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47528,7 +47528,7 @@
         <v>44771</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47585,7 +47585,7 @@
         <v>45609.70778935185</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47647,7 +47647,7 @@
         <v>45609.85146990741</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47704,7 +47704,7 @@
         <v>44743.59331018518</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45427.89121527778</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47823,7 +47823,7 @@
         <v>45839</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47880,7 +47880,7 @@
         <v>45587.62565972222</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -47937,7 +47937,7 @@
         <v>45601.56726851852</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -47994,7 +47994,7 @@
         <v>45177.61498842593</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48051,7 +48051,7 @@
         <v>45635.44788194444</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48108,7 +48108,7 @@
         <v>44763.40914351852</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>45630.52866898148</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>45728.38924768518</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48279,7 +48279,7 @@
         <v>45667.49878472222</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>45293</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48398,7 +48398,7 @@
         <v>45019.3959837963</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>44097</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48512,7 +48512,7 @@
         <v>45345.6059837963</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>45631.73952546297</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48626,7 +48626,7 @@
         <v>45631.74673611111</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48683,7 +48683,7 @@
         <v>44769</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48740,7 +48740,7 @@
         <v>44495.5893287037</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48797,7 +48797,7 @@
         <v>44749.55258101852</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48854,7 +48854,7 @@
         <v>44782</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>45882.59722222222</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -48968,7 +48968,7 @@
         <v>44217.40149305556</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>44732</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49082,7 +49082,7 @@
         <v>45401.3653125</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49139,7 +49139,7 @@
         <v>44719</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>44980</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49253,7 +49253,7 @@
         <v>45700</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49310,7 +49310,7 @@
         <v>45208.69671296296</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49367,7 +49367,7 @@
         <v>45238</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49424,7 +49424,7 @@
         <v>44698</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49481,7 +49481,7 @@
         <v>45841.74596064815</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49538,7 +49538,7 @@
         <v>45841.35611111111</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49595,7 +49595,7 @@
         <v>45469</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49652,7 +49652,7 @@
         <v>45743.44953703704</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49709,7 +49709,7 @@
         <v>45707.84997685185</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49766,7 +49766,7 @@
         <v>44777</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49823,7 +49823,7 @@
         <v>45085</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -49880,7 +49880,7 @@
         <v>45243.45289351852</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -49942,7 +49942,7 @@
         <v>44146</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -49999,7 +49999,7 @@
         <v>45884.48696759259</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50056,7 +50056,7 @@
         <v>44621</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50113,7 +50113,7 @@
         <v>44760</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50170,7 +50170,7 @@
         <v>45042.74291666667</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50227,7 +50227,7 @@
         <v>44375</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50284,7 +50284,7 @@
         <v>45219</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50341,7 +50341,7 @@
         <v>45442</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45841.5737962963</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50455,7 +50455,7 @@
         <v>45068.51783564815</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50512,7 +50512,7 @@
         <v>45532</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50569,7 +50569,7 @@
         <v>45063</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50626,7 +50626,7 @@
         <v>45212</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50683,7 +50683,7 @@
         <v>45706.61178240741</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>44398</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50807,7 +50807,7 @@
         <v>45191</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>44510.51422453704</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -50931,7 +50931,7 @@
         <v>44815.74539351852</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>44380.77346064815</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51045,7 +51045,7 @@
         <v>45842.46885416667</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>45771</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51159,7 +51159,7 @@
         <v>45740.47288194444</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51216,7 +51216,7 @@
         <v>45730.69143518519</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51273,7 +51273,7 @@
         <v>45554.55707175926</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         <v>44670.4190162037</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51387,7 +51387,7 @@
         <v>44851</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51444,7 +51444,7 @@
         <v>45772.71221064815</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51501,7 +51501,7 @@
         <v>45215</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51558,7 +51558,7 @@
         <v>45640.58716435185</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51615,7 +51615,7 @@
         <v>45054</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>45575</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51729,7 +51729,7 @@
         <v>45691.41101851852</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -51786,7 +51786,7 @@
         <v>45772.29622685185</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -51843,7 +51843,7 @@
         <v>45708.61761574074</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -51900,7 +51900,7 @@
         <v>45729.60859953704</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45328.46336805556</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52019,7 +52019,7 @@
         <v>45589.6756712963</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52076,7 +52076,7 @@
         <v>45236.46369212963</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>45055.43509259259</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52190,7 +52190,7 @@
         <v>45735.59287037037</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52247,7 +52247,7 @@
         <v>45075</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45735.36873842592</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45764.6359837963</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52418,7 +52418,7 @@
         <v>44596.66335648148</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52480,7 +52480,7 @@
         <v>45721.65858796296</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -52537,7 +52537,7 @@
         <v>44549</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -52594,7 +52594,7 @@
         <v>45456</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -52651,7 +52651,7 @@
         <v>44145</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -52708,7 +52708,7 @@
         <v>45063</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -52765,7 +52765,7 @@
         <v>45065.55917824074</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>45490.45342592592</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -52889,7 +52889,7 @@
         <v>44152</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -52951,7 +52951,7 @@
         <v>45469</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53008,7 +53008,7 @@
         <v>44459</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53070,7 +53070,7 @@
         <v>45888.60714120371</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53127,7 +53127,7 @@
         <v>44452</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -53184,7 +53184,7 @@
         <v>45581</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -53241,7 +53241,7 @@
         <v>44124</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -53303,7 +53303,7 @@
         <v>45531</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -53360,7 +53360,7 @@
         <v>44760</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -53417,7 +53417,7 @@
         <v>44760</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -53474,7 +53474,7 @@
         <v>44816</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -53531,7 +53531,7 @@
         <v>44319</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -53588,7 +53588,7 @@
         <v>45089</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -53645,7 +53645,7 @@
         <v>44691.5652662037</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -53702,7 +53702,7 @@
         <v>44326</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -53759,7 +53759,7 @@
         <v>44908.77368055555</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -53816,7 +53816,7 @@
         <v>45152</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -53873,7 +53873,7 @@
         <v>45845</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -53930,7 +53930,7 @@
         <v>45844.62609953704</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -53987,7 +53987,7 @@
         <v>45740.47550925926</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -54044,7 +54044,7 @@
         <v>45740.47724537037</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -54101,7 +54101,7 @@
         <v>45344</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -54158,7 +54158,7 @@
         <v>44251</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -54215,7 +54215,7 @@
         <v>45548.72306712963</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -54272,7 +54272,7 @@
         <v>45844.91234953704</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -54334,7 +54334,7 @@
         <v>45518</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -54391,7 +54391,7 @@
         <v>45890.56001157407</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -54448,7 +54448,7 @@
         <v>45231.34144675926</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -54505,7 +54505,7 @@
         <v>45104</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>45033</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -54624,7 +54624,7 @@
         <v>44992</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -54681,7 +54681,7 @@
         <v>44483</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -54738,7 +54738,7 @@
         <v>45748</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -54795,7 +54795,7 @@
         <v>44769.66864583334</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -54852,7 +54852,7 @@
         <v>45054.54091435186</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -54909,7 +54909,7 @@
         <v>45054</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -54966,7 +54966,7 @@
         <v>45890.68083333333</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -55023,7 +55023,7 @@
         <v>44306</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -55085,7 +55085,7 @@
         <v>45183</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -55142,7 +55142,7 @@
         <v>45104</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -55199,7 +55199,7 @@
         <v>45894.48322916667</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -55256,7 +55256,7 @@
         <v>45022.61003472222</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -55313,7 +55313,7 @@
         <v>45893</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -55370,7 +55370,7 @@
         <v>45894.68864583333</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -55427,7 +55427,7 @@
         <v>45893</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -55484,7 +55484,7 @@
         <v>44854</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -55541,7 +55541,7 @@
         <v>44778.69210648148</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -55598,7 +55598,7 @@
         <v>44747</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -55655,7 +55655,7 @@
         <v>44832</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -55712,7 +55712,7 @@
         <v>44960.60469907407</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -55769,7 +55769,7 @@
         <v>45894.6353125</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -55826,7 +55826,7 @@
         <v>45852.58030092593</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -55883,7 +55883,7 @@
         <v>45894.70854166667</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -55940,7 +55940,7 @@
         <v>45894.71101851852</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -55997,7 +55997,7 @@
         <v>45895.3867824074</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -56054,7 +56054,7 @@
         <v>44682.78430555556</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -56111,7 +56111,7 @@
         <v>44252</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -56168,7 +56168,7 @@
         <v>45853</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -56225,7 +56225,7 @@
         <v>45895.38778935185</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -56282,7 +56282,7 @@
         <v>45587</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -56339,7 +56339,7 @@
         <v>45085.5309375</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -56401,7 +56401,7 @@
         <v>45853</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -56458,7 +56458,7 @@
         <v>45896.38466435186</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -56515,7 +56515,7 @@
         <v>45370</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -56572,7 +56572,7 @@
         <v>45897.50802083333</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -56629,7 +56629,7 @@
         <v>45897.51077546296</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -56686,7 +56686,7 @@
         <v>45897.51328703704</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -56743,7 +56743,7 @@
         <v>45855.69387731481</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -56805,7 +56805,7 @@
         <v>45898.54921296296</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -56862,7 +56862,7 @@
         <v>45898.61054398148</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -56919,7 +56919,7 @@
         <v>45898.62625</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -56976,7 +56976,7 @@
         <v>45898.38552083333</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -57038,7 +57038,7 @@
         <v>45898.40480324074</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -57100,7 +57100,7 @@
         <v>45898.45636574074</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -57157,7 +57157,7 @@
         <v>45855.57033564815</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -57219,7 +57219,7 @@
         <v>45855.68413194444</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -57281,7 +57281,7 @@
         <v>44925</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -57338,7 +57338,7 @@
         <v>45898.68826388889</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -57395,7 +57395,7 @@
         <v>45733.82105324074</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -57452,7 +57452,7 @@
         <v>44528.91494212963</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -57509,7 +57509,7 @@
         <v>44866.49827546296</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -57566,7 +57566,7 @@
         <v>45561.62141203704</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -57623,7 +57623,7 @@
         <v>45898.45976851852</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -57685,7 +57685,7 @@
         <v>45898.37636574074</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -57747,7 +57747,7 @@
         <v>44922</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45898.5315625</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -57861,7 +57861,7 @@
         <v>45898.62373842593</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -57918,7 +57918,7 @@
         <v>44767.60601851852</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -57975,7 +57975,7 @@
         <v>44490.02482638889</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -58032,7 +58032,7 @@
         <v>44490.03621527777</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -58089,7 +58089,7 @@
         <v>44995</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -58146,7 +58146,7 @@
         <v>45886</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -58203,7 +58203,7 @@
         <v>44750.66068287037</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -58260,7 +58260,7 @@
         <v>44750</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -58317,7 +58317,7 @@
         <v>45338</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -58374,7 +58374,7 @@
         <v>45082</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -58431,7 +58431,7 @@
         <v>45082.68922453704</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -58488,7 +58488,7 @@
         <v>44771</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -58550,7 +58550,7 @@
         <v>45903.47270833333</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -58612,7 +58612,7 @@
         <v>45903.61431712963</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -58674,7 +58674,7 @@
         <v>44813</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -58731,7 +58731,7 @@
         <v>44376.50728009259</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -58788,7 +58788,7 @@
         <v>45468.45877314815</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -58845,7 +58845,7 @@
         <v>45903.47456018518</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -58907,7 +58907,7 @@
         <v>45261</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -58964,7 +58964,7 @@
         <v>45259</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -59021,7 +59021,7 @@
         <v>45253.61146990741</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -59078,7 +59078,7 @@
         <v>45435.43466435185</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -59135,7 +59135,7 @@
         <v>45435.43820601852</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -59192,7 +59192,7 @@
         <v>45621.34425925926</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -59254,7 +59254,7 @@
         <v>45621.35712962963</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -59316,7 +59316,7 @@
         <v>45840</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -59373,7 +59373,7 @@
         <v>45600.411875</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -59430,7 +59430,7 @@
         <v>45435.43123842592</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -59487,7 +59487,7 @@
         <v>45282</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -59544,7 +59544,7 @@
         <v>44938</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -59601,7 +59601,7 @@
         <v>44260</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -59663,7 +59663,7 @@
         <v>45888</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -59720,7 +59720,7 @@
         <v>45776.47122685185</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -59777,7 +59777,7 @@
         <v>44753</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -59834,7 +59834,7 @@
         <v>44698</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -59896,7 +59896,7 @@
         <v>45729.72851851852</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -59958,7 +59958,7 @@
         <v>45868.62267361111</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -60015,7 +60015,7 @@
         <v>44777</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -60072,7 +60072,7 @@
         <v>45668.67446759259</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -60129,7 +60129,7 @@
         <v>45670.3079050926</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -60186,7 +60186,7 @@
         <v>44218</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -60243,7 +60243,7 @@
         <v>45007</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -60300,7 +60300,7 @@
         <v>44599.58428240741</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -60357,7 +60357,7 @@
         <v>45910.5819212963</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -60414,7 +60414,7 @@
         <v>45446.4287962963</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -60471,7 +60471,7 @@
         <v>45713.92623842593</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -60528,7 +60528,7 @@
         <v>45525</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -60585,7 +60585,7 @@
         <v>44743.59765046297</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -60647,7 +60647,7 @@
         <v>45908</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -60704,7 +60704,7 @@
         <v>45910</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -60761,7 +60761,7 @@
         <v>45640.57305555556</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -60818,7 +60818,7 @@
         <v>44326.61967592593</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -60875,7 +60875,7 @@
         <v>44858</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -60932,7 +60932,7 @@
         <v>45183</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -60989,7 +60989,7 @@
         <v>45859</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -61046,7 +61046,7 @@
         <v>45859</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -61103,7 +61103,7 @@
         <v>45638.5987037037</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -61165,7 +61165,7 @@
         <v>45453</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -61222,7 +61222,7 @@
         <v>45770</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -61279,7 +61279,7 @@
         <v>45310.40628472222</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -61336,7 +61336,7 @@
         <v>45310</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -61393,7 +61393,7 @@
         <v>44700.50659722222</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -61450,7 +61450,7 @@
         <v>45254</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -61507,7 +61507,7 @@
         <v>45089</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -61564,7 +61564,7 @@
         <v>45159</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -61621,7 +61621,7 @@
         <v>45322</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -61678,7 +61678,7 @@
         <v>45414.58650462963</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -61735,7 +61735,7 @@
         <v>45162</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -61797,7 +61797,7 @@
         <v>45679</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -61854,7 +61854,7 @@
         <v>45139</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -61911,7 +61911,7 @@
         <v>45019.28847222222</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -61968,7 +61968,7 @@
         <v>45082.69179398148</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -62025,7 +62025,7 @@
         <v>45482.53388888889</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -62082,7 +62082,7 @@
         <v>44956</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -62139,7 +62139,7 @@
         <v>44956</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -62196,7 +62196,7 @@
         <v>45084.57695601852</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -62258,7 +62258,7 @@
         <v>45257</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -62315,7 +62315,7 @@
         <v>44803</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -62372,7 +62372,7 @@
         <v>44687</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -62429,7 +62429,7 @@
         <v>44110</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -62491,7 +62491,7 @@
         <v>44456</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -62548,7 +62548,7 @@
         <v>44732</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -62605,7 +62605,7 @@
         <v>45056</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -62662,7 +62662,7 @@
         <v>45530</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -62719,7 +62719,7 @@
         <v>45218.65849537037</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -62776,7 +62776,7 @@
         <v>44817.56120370371</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -62833,7 +62833,7 @@
         <v>44390</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -62890,7 +62890,7 @@
         <v>45022</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -62947,7 +62947,7 @@
         <v>45723</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -63009,7 +63009,7 @@
         <v>44841.52804398148</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -63071,7 +63071,7 @@
         <v>45518</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -63128,7 +63128,7 @@
         <v>45757.61421296297</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -63185,7 +63185,7 @@
         <v>45721.89123842592</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -63242,7 +63242,7 @@
         <v>45708</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -63304,7 +63304,7 @@
         <v>44934</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -63361,7 +63361,7 @@
         <v>44778</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -63418,7 +63418,7 @@
         <v>44581</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -63475,7 +63475,7 @@
         <v>45376.55704861111</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -63532,7 +63532,7 @@
         <v>45293.37263888889</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -63589,7 +63589,7 @@
         <v>45245</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -63646,7 +63646,7 @@
         <v>45245</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -63703,7 +63703,7 @@
         <v>44956.65920138889</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -63760,7 +63760,7 @@
         <v>44931.65626157408</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -63817,7 +63817,7 @@
         <v>45460.45523148148</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -63874,7 +63874,7 @@
         <v>45293</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -63931,7 +63931,7 @@
         <v>45726.48377314815</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -63988,7 +63988,7 @@
         <v>44321</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -64045,7 +64045,7 @@
         <v>45118</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -64107,7 +64107,7 @@
         <v>45723</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -64169,7 +64169,7 @@
         <v>45617.57439814815</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -64226,7 +64226,7 @@
         <v>45706.60130787037</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -64288,7 +64288,7 @@
         <v>44900</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -64345,7 +64345,7 @@
         <v>44714.92253472222</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -64402,7 +64402,7 @@
         <v>45245</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -64459,7 +64459,7 @@
         <v>45356.47784722222</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -64516,7 +64516,7 @@
         <v>45092</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -64573,7 +64573,7 @@
         <v>44637</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -64630,7 +64630,7 @@
         <v>44816</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -64687,7 +64687,7 @@
         <v>45757.60658564815</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -64744,7 +64744,7 @@
         <v>45760.91174768518</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -64801,7 +64801,7 @@
         <v>45075.90703703704</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -64858,7 +64858,7 @@
         <v>45490.60572916667</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -64915,7 +64915,7 @@
         <v>45638.59979166667</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -64977,7 +64977,7 @@
         <v>45357</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -65034,7 +65034,7 @@
         <v>45058.78607638889</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -65091,7 +65091,7 @@
         <v>45600.86128472222</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>

--- a/Översikt NORRTÄLJE.xlsx
+++ b/Översikt NORRTÄLJE.xlsx
@@ -567,7 +567,7 @@
         <v>45135</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>44757</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>44249</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>45757</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         <v>44909</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>45457</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>45226</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>45367</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>45715</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>44869</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>44949</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>45436</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>45190</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>44263</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>44550</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>44467</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45600</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>45586.88145833334</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>45638</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>45688.38224537037</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>44846</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>44858</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>44447</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>45400.5958912037</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>44650</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>45847.48436342592</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45800</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>45748.6521875</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>45831.53390046296</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>45068</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>44544</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         <v>45784.32179398148</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>45783.58123842593</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>44711</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>44545</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44336</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>44839</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>45847.47052083333</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4310,7 +4310,7 @@
         <v>45898.62723379629</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4398,7 +4398,7 @@
         <v>45722</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>44300</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>44749</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4673,7 +4673,7 @@
         <v>44843</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>44279</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>45611.47233796296</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>45616.54866898148</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>44866</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>45821</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>44945</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>44698</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>45847.47685185185</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>44743.64592592593</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>44370</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>44489</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5733,7 +5733,7 @@
         <v>45723</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
         <v>45219</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>44763</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>45609.37094907407</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6095,7 +6095,7 @@
         <v>44670</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>45446.35888888889</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>45226</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>45772.30234953704</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>45800</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>44868</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>44872</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>44573</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>44102</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44564.66387731482</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>44161</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         <v>44363</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>44788.70217592592</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>44680</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7309,7 +7309,7 @@
         <v>44778.92797453704</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>44695.43527777777</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>45784.54878472222</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>44855</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         <v>44620</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
         <v>44956</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>45794.63298611111</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>45800</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>45146</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8074,7 +8074,7 @@
         <v>45532</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>45803.62766203703</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>45687.34177083334</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8347,7 +8347,7 @@
         <v>45754</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>44965</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
         <v>45826.46392361111</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>45741.38688657407</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>44704</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>44489</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>45798</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>45065</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>44207</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>44683</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>45841.5721875</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>45708</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>45450.63958333333</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>45468.45995370371</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>45841.56996527778</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         <v>45474</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>45735.54510416667</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>44955.71322916666</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>45081</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>45082</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>45888.62712962963</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>44993</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>45092</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>44863</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>45280</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>45897.56356481482</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>45904.6575</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10680,7 +10680,7 @@
         <v>45609.83747685186</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>45225</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>45205</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>44743.59504629629</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>44210</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11082,7 +11082,7 @@
         <v>44209</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
         <v>44306</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         <v>44642</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>44650.8699537037</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11315,7 +11315,7 @@
         <v>44540</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>44447</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>44833</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>44284.59546296296</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>44420</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>44420</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>44330</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>44097</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>44777</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>44728.73465277778</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44810.85092592592</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44552</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>44560</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         <v>44470.72148148148</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>44634</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12190,7 +12190,7 @@
         <v>44581.75819444445</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>44771</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v>44111.45320601852</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12361,7 +12361,7 @@
         <v>44477.94327546296</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>44380</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>44524</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>44574.42978009259</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>44516.72827546296</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>44103</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44868</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         <v>44309.47061342592</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44834</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44400</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>44161</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44252</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44451</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>44496</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>44626</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>44690</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>44682.79203703703</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>44858</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>44244</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>44708</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>44642</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44776</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44103</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13692,7 +13692,7 @@
         <v>44746</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>44176</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13806,7 +13806,7 @@
         <v>44214</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>44306</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13920,7 +13920,7 @@
         <v>44727</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13977,7 +13977,7 @@
         <v>44845.47585648148</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14034,7 +14034,7 @@
         <v>44543</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44543</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>44495</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>44749.61980324074</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>44882</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>44224</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14376,7 +14376,7 @@
         <v>44545.4189699074</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>44882.44732638889</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>44314</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>44279</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>44300</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>44722</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>44742</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14780,7 +14780,7 @@
         <v>44756.40881944444</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>44806.34577546296</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>44124</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>44294</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15008,7 +15008,7 @@
         <v>44330</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>44330</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15122,7 +15122,7 @@
         <v>44511.69885416667</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>44510</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>44447</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>44391.5580787037</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>44435</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15407,7 +15407,7 @@
         <v>44867</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         <v>44571</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>44453</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>44511</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>44495</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>44201</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>44683</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
         <v>44201</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>44375</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>44539</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>44516.5275462963</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>44496</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>44414.81494212963</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>44299</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>44380</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>44594.75950231482</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>44363.5784375</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>44712.83118055556</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>44769.62320601852</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16490,7 +16490,7 @@
         <v>44572</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16547,7 +16547,7 @@
         <v>44698</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>44251.43971064815</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>44397</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>44650.92714120371</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>44543</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16837,7 +16837,7 @@
         <v>44543</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>44309</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>44760</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>44609</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>44817.70516203704</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>44725.49491898148</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>44427</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         <v>44545</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>44545</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>44477</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>44845.47672453704</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>44270</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>44270</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>44621</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>44496.77542824074</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>44526</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>44658</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>44100</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>44580</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>44584.91538194445</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>44678</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>44816.89569444444</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18101,7 +18101,7 @@
         <v>44682.75924768519</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>44682.77616898148</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18215,7 +18215,7 @@
         <v>44623</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>44665.66407407408</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>44880.68423611111</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>44637</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>44777</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>44735</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>44230</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>44230</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18671,7 +18671,7 @@
         <v>44637</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>44655.45373842592</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>44105</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18842,7 +18842,7 @@
         <v>44763.4182175926</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>44665.65474537037</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>44665.78351851852</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>44533</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>44132</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>44342</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>44704</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>44595</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>44466.37496527778</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>44543</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>44682.76528935185</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>44523.61635416667</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         <v>44376</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
         <v>44595</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>44370.72197916666</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>44725</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>44744</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>44735</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>44176</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>44815</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>44826</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>44326</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>44495</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>45075.91362268518</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20225,7 +20225,7 @@
         <v>45075.91971064815</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>44764</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20339,7 +20339,7 @@
         <v>45051.455</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>44098</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>45749</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>45362.62811342593</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>44868</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>44284</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>45203.63303240741</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>44824.36069444445</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>44251</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20862,7 +20862,7 @@
         <v>45621.34813657407</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44419</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45772.3078125</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>44524</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>45625</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>45208</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21209,7 +21209,7 @@
         <v>44879.70518518519</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21266,7 +21266,7 @@
         <v>44379</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21323,7 +21323,7 @@
         <v>44833.40876157407</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45730.35026620371</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45772.51127314815</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45405.57927083333</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21551,7 +21551,7 @@
         <v>44272</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>44743.47407407407</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21665,7 +21665,7 @@
         <v>44315</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>45705.66126157407</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>45330.50098379629</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>44266</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>44376</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21960,7 +21960,7 @@
         <v>45218</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>45772.30436342592</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>44300</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>44575.52831018518</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22212,7 +22212,7 @@
         <v>45273</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>45644.47878472223</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22326,7 +22326,7 @@
         <v>45356.4722800926</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>44231</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>44949</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>44285</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>44643</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>45086.3629050926</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>45253.55641203704</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>45737.43347222222</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>44949</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>44953.67443287037</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>45175</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>44963</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>44840</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>45433.58431712963</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>45694.68207175926</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>45383</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45435</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45084.54459490741</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>44895</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>44350</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>44143</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>45397</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23595,7 +23595,7 @@
         <v>44882</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23652,7 +23652,7 @@
         <v>45473.94501157408</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45259</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>45455.33037037037</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23823,7 +23823,7 @@
         <v>45147.65222222222</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>45147.65311342593</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>45147</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45450.64208333333</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>45450</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45755.36583333334</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>45253.63089120371</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24232,7 +24232,7 @@
         <v>45776.62563657408</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>45316.60306712963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44556</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45223</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>44272</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45239</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45776.47346064815</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45776.46369212963</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45776.59871527777</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44705.60626157407</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>45190.55609953704</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44845.48064814815</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>44470</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>45558.46283564815</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>44621</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45391.3395949074</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>45454.65774305556</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>44868.45741898148</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45485</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>44502</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>45104</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25429,7 +25429,7 @@
         <v>45104</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25486,7 +25486,7 @@
         <v>45783</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>45769</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44809</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>45202</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>45376.64532407407</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>45783.66429398148</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>44510</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>45075.90270833333</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>45075.91042824074</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -26014,7 +26014,7 @@
         <v>45075.91265046296</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>45075.92153935185</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>45576</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>44105</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26242,7 +26242,7 @@
         <v>44962</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26299,7 +26299,7 @@
         <v>45385.38146990741</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26356,7 +26356,7 @@
         <v>45089</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45131.666875</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45549</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>44866.63775462963</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>45187</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26641,7 +26641,7 @@
         <v>45735</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>45709.39361111111</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26760,7 +26760,7 @@
         <v>45418</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>45448.56746527777</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26874,7 +26874,7 @@
         <v>45385.36243055556</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26931,7 +26931,7 @@
         <v>45485.60261574074</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>45257</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -27045,7 +27045,7 @@
         <v>45536</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>45418.6968287037</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>45170</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27216,7 +27216,7 @@
         <v>44362.37172453704</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>44525</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27335,7 +27335,7 @@
         <v>44546</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>45572.57828703704</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>44516</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>44516.40674768519</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27573,7 +27573,7 @@
         <v>45063.35880787037</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>44956</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27687,7 +27687,7 @@
         <v>45468.45541666666</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>45468.45747685185</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
         <v>45460.44347222222</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27858,7 +27858,7 @@
         <v>44642.55565972222</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>44472</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>45785.65300925926</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>45610.39271990741</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>44153</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         <v>45537</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>45579</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>45119.57728009259</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28314,7 +28314,7 @@
         <v>44769.66039351852</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>45463.80486111111</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>45831.56521990741</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         <v>45457</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>45271</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28604,7 +28604,7 @@
         <v>45642.64634259259</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>45468.45628472222</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28718,7 +28718,7 @@
         <v>45352.74090277778</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28775,7 +28775,7 @@
         <v>45260</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28832,7 +28832,7 @@
         <v>44637</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>44325</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28951,7 +28951,7 @@
         <v>44578</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -29008,7 +29008,7 @@
         <v>44461</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>45443</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>45408.57707175926</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>44470.72987268519</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>44834.38636574074</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>44113</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29355,7 +29355,7 @@
         <v>45245</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>44333</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29469,7 +29469,7 @@
         <v>45786.55645833333</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29531,7 +29531,7 @@
         <v>45715</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45635.88849537037</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29650,7 +29650,7 @@
         <v>44108</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>44953.69298611111</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         <v>45533</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45547</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>44139.54078703704</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45524</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>44350</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45341.39853009259</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>44584.91001157407</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45177</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>45721.88684027778</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30277,7 +30277,7 @@
         <v>45483.57244212963</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30334,7 +30334,7 @@
         <v>44100</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>44869</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45600.4558912037</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45540</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>45272.64479166667</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>45272</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>44637</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>44474.62141203704</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30795,7 +30795,7 @@
         <v>45169</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>45385.37922453704</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>45729.7271875</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>44952.57989583333</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>44795</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>45469</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>45469</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>45075</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>45075</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>45075.90934027778</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>45713</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>45089</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31494,7 +31494,7 @@
         <v>45436</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>45518</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31608,7 +31608,7 @@
         <v>45735</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31665,7 +31665,7 @@
         <v>45475.61896990741</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31722,7 +31722,7 @@
         <v>45203.83891203703</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45589.68289351852</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31836,7 +31836,7 @@
         <v>44596</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>45636.38974537037</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>44395</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32007,7 +32007,7 @@
         <v>44708.67822916667</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>45840.70885416667</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>45798.66767361111</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32178,7 +32178,7 @@
         <v>44132</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32235,7 +32235,7 @@
         <v>45786</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32292,7 +32292,7 @@
         <v>45639.45166666667</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>45798.67082175926</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32406,7 +32406,7 @@
         <v>45798</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>45798.66104166667</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45797.58399305555</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>44607</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>45639.47385416667</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32691,7 +32691,7 @@
         <v>45586</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>45644.90815972222</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>44540</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32862,7 +32862,7 @@
         <v>45797.58350694444</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32919,7 +32919,7 @@
         <v>45414.65855324074</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32976,7 +32976,7 @@
         <v>44425</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33033,7 +33033,7 @@
         <v>44425</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>45450.64643518518</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>44133</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33209,7 +33209,7 @@
         <v>45640.60240740741</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33266,7 +33266,7 @@
         <v>45600.47275462963</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33323,7 +33323,7 @@
         <v>44580</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33380,7 +33380,7 @@
         <v>45089</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33437,7 +33437,7 @@
         <v>45478.42887731481</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33494,7 +33494,7 @@
         <v>45113</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33551,7 +33551,7 @@
         <v>45113</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33608,7 +33608,7 @@
         <v>44673</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>44985</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44904</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>45800</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>44648</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>44643</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33950,7 +33950,7 @@
         <v>45800</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>45800</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34064,7 +34064,7 @@
         <v>44143</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34121,7 +34121,7 @@
         <v>44901</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34178,7 +34178,7 @@
         <v>45799</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34235,7 +34235,7 @@
         <v>45800</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>45800</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34349,7 +34349,7 @@
         <v>45803.4675</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44816</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34463,7 +34463,7 @@
         <v>45456</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34520,7 +34520,7 @@
         <v>45617.58453703704</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>45224</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34634,7 +34634,7 @@
         <v>45800</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34696,7 +34696,7 @@
         <v>44592</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>45803.69228009259</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>45559.54706018518</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34867,7 +34867,7 @@
         <v>45121</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>45075.91148148148</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>45804.74479166666</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35038,7 +35038,7 @@
         <v>45726.48152777777</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>45549</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35152,7 +35152,7 @@
         <v>44813</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35209,7 +35209,7 @@
         <v>45075</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>45803.66587962963</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35323,7 +35323,7 @@
         <v>44145</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>45586</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>44649</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>44155.69458333333</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>45610.47414351852</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45847.37414351852</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35670,7 +35670,7 @@
         <v>45232</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35727,7 +35727,7 @@
         <v>44993.66707175926</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>45735.36594907408</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35846,7 +35846,7 @@
         <v>44124</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45729.71065972222</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35965,7 +35965,7 @@
         <v>44511.70518518519</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36022,7 +36022,7 @@
         <v>45531</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>45376.55484953704</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36136,7 +36136,7 @@
         <v>44977</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36193,7 +36193,7 @@
         <v>45386.34175925926</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36250,7 +36250,7 @@
         <v>45183</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36307,7 +36307,7 @@
         <v>44525</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36369,7 +36369,7 @@
         <v>44644</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36426,7 +36426,7 @@
         <v>44635</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36483,7 +36483,7 @@
         <v>44656</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36545,7 +36545,7 @@
         <v>45687.5038425926</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36607,7 +36607,7 @@
         <v>45810.42393518519</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36664,7 +36664,7 @@
         <v>44670</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36721,7 +36721,7 @@
         <v>45695.57881944445</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45608</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36840,7 +36840,7 @@
         <v>45617.62358796296</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>45069</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36974,7 +36974,7 @@
         <v>45442.45686342593</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37031,7 +37031,7 @@
         <v>45208.58004629629</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37088,7 +37088,7 @@
         <v>45155</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37145,7 +37145,7 @@
         <v>45790.81410879629</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37202,7 +37202,7 @@
         <v>44938</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>45810.5333912037</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37316,7 +37316,7 @@
         <v>45427.88731481481</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37373,7 +37373,7 @@
         <v>45202.65660879629</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>45664</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37487,7 +37487,7 @@
         <v>45810.45236111111</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37544,7 +37544,7 @@
         <v>45810.45263888889</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37601,7 +37601,7 @@
         <v>44624.59434027778</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37658,7 +37658,7 @@
         <v>44179</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>44162</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37777,7 +37777,7 @@
         <v>45810.45633101852</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>45147.65407407407</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>44687</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37953,7 +37953,7 @@
         <v>45811.60451388889</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38010,7 +38010,7 @@
         <v>45757.65178240741</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38067,7 +38067,7 @@
         <v>45775.41451388889</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38124,7 +38124,7 @@
         <v>44959.74533564815</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38181,7 +38181,7 @@
         <v>44902</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38238,7 +38238,7 @@
         <v>44697</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38295,7 +38295,7 @@
         <v>45735</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38352,7 +38352,7 @@
         <v>45146</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38414,7 +38414,7 @@
         <v>45522.44414351852</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>45687</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38533,7 +38533,7 @@
         <v>45813.63650462963</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45813.66961805556</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45813.6799537037</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38704,7 +38704,7 @@
         <v>45813.4709375</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>45685.44592592592</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38823,7 +38823,7 @@
         <v>45757.62482638889</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38880,7 +38880,7 @@
         <v>45534.38240740741</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>44923.90159722222</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>44183</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45174.68702546296</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>45412.4104050926</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45376.55638888889</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>45686.65545138889</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>45721.40780092592</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>44585</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>45709.40231481481</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39475,7 +39475,7 @@
         <v>44704</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39532,7 +39532,7 @@
         <v>45817.2565625</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39589,7 +39589,7 @@
         <v>45817.30329861111</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39646,7 +39646,7 @@
         <v>45817.31085648148</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39703,7 +39703,7 @@
         <v>45817.31708333334</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39760,7 +39760,7 @@
         <v>45817.31986111111</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39817,7 +39817,7 @@
         <v>45817.33503472222</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>45747.63471064815</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39936,7 +39936,7 @@
         <v>45706.40086805556</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39998,7 +39998,7 @@
         <v>45670.65921296296</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40055,7 +40055,7 @@
         <v>45817.291875</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40112,7 +40112,7 @@
         <v>45817.32538194444</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40169,7 +40169,7 @@
         <v>45552.52827546297</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40226,7 +40226,7 @@
         <v>45208</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40283,7 +40283,7 @@
         <v>45208</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40340,7 +40340,7 @@
         <v>45817.25471064815</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45237</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>45145.63584490741</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>44945.67409722223</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40568,7 +40568,7 @@
         <v>44937</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40625,7 +40625,7 @@
         <v>45817.34083333334</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45145.51</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>45700</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40801,7 +40801,7 @@
         <v>45215</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40858,7 +40858,7 @@
         <v>44680</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40915,7 +40915,7 @@
         <v>44629</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40977,7 +40977,7 @@
         <v>44617</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41034,7 +41034,7 @@
         <v>45692</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41091,7 +41091,7 @@
         <v>45188.41637731482</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41153,7 +41153,7 @@
         <v>45245</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41210,7 +41210,7 @@
         <v>45155</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41267,7 +41267,7 @@
         <v>45254</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41324,7 +41324,7 @@
         <v>45260.43225694444</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41381,7 +41381,7 @@
         <v>44708</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>44708.36708333333</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>45260.4333449074</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41557,7 +41557,7 @@
         <v>44746.58530092592</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41614,7 +41614,7 @@
         <v>44714.56040509259</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41671,7 +41671,7 @@
         <v>45824.37275462963</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41733,7 +41733,7 @@
         <v>45679</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>44684</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41847,7 +41847,7 @@
         <v>45127.69371527778</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41909,7 +41909,7 @@
         <v>45245</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41966,7 +41966,7 @@
         <v>44743.67418981482</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42028,7 +42028,7 @@
         <v>44732</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42085,7 +42085,7 @@
         <v>45208.70996527778</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42142,7 +42142,7 @@
         <v>45205</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45629.65143518519</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>44181</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42318,7 +42318,7 @@
         <v>44888</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42375,7 +42375,7 @@
         <v>44867.62090277778</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42432,7 +42432,7 @@
         <v>45701.44372685185</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42489,7 +42489,7 @@
         <v>45223</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42546,7 +42546,7 @@
         <v>44722</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42603,7 +42603,7 @@
         <v>45831.51659722222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>45831.65079861111</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42722,7 +42722,7 @@
         <v>44611</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42779,7 +42779,7 @@
         <v>45128</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42836,7 +42836,7 @@
         <v>44986.5887962963</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42893,7 +42893,7 @@
         <v>45048</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42950,7 +42950,7 @@
         <v>45831.4844212963</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43007,7 +43007,7 @@
         <v>45832.66385416667</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43064,7 +43064,7 @@
         <v>45831.54618055555</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>45740.47055555556</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43178,7 +43178,7 @@
         <v>44775</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43235,7 +43235,7 @@
         <v>44799.65013888889</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43292,7 +43292,7 @@
         <v>45223</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43349,7 +43349,7 @@
         <v>45680.42665509259</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45293</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43468,7 +43468,7 @@
         <v>45219.56697916667</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43525,7 +43525,7 @@
         <v>45834</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43582,7 +43582,7 @@
         <v>45876.45253472222</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43644,7 +43644,7 @@
         <v>45728.38409722222</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43701,7 +43701,7 @@
         <v>44813.59915509259</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43758,7 +43758,7 @@
         <v>44325</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43815,7 +43815,7 @@
         <v>45834.6447337963</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>45699.46283564815</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43929,7 +43929,7 @@
         <v>45070</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -43986,7 +43986,7 @@
         <v>45834.65538194445</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44043,7 +44043,7 @@
         <v>44693</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44100,7 +44100,7 @@
         <v>44963</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44157,7 +44157,7 @@
         <v>45112</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44214,7 +44214,7 @@
         <v>44266</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44271,7 +44271,7 @@
         <v>44266</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44328,7 +44328,7 @@
         <v>44867</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44385,7 +44385,7 @@
         <v>44778</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44442,7 +44442,7 @@
         <v>45623.62563657408</v>
       </c>
       